--- a/Freedenian_Ideologies_Global_Dataset_2026-10-03.xlsx
+++ b/Freedenian_Ideologies_Global_Dataset_2026-10-03.xlsx
@@ -15,9 +15,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'195 States'!$A$1:$M$196</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Methodology'!$A$1:$B$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sources'!$A$1:$C$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Change log'!$A$1:$F$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Methodology'!$A$1:$B$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sources'!$A$1:$C$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Change log'!$A$1:$F$112</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -46,12 +46,17 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE2D6"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -66,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -75,6 +80,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12687,7 +12695,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Conservative core combined strongly with nationalism, populism, religion or authoritarianism.</t>
+          <t>Conservative core combined strongly with nationalism, populism, religious-nationalist claims or authoritarian rule.</t>
         </is>
       </c>
     </row>
@@ -12843,7 +12851,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Religious legitimacy fused with dynastic or national authority.</t>
+          <t>Theocratic claims to legitimacy fused with dynastic or national authority.</t>
         </is>
       </c>
     </row>
@@ -13050,7 +13058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -13070,355 +13078,367 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Snapshot date</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-03 (leaders as in the corrected conservatism dataset of the same date)</t>
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Created with Claude. Illustrative only.</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>This dataset's ideological codes were created with Claude (Anthropic's AI model), starting from a dataset generated with ChatGPT. It is a representative teaching illustration, not the result of actual research. Treat every code as material to question, not as evidence.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Snapshot date</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>195 states: 193 UN members + Palestine + Vatican City. Country names follow UN short names.</t>
+          <t>2026-10-03 (leaders as in the corrected conservatism dataset of the same date)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Leader source</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Wikipedia list of current heads of state and government (retrieved 2026-10-03), cross-checked against news reports. Unchanged from the source dataset.</t>
+          <t>195 states: 193 UN members + Palestine + Vatican City. Country names follow UN short names.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Framework</t>
+          <t>Leader source</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Michael Freeden's morphological approach: an ideology is a configuration of core, adjacent and peripheral concepts, each 'decontested' (given one settled meaning). Families are identified by their core concepts, not by a left-right position or a checklist of policies. Each family appears in several decontested variants.</t>
+          <t>Heads of state and government are taken from the ChatGPT-generated source dataset, which states that they follow the Wikipedia list of current heads of state and government (retrieved 2026-10-03), cross-checked against news reports. They have not been independently verified for this revision.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Unit coded</t>
+          <t>Framework</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>The governing ideology of the executive that actually directs policy (normally the head of government, or the head of state where executive power sits there). A ceremonial head of state does not determine the code.</t>
+          <t>Michael Freeden's morphological approach: an ideology is a configuration of core, adjacent and peripheral concepts, each 'decontested' (given one settled meaning). Families are identified by their core concepts, not by a left-right position or a checklist of policies. Each family appears in several decontested variants.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Ideological family</t>
+          <t>Unit coded</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>The macro-ideology whose core concepts organise the government's programme: Liberalism, Conservatism, Socialism, plus Religious-political ideology and a residual Traditionalist-authoritarian category. Nationalism is never coded as the family: in Freeden's account it is thin-centred and needs a host, so it is recorded as a component (and signalled by "+" variants).</t>
+          <t>The governing ideology of the executive that actually directs policy (normally the head of government, or the head of state where executive power sits there). A ceremonial head of state does not determine the code.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Liberalism</t>
+          <t>Ideological family</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Core concepts (Freeden): liberty, rationality, individuality, progress, sociability, the general interest, and limited, accountable power.</t>
+          <t>The macro-ideology whose core concepts organise the government's programme: Liberalism, Conservatism, Socialism, plus Religious-political ideology and a residual Traditionalist-authoritarian category. Nationalism is never coded as the family: in Freeden's account it is thin-centred and needs a host, so it is recorded as a component (and signalled by "+" variants).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Conservatism</t>
+          <t>Liberalism</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Core concepts (Freeden): change must be controlled so that it appears natural and organic; social order has extra-human origins (history, God, nature, the market or monarchy) and is independent of human will.</t>
+          <t>Core concepts (Freeden): liberty, rationality, individuality, progress, sociability, the general interest, and limited, accountable power.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Socialism</t>
+          <t>Conservatism</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Core concepts (Freeden): the constitutive nature of the group, equality, human welfare as the goal of politics, human activity/praxis, and history as the arena of change.</t>
+          <t>Core concepts (Freeden): change must be controlled so that it appears natural and organic; social order has extra-human origins (history, God, nature, the market or monarchy) and is independent of human will.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Religious-political ideology</t>
+          <t>Socialism</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Political order is derived from religious doctrine and religious authority. Not one of Freeden's three macro-ideologies; included because his morphological method treats such belief systems as ideologies with their own core concepts (divine sovereignty, sacred law, clerical or dynastic-religious authority).</t>
+          <t>Core concepts (Freeden): the constitutive nature of the group, equality, human welfare as the goal of politics, human activity/praxis, and history as the arena of change.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Religious-political ideology</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Residual category, not a Freeden family: hierarchy, order, continuity and state authority dominate, but no liberal, conservative or socialist programme is sustained at the core. Typical of military, personalist and dominant-party regimes. Calling these conservative would overstate the presence of conservative morphology; nationalism usually appears as a component.</t>
+          <t>Political order is derived from religious doctrine and religious authority. Not one of Freeden's three macro-ideologies; included because his morphological method treats such belief systems as ideologies with their own core concepts (divine sovereignty, sacred law, clerical or dynastic-religious authority).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>L - Liberalism</t>
+          <t>Traditionalist-authoritarian</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Clear liberal morphology: social, market or centrist liberalism.</t>
+          <t>Residual category, not a Freeden family: hierarchy, order, continuity and state authority dominate, but no liberal, conservative or socialist programme is sustained at the core. Typical of military, personalist and dominant-party regimes. Calling these conservative would overstate the presence of conservative morphology; nationalism usually appears as a component.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>L+ - National / populist liberalism</t>
+          <t>L - Liberalism</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Liberal core combined strongly with nationalism or populism.</t>
+          <t>Clear liberal morphology: social, market or centrist liberalism.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>C - Conservatism</t>
+          <t>L+ - National / populist liberalism</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Clear conservative morphology: Christian-democratic, liberal-conservative or customary conservatism.</t>
+          <t>Liberal core combined strongly with nationalism or populism.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>C+ - National / religious / populist conservatism</t>
+          <t>C - Conservatism</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Conservative core combined strongly with nationalism, populism, religion or authoritarianism.</t>
+          <t>Clear conservative morphology: Christian-democratic, liberal-conservative or customary conservatism.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Cm - Monarchical traditionalism</t>
+          <t>C+ - National / religious / populist conservatism</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>A ruling monarchy manages change from above to preserve a dynastic and often religious order.</t>
+          <t>Conservative core combined strongly with nationalism, populism, religious-nationalist claims or authoritarian rule.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>S - Social democracy</t>
+          <t>Cm - Monarchical traditionalism</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Social democracy or democratic socialism within a competitive democracy.</t>
+          <t>A ruling monarchy manages change from above to preserve a dynastic and often religious order.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>S+ - Left-nationalist / left-populist socialism</t>
+          <t>S - Social democracy</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Socialist core combined strongly with nationalism, populism or authoritarianism.</t>
+          <t>Social democracy or democratic socialism within a competitive democracy.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>SM - Marxism-Leninism</t>
+          <t>S+ - Left-nationalist / left-populist socialism</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Communist party-state; the party's doctrine organises state and economy.</t>
+          <t>Socialist core combined strongly with nationalism, populism or authoritarianism.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>RE - Theocracy</t>
+          <t>SM - Marxism-Leninism</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Religious doctrine and clerical authority define the state.</t>
+          <t>Communist party-state; the party's doctrine organises state and economy.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>RE+ - Religious-national rule</t>
+          <t>RE - Theocracy</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Religious legitimacy fused with dynastic or national authority.</t>
+          <t>Religious doctrine and clerical authority define the state.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>T - Traditionalist-authoritarian</t>
+          <t>RE+ - Religious-national rule</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Order, hierarchy and continuity without a sustained macro-ideology (military, personalist or dominant-party rule).</t>
+          <t>Theocratic claims to legitimacy fused with dynastic or national authority.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>The "+" variants</t>
+          <t>T - Traditionalist-authoritarian</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>As in the earlier conservatism scheme (C vs C+), "+" marks a family core combined strongly with a thin-centred ideology (nationalism, populism) or with religion or authoritarian rule. C+ is national/religious/populist conservatism, S+ left-nationalist or left-populist socialism, L+ national or populist liberalism, RE+ religious-national rule.</t>
+          <t>Order, hierarchy and continuity without a sustained macro-ideology (military, personalist or dominant-party rule).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Secondary family</t>
+          <t>The "+" variants</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>A second family whose core concepts are clearly present in adjacent positions (e.g. coalition partners). Written VARIANT/SECONDARY, e.g. C/LIB = conservatism with liberal adjacency, T/SOC = traditionalist-authoritarian rule with a socialist legacy.</t>
+          <t>As in the earlier conservatism scheme (C vs C+), "+" marks a family core combined strongly with a thin-centred ideology (nationalism, populism), with theocratic or religious-nationalist claims, or with authoritarian rule. C+ is national/religious/populist conservatism, S+ left-nationalist or left-populist socialism, L+ national or populist liberalism, RE+ religious-national rule.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Thin-centred components</t>
+          <t>Secondary family</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Freeden's thin-centred ideologies that attach to a host: Nationalism, Populism (people vs. elite; see also Mudde 2004), Ecologism (green), Feminism. Listed where they visibly shape the governing programme.</t>
+          <t>A second family whose core concepts are clearly present in adjacent positions (e.g. coalition partners). Written VARIANT/SECONDARY, e.g. C/LIB = conservatism with liberal adjacency, T/SOC = traditionalist-authoritarian rule with a socialist legacy.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Adjacent concepts / regime context</t>
+          <t>Thin-centred components</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Religion and Developmentalism are recorded as adjacent concepts. Authoritarian rule is regime context, not an ideology: it is recorded so that students can separate how power is held from what ideas justify it.</t>
+          <t>Freeden's thin-centred ideologies that attach to a host: Nationalism, Populism (people vs. elite; see also Mudde 2004), Ecologism (green), Feminism. Listed where they visibly shape the governing programme.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Hard cases</t>
+          <t>Adjacent concepts / regime context</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Russia is coded C+ because "traditional values" conservatism is now official doctrine, not just regime practice. North Korea stays in the socialist family (SM) although Juche nationalism dominates its core. Ex-Marxist dominant parties (Angola, Mozambique, Tanzania, Eritrea, Zimbabwe, Republic of the Congo) are coded T with SOC as secondary family, because socialism survives only as a legacy.</t>
+          <t>Religion and Developmentalism are recorded as adjacent concepts. Authoritarian rule is regime context, not an ideology: it is recorded so that students can separate how power is held from what ideas justify it.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Previous code</t>
+          <t>Hard cases</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>The final column keeps the code from the conservatism-only scheme (C, C+, L/C, R, T and hybrids) so the two classifications can be compared.</t>
+          <t>Russia is coded C+ because "traditional values" conservatism is now official doctrine, not just regime practice. North Korea stays in the socialist family (SM) although Juche nationalism dominates its core. Ex-Marxist dominant parties (Angola, Mozambique, Tanzania, Eritrea, Zimbabwe, Republic of the Congo) are coded T with SOC as secondary family, because socialism survives only as a legacy.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>Previous code</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>The final column keeps the code from the conservatism-only scheme (C, C+, L/C, R, T and hybrids) so the two classifications can be compared.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
           <t>Caveat</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Codes are interpretive judgements for teaching and discussion, not measurements. Coalitions, caretaker and transitional governments are coded by their dominant governing morphology. The policy column is descriptive and unchanged from the source dataset.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B30"/>
+  <autoFilter ref="A1:B31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13429,7 +13449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -13457,68 +13477,64 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Current leaders</t>
+          <t>Base dataset</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>UN Protocol &amp; Liaison Service</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.un.org/dgacm/en/content/protocol/hshgnfa</t>
-        </is>
-      </c>
+          <t>Freedenian Conservatism Global Dataset (snapshot 2026-10-03, corrected), generated with ChatGPT and supplied for this course; ideological codes revised with Claude.</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Current leaders cross-check</t>
+          <t>Current leaders</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CIA World Leaders</t>
+          <t>UN Protocol &amp; Liaison Service</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>https://www.cia.gov/resources/world-leaders/</t>
+          <t>https://www.un.org/dgacm/en/content/protocol/hshgnfa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Current heads list used for 2026 snapshot</t>
+          <t>Current leaders cross-check</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Wikipedia – List of current heads of state and government</t>
+          <t>CIA World Leaders</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/List_of_current_heads_of_state_and_government</t>
+          <t>https://www.cia.gov/resources/world-leaders/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Freeden framework</t>
+          <t>Current heads list used for 2026 snapshot</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Stanford Encyclopedia of Philosophy – Conservatism</t>
+          <t>Wikipedia – List of current heads of state and government</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>https://seop.illc.uva.nl/entries/conservatism/</t>
+          <t>https://en.wikipedia.org/wiki/List_of_current_heads_of_state_and_government</t>
         </is>
       </c>
     </row>
@@ -13530,50 +13546,54 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Freeden, M. (1996) Ideologies and Political Theory: A Conceptual Approach. Oxford: Clarendon Press.</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n"/>
+          <t>Stanford Encyclopedia of Philosophy – Conservatism</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>https://seop.illc.uva.nl/entries/conservatism/</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Thin-centred nationalism</t>
+          <t>Freeden framework</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Freeden, M. (1998) "Is Nationalism a Distinct Ideology?" Political Studies 46(4): 748-765.</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1111/1467-9248.00165</t>
-        </is>
-      </c>
+          <t>Freeden, M. (1996) Ideologies and Political Theory: A Conceptual Approach. Oxford: Clarendon Press.</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Freeden framework (introductory)</t>
+          <t>Thin-centred nationalism</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Freeden, M. (2003) Ideology: A Very Short Introduction. Oxford: Oxford University Press.</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n"/>
+          <t>Freeden, M. (1998) "Is Nationalism a Distinct Ideology?" Political Studies 46(4): 748-765.</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1111/1467-9248.00165</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Families and variants</t>
+          <t>Freeden framework (introductory)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Freeden, M., Sargent, L.T. and Stears, M. (eds) (2013) The Oxford Handbook of Political Ideologies. Oxford: Oxford University Press.</t>
+          <t>Freeden, M. (2003) Ideology: A Very Short Introduction. Oxford: Oxford University Press.</t>
         </is>
       </c>
       <c r="C9" s="2" t="n"/>
@@ -13581,22 +13601,35 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>Families and variants</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Freeden, M., Sargent, L.T. and Stears, M. (eds) (2013) The Oxford Handbook of Political Ideologies. Oxford: Oxford University Press.</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>Thin-centred populism</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Mudde, C. (2004) "The Populist Zeitgeist." Government and Opposition 39(4): 541-563.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1111/j.1477-7053.2004.00135.x</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C10"/>
+  <autoFilter ref="A1:C11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13607,7 +13640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F111"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13653,7 +13686,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Recoding</t>
+          <t>Notice</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -13663,22 +13696,22 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Methodology</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Five families with nationalism as a possible primary family (LIB, CON, SOC, NAT, REL)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Variants within each family (L, L+; C, C+, Cm; S, S+, SM; RE, RE+) plus residual T; nationalism only as a component</t>
+          <t>"Created with Claude. Illustrative only." notice; ChatGPT origin of the base dataset recorded; "+" variants worded as theocratic or religious-nationalist claims rather than religion</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Nationalism is thin-centred (Freeden 1998) and is not treated as a host ideology; variants show the range of decontested forms within each family, as C and C+ did in the conservatism scheme</t>
+          <t>Clarify provenance and that the dataset is a teaching illustration, not research</t>
         </is>
       </c>
     </row>
@@ -13690,7 +13723,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>All 195 states</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -13700,17 +13733,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>NAT/SOC</t>
+          <t>Five families with nationalism as a possible primary family (LIB, CON, SOC, NAT, REL)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>Variants within each family (L, L+; C, C+, Cm; S, S+, SM; RE, RE+) plus residual T; nationalism only as a component</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
+          <t>Nationalism is thin-centred (Freeden 1998) and is not treated as a host ideology; variants show the range of decontested forms within each family, as C and C+ did in the conservatism scheme</t>
         </is>
       </c>
     </row>
@@ -13722,7 +13755,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -13737,7 +13770,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>T/SOC</t>
+          <t>S+</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -13754,7 +13787,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -13764,12 +13797,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/SOC</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>T/SOC</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -13786,7 +13819,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -13796,12 +13829,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>NAT/CON</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -13818,7 +13851,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -13833,7 +13866,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>T/SOC</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -13850,7 +13883,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Belarus</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -13860,12 +13893,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>NAT/LIB</t>
+          <t>NAT/CON</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>C+/SOC</t>
+          <t>T/SOC</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -13882,7 +13915,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -13892,12 +13925,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>NAT/SOC</t>
+          <t>NAT/LIB</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>C+/SOC</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -13914,7 +13947,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -13946,7 +13979,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -13956,12 +13989,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/SOC</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>S+</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -13978,7 +14011,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -13988,12 +14021,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>NAT/CON</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>T/CON</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -14010,7 +14043,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -14025,7 +14058,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>T/CON</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -14042,7 +14075,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Central African Republic</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -14052,7 +14085,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/CON</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -14074,7 +14107,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Chad</t>
+          <t>Central African Republic</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -14106,7 +14139,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Chad</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -14116,12 +14149,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>NAT/REL</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>T/REL</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -14138,7 +14171,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -14148,12 +14181,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>NAT/CON</t>
+          <t>NAT/REL</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>T/REL</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -14170,7 +14203,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Djibouti</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -14180,12 +14213,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/CON</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -14202,7 +14235,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Djibouti</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -14234,7 +14267,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>El Salvador</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -14244,12 +14277,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>NAT/CON</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -14266,7 +14299,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Equatorial Guinea</t>
+          <t>El Salvador</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -14276,12 +14309,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/CON</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -14298,7 +14331,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Eritrea</t>
+          <t>Equatorial Guinea</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -14308,12 +14341,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>NAT/SOC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>T/SOC</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -14330,7 +14363,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Eritrea</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -14340,12 +14373,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>NAT/LIB</t>
+          <t>NAT/SOC</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>T/LIB</t>
+          <t>T/SOC</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -14362,7 +14395,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -14372,12 +14405,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/LIB</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>T/LIB</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -14394,7 +14427,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -14404,12 +14437,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>NAT/CON</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -14426,7 +14459,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -14436,12 +14469,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/CON</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -14458,7 +14491,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -14490,7 +14523,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -14500,12 +14533,12 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>NAT/CON</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -14522,7 +14555,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -14554,7 +14587,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -14586,7 +14619,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -14596,12 +14629,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/CON</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -14618,7 +14651,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Kyrgyzstan</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -14628,12 +14661,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>NAT/CON</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>T/CON</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -14650,7 +14683,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Libya</t>
+          <t>Kyrgyzstan</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -14660,12 +14693,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>NAT/LIB</t>
+          <t>NAT/CON</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>T/LIB</t>
+          <t>T/CON</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -14682,7 +14715,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Libya</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -14692,12 +14725,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/LIB</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>T/LIB</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -14714,7 +14747,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Maldives</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -14724,12 +14757,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>NAT/REL</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -14746,7 +14779,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>Maldives</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -14756,12 +14789,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/REL</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -14778,7 +14811,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Mauritania</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -14788,12 +14821,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>NAT/REL</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>T/REL</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -14810,7 +14843,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Mauritania</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -14820,12 +14853,12 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>NAT/SOC</t>
+          <t>NAT/REL</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>T/SOC</t>
+          <t>T/REL</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -14842,7 +14875,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -14852,12 +14885,12 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>NAT/REL</t>
+          <t>NAT/SOC</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>T/REL</t>
+          <t>T/SOC</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -14874,7 +14907,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Nicaragua</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -14884,12 +14917,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>NAT/SOC</t>
+          <t>NAT/REL</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>T/REL</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -14906,7 +14939,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Niger</t>
+          <t>Nicaragua</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -14916,12 +14949,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/SOC</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>S+</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -14938,7 +14971,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>North Korea</t>
+          <t>Niger</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -14948,12 +14981,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>NAT/SOC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>SM</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -14970,7 +15003,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>North Korea</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -14980,12 +15013,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>NAT/REL</t>
+          <t>NAT/SOC</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -15002,7 +15035,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Palestine</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -15012,12 +15045,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/REL</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -15034,7 +15067,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Republic of the Congo</t>
+          <t>Palestine</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -15044,12 +15077,12 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>NAT/SOC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>T/SOC</t>
+          <t>S+</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -15066,7 +15099,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Republic of the Congo</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -15076,12 +15109,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>NAT/CON</t>
+          <t>NAT/SOC</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>T/SOC</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -15098,7 +15131,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -15108,12 +15141,12 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/CON</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -15130,7 +15163,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -15140,12 +15173,12 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>NAT/SOC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -15162,7 +15195,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -15172,12 +15205,12 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>NAT/CON</t>
+          <t>NAT/SOC</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>S+</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -15194,7 +15227,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -15204,12 +15237,12 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>NAT/SOC</t>
+          <t>NAT/CON</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>S+/CON</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -15226,7 +15259,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -15236,12 +15269,12 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>NAT/REL</t>
+          <t>NAT/SOC</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>T/REL</t>
+          <t>S+/CON</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -15258,7 +15291,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -15268,12 +15301,12 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/REL</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>T/REL</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -15290,7 +15323,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Sudan</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -15322,7 +15355,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Tajikistan</t>
+          <t>Sudan</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -15354,7 +15387,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Tajikistan</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -15364,12 +15397,12 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>NAT/SOC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>T/SOC</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -15386,7 +15419,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Timor-Leste</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -15396,12 +15429,12 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/SOC</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>L+</t>
+          <t>T/SOC</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -15418,7 +15451,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Timor-Leste</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -15433,7 +15466,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>L+</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -15450,7 +15483,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -15482,7 +15515,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Turkmenistan</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -15514,7 +15547,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Turkmenistan</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -15524,12 +15557,12 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>NAT/CON</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>T/CON</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -15546,7 +15579,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -15561,7 +15594,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>T/CON</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -15578,7 +15611,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -15588,12 +15621,12 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/CON</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -15610,7 +15643,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -15620,12 +15653,12 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>NAT/REL</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>T/REL</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -15642,7 +15675,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -15652,12 +15685,12 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/REL</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>T/SOC</t>
+          <t>T/REL</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -15674,7 +15707,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>All 195 states</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -15684,17 +15717,17 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Conservatism-only scheme (C, C+, L/C, R, T)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Freeden ideological families (LIB, CON, SOC, NAT, REL) + secondary family + thin-centred components</t>
+          <t>T/SOC</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Dataset broadened from "how conservative is this government?" to "which ideological family organises it?"; previous code retained in the last column</t>
+          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
         </is>
       </c>
     </row>
@@ -15706,7 +15739,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>All 195 states</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -15716,17 +15749,17 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>R - centre-right security-oriented</t>
+          <t>Conservatism-only scheme (C, C+, L/C, R, T)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>SOC/NAT - social democracy (LSDP-led coalition)</t>
+          <t>Freeden ideological families (LIB, CON, SOC, NAT, REL) + secondary family + thin-centred components</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Prime Minister Sinkevičius leads the Social Democratic Party (LSDP); previous R code did not match the governing party</t>
+          <t>Dataset broadened from "how conservative is this government?" to "which ideological family organises it?"; previous code retained in the last column</t>
         </is>
       </c>
     </row>
@@ -15738,7 +15771,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>T-coded states (39)</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -15748,17 +15781,17 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>T - traditionalist-authoritarian</t>
+          <t>R - centre-right security-oriented</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>NAT, CON (monarchical traditionalism) or REL</t>
+          <t>SOC/NAT - social democracy (LSDP-led coalition)</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>The residual T category is not a Freeden family; split by the core concepts that organise each regime</t>
+          <t>Prime Minister Sinkevičius leads the Social Democratic Party (LSDP); previous R code did not match the governing party</t>
         </is>
       </c>
     </row>
@@ -15770,7 +15803,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>L/C-coded states (59)</t>
+          <t>T-coded states (39)</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -15780,81 +15813,81 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>L/C</t>
+          <t>T - traditionalist-authoritarian</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>LIB or SOC (social democracy) by governing party, NAT where liberation/developmental nationalism dominates</t>
+          <t>NAT, CON (monarchical traditionalism) or REL</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>L/C merged liberal and socialist governments; Freeden treats liberalism and socialism as distinct macro-ideologies</t>
+          <t>The residual T category is not a Freeden family; split by the core concepts that organise each regime</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Factual</t>
+          <t>Recoding</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>L/C-coded states (59)</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Head of state</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Mohammed Shahabuddin</t>
+          <t>L/C</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Mirza Fakhrul Islam Alamgir</t>
+          <t>LIB or SOC (social democracy) by governing party, NAT where liberation/developmental nationalism dominates</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Shahabuddin resigned 24 Jul 2026; Alamgir elected 20 Aug 2026</t>
+          <t>L/C merged liberal and socialist governments; Freeden treats liberalism and socialism as distinct macro-ideologies</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>C/L split</t>
+          <t>Factual</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Head of state</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>C/L — centre-right liberal</t>
+          <t>Mohammed Shahabuddin</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>R — centre-right liberal</t>
+          <t>Mirza Fakhrul Islam Alamgir</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
+          <t>Shahabuddin resigned 24 Jul 2026; Alamgir elected 20 Aug 2026</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15899,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -15876,17 +15909,17 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>C/L — fragmented coalition</t>
+          <t>C/L — centre-right liberal</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L/C — fragmented coalition</t>
+          <t>R — centre-right liberal</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
+          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
         </is>
       </c>
     </row>
@@ -15898,7 +15931,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Congo, Democratic Republic of the</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -15908,12 +15941,12 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>C/L — centrist-developmental</t>
+          <t>C/L — fragmented coalition</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>L/C — centrist-developmental</t>
+          <t>L/C — fragmented coalition</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -15930,7 +15963,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Congo, Democratic Republic of the</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -15940,17 +15973,17 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>C/L — moderate centre-right</t>
+          <t>C/L — centrist-developmental</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>R — moderate centre-right</t>
+          <t>L/C — centrist-developmental</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
+          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
         </is>
       </c>
     </row>
@@ -15962,7 +15995,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -15972,17 +16005,17 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>C/L — liberal-centrist, not primarily conservative</t>
+          <t>C/L — moderate centre-right</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>L/C — liberal-centrist, not primarily conservative</t>
+          <t>R — moderate centre-right</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
+          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
         </is>
       </c>
     </row>
@@ -15994,7 +16027,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -16004,12 +16037,12 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>C/L — developmental-centrist</t>
+          <t>C/L — liberal-centrist, not primarily conservative</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L/C — developmental-centrist</t>
+          <t>L/C — liberal-centrist, not primarily conservative</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -16026,7 +16059,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -16036,17 +16069,17 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>C/L — developmental centre-right</t>
+          <t>C/L — developmental-centrist</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>R — developmental centre-right</t>
+          <t>L/C — developmental-centrist</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
+          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
         </is>
       </c>
     </row>
@@ -16058,7 +16091,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Kiribati</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -16068,17 +16101,17 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>C/L — developmental-centrist</t>
+          <t>C/L — developmental centre-right</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L/C — developmental-centrist</t>
+          <t>R — developmental centre-right</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
+          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
         </is>
       </c>
     </row>
@@ -16090,7 +16123,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Kiribati</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -16100,17 +16133,17 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>C/L — centre-right liberal</t>
+          <t>C/L — developmental-centrist</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>R — centre-right liberal</t>
+          <t>L/C — developmental-centrist</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
+          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
         </is>
       </c>
     </row>
@@ -16122,7 +16155,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -16132,17 +16165,17 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>C/L — institutional/coalitional</t>
+          <t>C/L — centre-right liberal</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L/C — institutional/coalitional</t>
+          <t>R — centre-right liberal</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
+          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
         </is>
       </c>
     </row>
@@ -16154,7 +16187,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -16164,17 +16197,17 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>C/L — centre-right developmental</t>
+          <t>C/L — institutional/coalitional</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>R — centre-right developmental</t>
+          <t>L/C — institutional/coalitional</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
+          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
         </is>
       </c>
     </row>
@@ -16186,7 +16219,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Libya</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -16196,17 +16229,17 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>C/L — fragmented transitional</t>
+          <t>C/L — centre-right developmental</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>L/C — fragmented transitional</t>
+          <t>R — centre-right developmental</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
+          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
         </is>
       </c>
     </row>
@@ -16218,7 +16251,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Libya</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -16228,17 +16261,17 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>C/L — centre-right security-oriented</t>
+          <t>C/L — fragmented transitional</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>R — centre-right security-oriented</t>
+          <t>L/C — fragmented transitional</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
+          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
         </is>
       </c>
     </row>
@@ -16250,7 +16283,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -16260,12 +16293,12 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>C/L — centre-right</t>
+          <t>C/L — centre-right security-oriented</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>R — centre-right</t>
+          <t>R — centre-right security-oriented</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -16282,7 +16315,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -16292,17 +16325,17 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>C/L — coalition/centrist</t>
+          <t>C/L — centre-right</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>L/C — coalition/centrist</t>
+          <t>R — centre-right</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
+          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
         </is>
       </c>
     </row>
@@ -16314,7 +16347,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Moldova</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -16324,12 +16357,12 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>C/L — liberal-centrist</t>
+          <t>C/L — coalition/centrist</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L/C — liberal-centrist</t>
+          <t>L/C — coalition/centrist</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -16346,7 +16379,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Moldova</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -16356,12 +16389,12 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>C/L — populist-centrist</t>
+          <t>C/L — liberal-centrist</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>L/C — populist-centrist</t>
+          <t>L/C — liberal-centrist</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -16378,7 +16411,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -16388,17 +16421,17 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>C/L — centre-right</t>
+          <t>C/L — populist-centrist</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>R — centre-right</t>
+          <t>L/C — populist-centrist</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
+          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
         </is>
       </c>
     </row>
@@ -16410,7 +16443,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Papua New Guinea</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -16420,17 +16453,17 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>C/L — developmental-centrist</t>
+          <t>C/L — centre-right</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>L/C — developmental-centrist</t>
+          <t>R — centre-right</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
+          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
         </is>
       </c>
     </row>
@@ -16442,7 +16475,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Papua New Guinea</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -16452,12 +16485,12 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>C/L — split executive</t>
+          <t>C/L — developmental-centrist</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>L/C — split executive</t>
+          <t>L/C — developmental-centrist</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -16474,7 +16507,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -16484,12 +16517,12 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>C/L — centrist caretaker</t>
+          <t>C/L — split executive</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>L/C — centrist caretaker</t>
+          <t>L/C — split executive</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -16506,7 +16539,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Saint Vincent and the Grenadines</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -16516,17 +16549,17 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>C/L — centre-right</t>
+          <t>C/L — centrist caretaker</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>R — centre-right</t>
+          <t>L/C — centrist caretaker</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
+          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
         </is>
       </c>
     </row>
@@ -16538,7 +16571,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Samoa</t>
+          <t>Saint Vincent and the Grenadines</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -16548,17 +16581,17 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>C/L — customary/centrist</t>
+          <t>C/L — centre-right</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>L/C — customary/centrist</t>
+          <t>R — centre-right</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
+          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
         </is>
       </c>
     </row>
@@ -16570,7 +16603,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>San Marino</t>
+          <t>Samoa</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -16580,12 +16613,12 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>C/L — centrist</t>
+          <t>C/L — customary/centrist</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>L/C — centrist</t>
+          <t>L/C — customary/centrist</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -16602,7 +16635,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>São Tomé and Príncipe</t>
+          <t>San Marino</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -16612,12 +16645,12 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>C/L — centre-right/centrist</t>
+          <t>C/L — centrist</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>L/C — centre-right/centrist</t>
+          <t>L/C — centrist</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -16634,7 +16667,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>São Tomé and Príncipe</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -16644,12 +16677,12 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>C/L — nationalist-developmental</t>
+          <t>C/L — centre-right/centrist</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>L/C — nationalist-developmental</t>
+          <t>L/C — centre-right/centrist</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -16666,7 +16699,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Solomon Islands</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -16676,17 +16709,17 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>C/L — centre-right/coalitional</t>
+          <t>C/L — nationalist-developmental</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>R — centre-right/coalitional</t>
+          <t>L/C — nationalist-developmental</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
+          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
         </is>
       </c>
     </row>
@@ -16698,7 +16731,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Solomon Islands</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -16708,17 +16741,17 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>C/L — coalition/centrist</t>
+          <t>C/L — centre-right/coalitional</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>L/C — coalition/centrist</t>
+          <t>R — centre-right/coalitional</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
+          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
         </is>
       </c>
     </row>
@@ -16730,7 +16763,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -16740,17 +16773,17 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>C/L — centre-right caretaker</t>
+          <t>C/L — coalition/centrist</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>R — centre-right caretaker</t>
+          <t>L/C — coalition/centrist</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
+          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
         </is>
       </c>
     </row>
@@ -16762,7 +16795,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -16772,17 +16805,17 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>C/L — consociational centre</t>
+          <t>C/L — centre-right caretaker</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>L/C — consociational centre</t>
+          <t>R — centre-right caretaker</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
+          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
         </is>
       </c>
     </row>
@@ -16794,7 +16827,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -16804,12 +16837,12 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>C/L — developmental-centrist</t>
+          <t>C/L — consociational centre</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>L/C — developmental-centrist</t>
+          <t>L/C — consociational centre</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -16826,7 +16859,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Timor-Leste</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -16836,12 +16869,12 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>C/L — nationalist-developmental</t>
+          <t>C/L — developmental-centrist</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>L/C — nationalist-developmental</t>
+          <t>L/C — developmental-centrist</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -16858,7 +16891,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Trinidad and Tobago</t>
+          <t>Timor-Leste</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -16868,12 +16901,12 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>C/L — centre-right/centrist</t>
+          <t>C/L — nationalist-developmental</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>L/C — centre-right/centrist</t>
+          <t>L/C — nationalist-developmental</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -16890,7 +16923,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Trinidad and Tobago</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -16900,12 +16933,12 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>C/L — wartime national-centrist</t>
+          <t>C/L — centre-right/centrist</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>L/C — wartime national-centrist</t>
+          <t>L/C — centre-right/centrist</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -16922,7 +16955,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -16932,12 +16965,12 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>C/L — liberal-centrist</t>
+          <t>C/L — wartime national-centrist</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>L/C — liberal-centrist</t>
+          <t>L/C — wartime national-centrist</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -16949,32 +16982,32 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Naming</t>
+          <t>C/L split</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Congo, Democratic Republic of the</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Congo, Democratic Republic of the</t>
+          <t>C/L — liberal-centrist</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>L/C — liberal-centrist</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Use UN official short name</t>
+          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
         </is>
       </c>
     </row>
@@ -16986,7 +17019,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Congo, Republic of the</t>
+          <t>Congo, Democratic Republic of the</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -16996,12 +17029,12 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Congo, Republic of the</t>
+          <t>Congo, Democratic Republic of the</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Republic of the Congo</t>
+          <t>Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -17018,7 +17051,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Congo, Republic of the</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -17028,12 +17061,12 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Congo, Republic of the</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Republic of the Congo</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -17050,7 +17083,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Micronesia</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -17060,12 +17093,12 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Micronesia</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Federated States of Micronesia</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -17082,27 +17115,27 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Micronesia</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Head of state / government</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Bongbong Marcos</t>
+          <t>Micronesia</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Ferdinand "Bongbong" Marcos Jr.</t>
+          <t>Federated States of Micronesia</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Full formal name</t>
+          <t>Use UN official short name</t>
         </is>
       </c>
     </row>
@@ -17114,27 +17147,27 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Head of state</t>
+          <t>Head of state / government</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Salman</t>
+          <t>Bongbong Marcos</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Salman bin Abdulaziz Al Saud</t>
+          <t>Ferdinand "Bongbong" Marcos Jr.</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Full name for consistency</t>
+          <t>Full formal name</t>
         </is>
       </c>
     </row>
@@ -17146,32 +17179,64 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Head of state</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Salman</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Salman bin Abdulaziz Al Saud</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Full name for consistency</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Naming</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>Turkey</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Turkey</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Türkiye</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Use UN official short name</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F111"/>
+  <autoFilter ref="A1:F112"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Freedenian_Ideologies_Global_Dataset_2026-10-03.xlsx
+++ b/Freedenian_Ideologies_Global_Dataset_2026-10-03.xlsx
@@ -14,10 +14,10 @@
     <sheet name="Change log" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'195 States'!$A$1:$M$196</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Methodology'!$A$1:$B$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sources'!$A$1:$C$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Change log'!$A$1:$F$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'195 States'!$A$1:$O$196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Methodology'!$A$1:$B$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sources'!$A$1:$C$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Change log'!$A$1:$F$115</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,22 +450,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M196"/>
+  <dimension ref="A1:O196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="46" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="55" customWidth="1" min="12" max="12"/>
-    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="55" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -521,15 +523,25 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Adjacent concepts / regime context</t>
+          <t>Adjacent concepts</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Regime type (V-Dem RoW, 2025)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>V-Dem note</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Policy approach / key domains</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Previous code (conservatism-only scheme)</t>
         </is>
@@ -578,17 +590,19 @@
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>Tradition/religion; sharia; authority/order; restrictive social policy; state-controlled economy; restrictive migration; security-first foreign policy</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>T — traditionalist-authoritarian</t>
         </is>
@@ -644,10 +658,20 @@
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the next category up</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
           <t>EU integration; social-democratic governance; market economy; gradual institutional reform; pragmatic migration policy</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>L/C — centre-left</t>
         </is>
@@ -700,17 +724,19 @@
           <t>Nationalism</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>National sovereignty; state role in economy; social conservatism; controlled migration; hydrocarbons; security/state continuity</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>T — nationalist-authoritarian</t>
         </is>
@@ -766,10 +792,16 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>Not covered by V-Dem</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
           <t>Small-state market economy; institutional continuity; Catholic heritage; open European orientation</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>C/L — liberal-conservative hybrid</t>
         </is>
@@ -793,7 +825,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -803,7 +835,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -828,15 +860,21 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Authoritarian rule; Developmentalism</t>
+          <t>Developmentalism</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>State authority; national development; market reform with state role; social conservatism; energy/resources; security</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>C+/T — nationalist-developmental</t>
         </is>
@@ -892,10 +930,16 @@
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>Not covered by V-Dem</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>Social-democratic Caribbean governance; market economy; tourism; moderate social policy</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>L/C — centre-left</t>
         </is>
@@ -955,10 +999,16 @@
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>Radical market liberalisation; individual liberty; deregulation; reduced state; restrictive fiscal policy; socially mixed; strong Western alignment</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>R — libertarian right, not primarily conservative</t>
         </is>
@@ -1010,10 +1060,16 @@
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
           <t>Market economy; democratic/institutional reform; secular social policy; security-focused foreign policy</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>L/C — liberal-centrist</t>
         </is>
@@ -1073,10 +1129,16 @@
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
           <t>Mixed economy; welfare state; multicultural migration; climate transition; alliance with US</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>L — centre-left</t>
         </is>
@@ -1132,10 +1194,20 @@
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the category below</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>Market economy + social partnership; institutional continuity; controlled migration; pragmatic climate policy; EU/NATO-aligned security</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>C — Christian-democratic conservative</t>
         </is>
@@ -1159,7 +1231,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1169,7 +1241,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -1180,7 +1252,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Authoritarian state nationalism</t>
+          <t>State nationalism with dynastic continuity</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1188,17 +1260,19 @@
           <t>Nationalism</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
           <t>National sovereignty; executive authority; traditional social order; hydrocarbons; restrictive migration; security-first foreign policy</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>T — authoritarian-nationalist</t>
         </is>
@@ -1254,10 +1328,16 @@
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>Not covered by V-Dem</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
           <t>Social-democratic Caribbean model; tourism; moderate migration; climate/vulnerability policy</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>L/C — centre-left</t>
         </is>
@@ -1312,15 +1392,21 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Religion; Authoritarian rule</t>
+          <t>Religion</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>Dynastic authority; Sunni-Islamic tradition; state-led development; controlled migration; energy diversification; security alignment</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>T — monarchic traditionalist</t>
         </is>
@@ -1380,10 +1466,16 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
           <t>National identity; religious/social conservatism; market economy with state role; migration/labour policy; security and sovereignty</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>C+/N — conservative-nationalist hybrid</t>
         </is>
@@ -1439,10 +1531,20 @@
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the category below</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>Social-democratic welfare; tourism; progressive social policy; climate resilience; multilateral foreign policy</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>L — centre-left</t>
         </is>
@@ -1466,7 +1568,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1476,7 +1578,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1491,7 +1593,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Authoritarian state paternalism with Soviet-nostalgic nationalism</t>
+          <t>State paternalism with Soviet-nostalgic nationalism</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1499,17 +1601,19 @@
           <t>Nationalism</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>State authority; social conservatism; state economy; restrictive migration; energy/security dependence; continuity</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>T — authoritarian-traditionalist</t>
         </is>
@@ -1565,10 +1669,16 @@
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
           <t>Market economy; fiscal restraint; institutional order; stricter migration/integration; pragmatic climate/industry; NATO/EU</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>C — national/Christian-democratic conservative</t>
         </is>
@@ -1624,10 +1734,16 @@
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>Not covered by V-Dem</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
           <t>Mixed economy; social programmes; tourism; moderate migration; climate vulnerability</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>L/C — centre-left</t>
         </is>
@@ -1683,10 +1799,20 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the next category up</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
           <t>State capacity; economic development; market reform; order/security; infrastructure and regional security</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>C+/T — developmental-conservative hybrid</t>
         </is>
@@ -1746,10 +1872,20 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the category below</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
           <t>Monarchy and cultural continuity; regulated development; environmental stewardship; cautious social change</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>T/C — monarchic-traditionalist</t>
         </is>
@@ -1805,10 +1941,16 @@
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>Market reform; decentralisation; security/order; moderate social conservatism; pragmatic foreign policy</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>R — centre-right liberal</t>
         </is>
@@ -1872,10 +2014,20 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the next category up</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
           <t>Ethno-national and institutional interests; mixed economy; EU integration; migration/security; plural social positions</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>L/C — fragmented coalition</t>
         </is>
@@ -1931,10 +2083,16 @@
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
           <t>Social programmes; market economy; institutional democracy; mining; regional diplomacy</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>L/C — centre-left</t>
         </is>
@@ -1994,10 +2152,20 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the next category up</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
           <t>Social welfare; developmental state; progressive social policy; environmental protection; multilateral diplomacy</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>L — left</t>
         </is>
@@ -2054,17 +2222,19 @@
           <t>Nationalism</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
+          <t>Not covered by V-Dem</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
           <t>Absolute monarchy; Malay-Islamic tradition; state/energy economy; restrictive social policy; controlled migration</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>T — dynastic-religious traditionalist</t>
         </is>
@@ -2120,10 +2290,16 @@
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
           <t>National sovereignty; security; mixed economy; EU orientation; more restrictive migration; pragmatic energy policy</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>C+/L — mixed centre-right/national</t>
         </is>
@@ -2176,17 +2352,19 @@
           <t>Nationalism; Populism</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
           <t>National sovereignty; military authority; state-led development; traditional social order; restrictive external migration; anti-colonial foreign policy</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>T — military-nationalist</t>
         </is>
@@ -2210,7 +2388,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2220,7 +2398,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -2231,7 +2409,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Dominant-party authoritarianism (CNDD-FDD)</t>
+          <t>Dominant-party nationalism (CNDD-FDD)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2241,15 +2419,21 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Religion; Authoritarian rule</t>
+          <t>Religion</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
           <t>Executive authority; national unity; state-led development; socially conservative; security-first</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>T/C — nationalist-authoritarian hybrid</t>
         </is>
@@ -2305,10 +2489,16 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
           <t>Democratic institutions; tourism/services; social policy; climate resilience; EU/Atlantic orientation</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>L/C — centre-left/centrist</t>
         </is>
@@ -2332,7 +2522,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2342,7 +2532,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2357,7 +2547,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Dominant-party developmental authoritarianism (CPP)</t>
+          <t>Dominant-party developmentalism (CPP)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2367,15 +2557,21 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Authoritarian rule; Developmentalism</t>
+          <t>Developmentalism</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
           <t>Monarchy/continuity; authority; state-led development; socially conservative; controlled migration; China/ASEAN balancing</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>T/C — conservative-developmental</t>
         </is>
@@ -2399,7 +2595,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2409,7 +2605,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
@@ -2424,17 +2620,19 @@
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
           <t>Executive continuity; state authority; traditional social order; resource economy; security</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>T — authoritarian-traditionalist</t>
         </is>
@@ -2490,10 +2688,20 @@
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the next category up</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
           <t>Market economy + welfare; multicultural migration; climate/industrial policy; Atlantic/NATO orientation</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>L/C — liberal-centrist</t>
         </is>
@@ -2517,7 +2725,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2527,7 +2735,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -2538,21 +2746,23 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Personalist developmental authoritarianism</t>
+          <t>Personalist developmentalism</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
           <t>Executive authority; state-led development; security; resource extraction; sovereignty</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>T — authoritarian-developmental</t>
         </is>
@@ -2576,7 +2786,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2586,7 +2796,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
@@ -2605,17 +2815,19 @@
           <t>Nationalism</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
           <t>Authority/order; security; state-led development; traditional social order; regional security</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>T — military-nationalist</t>
         </is>
@@ -2675,10 +2887,20 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the category below</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
           <t>Traditional family/social order; law and order; private property/market economy; restrictive migration; energy pragmatism; security-oriented foreign policy</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>C — national-conservative</t>
         </is>
@@ -2733,15 +2955,21 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Authoritarian rule; Developmentalism</t>
+          <t>Developmentalism</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
           <t>Party authority; national continuity; state capitalism; social discipline; controlled migration; strategic autonomy</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>T/R — communist-nationalist, not conservative in Freedenian sense</t>
         </is>
@@ -2797,10 +3025,16 @@
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
           <t>Security/order; market economy; traditional social values; restrictive migration; resource/energy development; strong US/security ties</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>C+ — national-conservative</t>
         </is>
@@ -2824,7 +3058,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2834,7 +3068,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -2849,7 +3083,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Presidential authoritarianism with Islamic social order</t>
+          <t>Presidentialism with Islamic social order</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2859,15 +3093,21 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Religion; Authoritarian rule</t>
+          <t>Religion</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
           <t>Executive authority; Islamic social order; state-led development; security; regional diplomacy</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>T/C — presidential traditionalist</t>
         </is>
@@ -2927,10 +3167,16 @@
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
           <t>Security/order; market economy; fiscal reform; socially mixed; migration control; climate policy retained</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr">
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>C+ — populist/centre-right hybrid</t>
         </is>
@@ -2986,10 +3232,16 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
           <t>Market investment; infrastructure; state capacity; security; regional diplomacy</t>
         </is>
       </c>
-      <c r="M41" s="2" t="inlineStr">
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>R — developmental centre-right</t>
         </is>
@@ -3045,10 +3297,16 @@
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
           <t>EU/NATO; market + social state; national identity; controlled migration; energy pragmatism; security</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr">
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>C — Christian-democratic/national conservative</t>
         </is>
@@ -3101,17 +3359,19 @@
           <t>Nationalism</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
           <t>One-party authority; state economy; socialist social policy; controlled migration; security/sovereignty</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr">
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>L/T — communist authoritarian</t>
         </is>
@@ -3167,10 +3427,20 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the category below</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
           <t>Market economy; moderate social policy; EU orientation; controlled migration; energy/security in Eastern Mediterranean</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr">
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>C/L — centrist conservative-liberal</t>
         </is>
@@ -3226,10 +3496,16 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
           <t>Market economy with domestic spending; national sovereignty; migration restriction; climate-policy scepticism; NATO but less Ukraine activism</t>
         </is>
       </c>
-      <c r="M45" s="2" t="inlineStr">
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>C+ — populist-conservative hybrid</t>
         </is>
@@ -3289,10 +3565,16 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
           <t>State capacity; resource development; social programmes; security; regional diplomacy</t>
         </is>
       </c>
-      <c r="M46" s="2" t="inlineStr">
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>L/C — centrist-developmental</t>
         </is>
@@ -3352,10 +3634,16 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
           <t>Welfare state; restrictive migration; strong institutions; climate transition; NATO/security</t>
         </is>
       </c>
-      <c r="M47" s="2" t="inlineStr">
+      <c r="O47" s="2" t="inlineStr">
         <is>
           <t>L/C — social-democratic with restrictive migration</t>
         </is>
@@ -3379,7 +3667,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -3389,7 +3677,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
@@ -3404,17 +3692,19 @@
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
           <t>Executive authority; strategic infrastructure; state security; traditional social order; military/diplomatic balancing</t>
         </is>
       </c>
-      <c r="M48" s="2" t="inlineStr">
+      <c r="O48" s="2" t="inlineStr">
         <is>
           <t>T — authoritarian-developmental</t>
         </is>
@@ -3470,10 +3760,16 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
+          <t>Not covered by V-Dem</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
           <t>Public investment; social programmes; climate resilience; tourism; regional diplomacy</t>
         </is>
       </c>
-      <c r="M49" s="2" t="inlineStr">
+      <c r="O49" s="2" t="inlineStr">
         <is>
           <t>L/C — centre-left</t>
         </is>
@@ -3533,10 +3829,16 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
           <t>Market economy; private investment; migration control; moderate social conservatism; tourism/energy</t>
         </is>
       </c>
-      <c r="M50" s="2" t="inlineStr">
+      <c r="O50" s="2" t="inlineStr">
         <is>
           <t>R — moderate centre-right</t>
         </is>
@@ -3592,10 +3894,16 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
           <t>Security/order; market economy; fiscal reform; restrictive migration; energy/resource development</t>
         </is>
       </c>
-      <c r="M51" s="2" t="inlineStr">
+      <c r="O51" s="2" t="inlineStr">
         <is>
           <t>R/C — security-oriented centre-right</t>
         </is>
@@ -3619,7 +3927,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3629,7 +3937,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
@@ -3640,7 +3948,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Military-backed state authoritarianism</t>
+          <t>Military-backed state developmentalism</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3650,15 +3958,21 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>Authoritarian rule; Developmentalism</t>
+          <t>Developmentalism</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
           <t>Executive authority; traditional social order; state/development projects; controlled migration; energy; regional security</t>
         </is>
       </c>
-      <c r="M52" s="2" t="inlineStr">
+      <c r="O52" s="2" t="inlineStr">
         <is>
           <t>T — authoritarian-nationalist</t>
         </is>
@@ -3703,7 +4017,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Authoritarian populism (Bukele)</t>
+          <t>Security-first populism (Bukele)</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3711,17 +4025,19 @@
           <t>Nationalism; Populism</t>
         </is>
       </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
           <t>Public order/security; strong executive; pro-business with state intervention; socially conservative rhetoric; migration/security</t>
         </is>
       </c>
-      <c r="M53" s="2" t="inlineStr">
+      <c r="O53" s="2" t="inlineStr">
         <is>
           <t>C+ — authoritarian-populist hybrid</t>
         </is>
@@ -3745,7 +4061,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3755,7 +4071,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
@@ -3770,17 +4086,19 @@
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
           <t>Executive continuity; oil/state economy; social traditionalism; controlled migration; security</t>
         </is>
       </c>
-      <c r="M54" s="2" t="inlineStr">
+      <c r="O54" s="2" t="inlineStr">
         <is>
           <t>T — authoritarian-traditionalist</t>
         </is>
@@ -3804,7 +4122,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3814,7 +4132,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -3837,17 +4155,19 @@
           <t>Nationalism</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
           <t>National sovereignty; state control; social discipline; restricted migration; militarised security</t>
         </is>
       </c>
-      <c r="M55" s="2" t="inlineStr">
+      <c r="O55" s="2" t="inlineStr">
         <is>
           <t>T — authoritarian-nationalist</t>
         </is>
@@ -3903,10 +4223,16 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
           <t>Market economy; national security; restrictive migration/integration; digital state; strong NATO/EU orientation</t>
         </is>
       </c>
-      <c r="M56" s="2" t="inlineStr">
+      <c r="O56" s="2" t="inlineStr">
         <is>
           <t>C/L — liberal-conservative</t>
         </is>
@@ -3955,17 +4281,19 @@
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
           <t>Monarchical authority; customary tradition; state-led development; socially conservative; controlled migration</t>
         </is>
       </c>
-      <c r="M57" s="2" t="inlineStr">
+      <c r="O57" s="2" t="inlineStr">
         <is>
           <t>T — monarchic traditionalist</t>
         </is>
@@ -3989,7 +4317,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3999,7 +4327,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -4014,7 +4342,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Developmental-state authoritarianism (Prosperity Party)</t>
+          <t>Developmental-state ideology (Prosperity Party, 'medemer')</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -4024,15 +4352,21 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>Authoritarian rule; Developmentalism</t>
+          <t>Developmentalism</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
           <t>State capacity; developmentalism; mixed economy; traditional social order; security; regional diplomacy</t>
         </is>
       </c>
-      <c r="M58" s="2" t="inlineStr">
+      <c r="O58" s="2" t="inlineStr">
         <is>
           <t>C+/T — developmental-authoritarian hybrid</t>
         </is>
@@ -4088,10 +4422,16 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
+          <t>Not covered by V-Dem</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
           <t>Climate adaptation; public services; US security compact; migration/mobility</t>
         </is>
       </c>
-      <c r="M59" s="2" t="inlineStr">
+      <c r="O59" s="2" t="inlineStr">
         <is>
           <t>L/C — centrist</t>
         </is>
@@ -4147,10 +4487,20 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the category below</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
           <t>Market/tourism economy; customary institutions; moderate social conservatism; climate vulnerability; regional security</t>
         </is>
       </c>
-      <c r="M60" s="2" t="inlineStr">
+      <c r="O60" s="2" t="inlineStr">
         <is>
           <t>C/L — conservative-liberal hybrid</t>
         </is>
@@ -4206,10 +4556,16 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
           <t>Market economy; fiscal discipline; institutional continuity; restrictive migration; nuclear/climate pragmatism; strong NATO</t>
         </is>
       </c>
-      <c r="M61" s="2" t="inlineStr">
+      <c r="O61" s="2" t="inlineStr">
         <is>
           <t>C — liberal/Christian-democratic conservative</t>
         </is>
@@ -4261,10 +4617,20 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the category below</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
           <t>State capacity; market reform; secular republicanism; controlled migration; nuclear/energy transition; European strategic autonomy</t>
         </is>
       </c>
-      <c r="M62" s="2" t="inlineStr">
+      <c r="O62" s="2" t="inlineStr">
         <is>
           <t>L/C — liberal-centrist, not primarily conservative</t>
         </is>
@@ -4288,7 +4654,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -4298,7 +4664,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
@@ -4319,15 +4685,21 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>Authoritarian rule; Developmentalism</t>
+          <t>Developmentalism</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
           <t>Military authority; national resources; state-led development; social traditionalism; security</t>
         </is>
       </c>
-      <c r="M63" s="2" t="inlineStr">
+      <c r="O63" s="2" t="inlineStr">
         <is>
           <t>T — military-developmental</t>
         </is>
@@ -4379,10 +4751,20 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the next category up</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
           <t>Market/tourism; democratic institutions; moderate social policy; migration and regional diplomacy</t>
         </is>
       </c>
-      <c r="M64" s="2" t="inlineStr">
+      <c r="O64" s="2" t="inlineStr">
         <is>
           <t>L/C — centrist</t>
         </is>
@@ -4437,15 +4819,21 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>Religion; Authoritarian rule</t>
+          <t>Religion</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
           <t>National sovereignty; Orthodox cultural tradition; authority/order; restrictive NGO/foreign influence policy; migration/security; cautious EU orientation</t>
         </is>
       </c>
-      <c r="M65" s="2" t="inlineStr">
+      <c r="O65" s="2" t="inlineStr">
         <is>
           <t>C+ — national/traditionalist</t>
         </is>
@@ -4501,10 +4889,16 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
           <t>Social market; fiscal discipline; property/private enterprise; controlled migration; industrial climate transition; strong EU/NATO</t>
         </is>
       </c>
-      <c r="M66" s="2" t="inlineStr">
+      <c r="O66" s="2" t="inlineStr">
         <is>
           <t>C — Christian-democratic conservative</t>
         </is>
@@ -4564,10 +4958,16 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
           <t>Social/developmental state; market economy; democratic institutions; regional diplomacy</t>
         </is>
       </c>
-      <c r="M67" s="2" t="inlineStr">
+      <c r="O67" s="2" t="inlineStr">
         <is>
           <t>L/C — centre-left</t>
         </is>
@@ -4623,10 +5023,16 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
           <t>Market reform; institutional continuity; controlled migration; family/social conservatism; renewables + energy security; NATO/EU</t>
         </is>
       </c>
-      <c r="M68" s="2" t="inlineStr">
+      <c r="O68" s="2" t="inlineStr">
         <is>
           <t>C — liberal-conservative</t>
         </is>
@@ -4682,10 +5088,16 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
+          <t>Not covered by V-Dem</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
           <t>Social programmes; tourism; climate resilience; regional diplomacy</t>
         </is>
       </c>
-      <c r="M69" s="2" t="inlineStr">
+      <c r="O69" s="2" t="inlineStr">
         <is>
           <t>L/C — centre-left</t>
         </is>
@@ -4741,10 +5153,16 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
           <t>Anti-corruption/institutional reform; market economy; moderate social policy; migration/development</t>
         </is>
       </c>
-      <c r="M70" s="2" t="inlineStr">
+      <c r="O70" s="2" t="inlineStr">
         <is>
           <t>L/C — liberal-centrist</t>
         </is>
@@ -4768,7 +5186,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -4778,7 +5196,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr"/>
@@ -4797,17 +5215,19 @@
           <t>Nationalism</t>
         </is>
       </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
           <t>Military authority; national resources; state capacity; traditional social order; security</t>
         </is>
       </c>
-      <c r="M71" s="2" t="inlineStr">
+      <c r="O71" s="2" t="inlineStr">
         <is>
           <t>T — military-nationalist</t>
         </is>
@@ -4831,7 +5251,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -4841,7 +5261,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr"/>
@@ -4856,17 +5276,23 @@
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the next category up</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
           <t>Order/security; state continuity; resource/tactical governance</t>
         </is>
       </c>
-      <c r="M72" s="2" t="inlineStr">
+      <c r="O72" s="2" t="inlineStr">
         <is>
           <t>T — military/transitional</t>
         </is>
@@ -4926,10 +5352,20 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the category below</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
           <t>Resource-led development; infrastructure; market economy; social programmes; security/foreign investment</t>
         </is>
       </c>
-      <c r="M73" s="2" t="inlineStr">
+      <c r="O73" s="2" t="inlineStr">
         <is>
           <t>L/C — developmental-centrist</t>
         </is>
@@ -4981,10 +5417,16 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
           <t>Security/order; institutional rebuilding; humanitarian governance; migration/displacement</t>
         </is>
       </c>
-      <c r="M74" s="2" t="inlineStr">
+      <c r="O74" s="2" t="inlineStr">
         <is>
           <t>T/L — transitional security government</t>
         </is>
@@ -5044,10 +5486,20 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the category below</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
           <t>Security/order; private investment; traditional social values; restrictive migration; market economy</t>
         </is>
       </c>
-      <c r="M75" s="2" t="inlineStr">
+      <c r="O75" s="2" t="inlineStr">
         <is>
           <t>C — national-conservative</t>
         </is>
@@ -5103,10 +5555,16 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
           <t>EU-oriented centre-right; market economy; institutional repair; controlled migration; moderate social conservatism; security</t>
         </is>
       </c>
-      <c r="M76" s="2" t="inlineStr">
+      <c r="O76" s="2" t="inlineStr">
         <is>
           <t>C — centre-right conservative, post-Orbán</t>
         </is>
@@ -5166,10 +5624,16 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
           <t>Welfare state; market economy; climate/energy; moderate migration; Nordic institutions</t>
         </is>
       </c>
-      <c r="M77" s="2" t="inlineStr">
+      <c r="O77" s="2" t="inlineStr">
         <is>
           <t>L/C — social-democratic</t>
         </is>
@@ -5229,10 +5693,16 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
           <t>Hindu cultural/national identity; strong executive; mixed market/state development; restrictive citizenship/migration; energy pragmatism; strategic autonomy</t>
         </is>
       </c>
-      <c r="M78" s="2" t="inlineStr">
+      <c r="O78" s="2" t="inlineStr">
         <is>
           <t>C+ — national-cultural conservative</t>
         </is>
@@ -5292,10 +5762,20 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the next category up</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
           <t>National unity; authority; state-led industrial policy; social/family conservatism; migration controlled; resource/energy development; strategic autonomy</t>
         </is>
       </c>
-      <c r="M79" s="2" t="inlineStr">
+      <c r="O79" s="2" t="inlineStr">
         <is>
           <t>C+ — nationalist-developmental</t>
         </is>
@@ -5348,17 +5828,23 @@
           <t>Nationalism</t>
         </is>
       </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the category below</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
           <t>Islamic order; clerical authority; state-led economy; restrictive social policy; controlled migration; security/sovereignty</t>
         </is>
       </c>
-      <c r="M80" s="2" t="inlineStr">
+      <c r="O80" s="2" t="inlineStr">
         <is>
           <t>T — religious-authoritarian</t>
         </is>
@@ -5414,10 +5900,16 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
           <t>Religious/social tradition; authority; state/resources; security; migration/displacement; regional balancing</t>
         </is>
       </c>
-      <c r="M81" s="2" t="inlineStr">
+      <c r="O81" s="2" t="inlineStr">
         <is>
           <t>C+/T — religious-national coalition</t>
         </is>
@@ -5473,10 +5965,16 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
           <t>Market economy + welfare; relatively liberal social policy; migration/integration; climate transition; EU/Atlantic orientation</t>
         </is>
       </c>
-      <c r="M82" s="2" t="inlineStr">
+      <c r="O82" s="2" t="inlineStr">
         <is>
           <t>L/C — centrist</t>
         </is>
@@ -5536,10 +6034,20 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the next category up</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
           <t>Jewish national identity; security/order; market economy; socially conservative coalition; restrictive migration; defence-first foreign policy</t>
         </is>
       </c>
-      <c r="M83" s="2" t="inlineStr">
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>C+ — national-conservative</t>
         </is>
@@ -5595,10 +6103,20 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the category below</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
           <t>Traditional family/cultural identity; market + strategic state; restrictive migration; energy pragmatism; strong NATO/EU with sovereignty emphasis</t>
         </is>
       </c>
-      <c r="M84" s="2" t="inlineStr">
+      <c r="O84" s="2" t="inlineStr">
         <is>
           <t>C+ — national-conservative</t>
         </is>
@@ -5654,10 +6172,16 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
           <t>Private enterprise; law/order; moderate social conservatism; controlled migration; tourism/energy</t>
         </is>
       </c>
-      <c r="M85" s="2" t="inlineStr">
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>C/L — centre-right conservative</t>
         </is>
@@ -5713,10 +6237,16 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
           <t>Traditional institutions/family; national identity; market economy + fiscal stimulus; stronger defence; energy/nuclear pragmatism</t>
         </is>
       </c>
-      <c r="M86" s="2" t="inlineStr">
+      <c r="O86" s="2" t="inlineStr">
         <is>
           <t>C+ — national-conservative</t>
         </is>
@@ -5776,10 +6306,16 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
           <t>Monarchical authority; Islamic/tribal tradition; state-led economy; controlled migration/refugees; security diplomacy</t>
         </is>
       </c>
-      <c r="M87" s="2" t="inlineStr">
+      <c r="O87" s="2" t="inlineStr">
         <is>
           <t>T — monarchic traditionalist</t>
         </is>
@@ -5803,7 +6339,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -5813,7 +6349,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr"/>
@@ -5824,7 +6360,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Developmental authoritarianism</t>
+          <t>State-led developmentalism</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -5834,15 +6370,21 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>Authoritarian rule; Developmentalism</t>
+          <t>Developmentalism</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
           <t>Executive order; national identity; state/resource economy; controlled migration; energy development; multi-vector diplomacy</t>
         </is>
       </c>
-      <c r="M88" s="2" t="inlineStr">
+      <c r="O88" s="2" t="inlineStr">
         <is>
           <t>T — authoritarian-developmental</t>
         </is>
@@ -5906,10 +6448,20 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the category below</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
           <t>Religious/family values; market reform; security/order; migration management; development/energy; regional diplomacy</t>
         </is>
       </c>
-      <c r="M89" s="2" t="inlineStr">
+      <c r="O89" s="2" t="inlineStr">
         <is>
           <t>C+ — social/religious conservative + market-oriented</t>
         </is>
@@ -5965,10 +6517,16 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
+          <t>Not covered by V-Dem</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
           <t>Community/tradition; public development; climate adaptation; migration/mobility; regional diplomacy</t>
         </is>
       </c>
-      <c r="M90" s="2" t="inlineStr">
+      <c r="O90" s="2" t="inlineStr">
         <is>
           <t>L/C — developmental-centrist</t>
         </is>
@@ -6023,15 +6581,21 @@
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>Religion; Authoritarian rule</t>
+          <t>Religion</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
           <t>Dynastic authority; Islamic tradition; oil/state economy; controlled migration; energy; Gulf security</t>
         </is>
       </c>
-      <c r="M91" s="2" t="inlineStr">
+      <c r="O91" s="2" t="inlineStr">
         <is>
           <t>T — monarchic traditionalist</t>
         </is>
@@ -6055,7 +6619,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -6065,7 +6629,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -6080,7 +6644,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Authoritarian populism (Japarov)</t>
+          <t>Nationalist populism (Japarov)</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -6088,17 +6652,19 @@
           <t>Nationalism; Populism</t>
         </is>
       </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
           <t>Executive authority; national identity; state intervention; social conservatism; migration/security; regional balancing</t>
         </is>
       </c>
-      <c r="M92" s="2" t="inlineStr">
+      <c r="O92" s="2" t="inlineStr">
         <is>
           <t>C+/T — nationalist-authoritarian hybrid</t>
         </is>
@@ -6147,17 +6713,19 @@
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
           <t>Party authority; state economy; social discipline; controlled migration; hydropower/resources; regional balancing</t>
         </is>
       </c>
-      <c r="M93" s="2" t="inlineStr">
+      <c r="O93" s="2" t="inlineStr">
         <is>
           <t>T/L — communist-authoritarian</t>
         </is>
@@ -6213,10 +6781,16 @@
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
           <t>Market economy; national security; controlled migration; energy diversification; NATO/EU</t>
         </is>
       </c>
-      <c r="M94" s="2" t="inlineStr">
+      <c r="O94" s="2" t="inlineStr">
         <is>
           <t>R — centre-right liberal</t>
         </is>
@@ -6272,10 +6846,16 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
           <t>Sectarian balance; market/private economy; institutional reconstruction; refugee/migration pressures; regional security</t>
         </is>
       </c>
-      <c r="M95" s="2" t="inlineStr">
+      <c r="O95" s="2" t="inlineStr">
         <is>
           <t>L/C — institutional/coalitional</t>
         </is>
@@ -6331,10 +6911,16 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
           <t>Market investment; customary institutions; social programmes; migration/labour; regional diplomacy</t>
         </is>
       </c>
-      <c r="M96" s="2" t="inlineStr">
+      <c r="O96" s="2" t="inlineStr">
         <is>
           <t>R — centre-right developmental</t>
         </is>
@@ -6386,10 +6972,16 @@
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
           <t>Institutional reform; market economy; development; moderate social policy; regional diplomacy</t>
         </is>
       </c>
-      <c r="M97" s="2" t="inlineStr">
+      <c r="O97" s="2" t="inlineStr">
         <is>
           <t>L/C — centrist</t>
         </is>
@@ -6413,7 +7005,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -6423,7 +7015,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -6445,10 +7037,16 @@
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
           <t>State reconstruction; competing authorities; market/resource economy; migration/security; regional balancing</t>
         </is>
       </c>
-      <c r="M98" s="2" t="inlineStr">
+      <c r="O98" s="2" t="inlineStr">
         <is>
           <t>L/C — fragmented transitional</t>
         </is>
@@ -6504,10 +7102,16 @@
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
+          <t>Not covered by V-Dem</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
           <t>Property/private enterprise; constitutional monarchy; low-tax economy; institutional continuity; European cooperation</t>
         </is>
       </c>
-      <c r="M99" s="2" t="inlineStr">
+      <c r="O99" s="2" t="inlineStr">
         <is>
           <t>C — liberal-conservative</t>
         </is>
@@ -6563,10 +7167,20 @@
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the category below</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
           <t>Market economy; national security; migration control/integration; energy independence; NATO/EU</t>
         </is>
       </c>
-      <c r="M100" s="2" t="inlineStr">
+      <c r="O100" s="2" t="inlineStr">
         <is>
           <t>R — centre-right security-oriented</t>
         </is>
@@ -6622,10 +7236,16 @@
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
           <t>Market/finance; fiscal prudence; institutional continuity; moderate social policy; EU integration</t>
         </is>
       </c>
-      <c r="M101" s="2" t="inlineStr">
+      <c r="O101" s="2" t="inlineStr">
         <is>
           <t>C — Christian-democratic conservative</t>
         </is>
@@ -6649,7 +7269,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -6659,7 +7279,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr"/>
@@ -6674,17 +7294,19 @@
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
           <t>Order; state capacity; development; resource economy; security</t>
         </is>
       </c>
-      <c r="M102" s="2" t="inlineStr">
+      <c r="O102" s="2" t="inlineStr">
         <is>
           <t>T — military-transitional</t>
         </is>
@@ -6740,10 +7362,20 @@
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the category below</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
           <t>Market economy; institutional continuity; moderate social conservatism; development/agriculture</t>
         </is>
       </c>
-      <c r="M103" s="2" t="inlineStr">
+      <c r="O103" s="2" t="inlineStr">
         <is>
           <t>R — centre-right</t>
         </is>
@@ -6803,10 +7435,20 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the category below</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
           <t>Market economy + state development; Islamic institutional context; moderate social policy; controlled migration; ASEAN balancing</t>
         </is>
       </c>
-      <c r="M104" s="2" t="inlineStr">
+      <c r="O104" s="2" t="inlineStr">
         <is>
           <t>L/C — coalition/centrist</t>
         </is>
@@ -6866,10 +7508,20 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the category below</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
           <t>Islamic social order; national sovereignty; infrastructure/state role; controlled migration; maritime security; India-China balancing</t>
         </is>
       </c>
-      <c r="M105" s="2" t="inlineStr">
+      <c r="O105" s="2" t="inlineStr">
         <is>
           <t>C+ — national/religious conservative</t>
         </is>
@@ -6893,7 +7545,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -6903,7 +7555,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr"/>
@@ -6922,17 +7574,19 @@
           <t>Nationalism; Populism</t>
         </is>
       </c>
-      <c r="K106" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
           <t>Military authority; sovereignty; state-led development; traditional social order; security; anti-Western foreign policy</t>
         </is>
       </c>
-      <c r="M106" s="2" t="inlineStr">
+      <c r="O106" s="2" t="inlineStr">
         <is>
           <t>T — military-nationalist</t>
         </is>
@@ -6988,10 +7642,20 @@
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the next category up</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
           <t>Welfare/social policy; market/tourism; relatively liberal social policy; migration management; EU orientation</t>
         </is>
       </c>
-      <c r="M107" s="2" t="inlineStr">
+      <c r="O107" s="2" t="inlineStr">
         <is>
           <t>L/C — centre-left</t>
         </is>
@@ -7047,10 +7711,16 @@
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
+          <t>Not covered by V-Dem</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
           <t>Climate survival/adaptation; aid; US security ties; small-state governance</t>
         </is>
       </c>
-      <c r="M108" s="2" t="inlineStr">
+      <c r="O108" s="2" t="inlineStr">
         <is>
           <t>L/C — centrist</t>
         </is>
@@ -7074,7 +7744,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -7084,7 +7754,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -7110,10 +7780,16 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
           <t>Islamic tradition; executive authority; market/resource development; controlled migration; regional security</t>
         </is>
       </c>
-      <c r="M109" s="2" t="inlineStr">
+      <c r="O109" s="2" t="inlineStr">
         <is>
           <t>T/C — Islamic-national developmental</t>
         </is>
@@ -7169,10 +7845,20 @@
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the next category up</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
           <t>Welfare; diversified market economy; social pluralism; climate/vulnerability; regional diplomacy</t>
         </is>
       </c>
-      <c r="M110" s="2" t="inlineStr">
+      <c r="O110" s="2" t="inlineStr">
         <is>
           <t>L/C — centre-left</t>
         </is>
@@ -7232,10 +7918,20 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the next category up</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
           <t>State-led development; welfare; progressive social policy; migration diplomacy; energy sovereignty; regional/US balancing</t>
         </is>
       </c>
-      <c r="M111" s="2" t="inlineStr">
+      <c r="O111" s="2" t="inlineStr">
         <is>
           <t>L — left/national-developmental</t>
         </is>
@@ -7287,10 +7983,20 @@
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the category below</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
           <t>European integration; market reform; institutional strengthening; controlled migration; energy independence; security</t>
         </is>
       </c>
-      <c r="M112" s="2" t="inlineStr">
+      <c r="O112" s="2" t="inlineStr">
         <is>
           <t>L/C — liberal-centrist</t>
         </is>
@@ -7342,10 +8048,16 @@
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr">
         <is>
+          <t>Not covered by V-Dem</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr"/>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
           <t>Monarchical continuity; property/private wealth; regulated social order; low-tax/service economy; cautious reform</t>
         </is>
       </c>
-      <c r="M113" s="2" t="inlineStr">
+      <c r="O113" s="2" t="inlineStr">
         <is>
           <t>C — monarchical conservative</t>
         </is>
@@ -7401,10 +8113,20 @@
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the category below</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
           <t>National resources; state development; traditional culture; market economy; strategic balancing</t>
         </is>
       </c>
-      <c r="M114" s="2" t="inlineStr">
+      <c r="O114" s="2" t="inlineStr">
         <is>
           <t>C+/L — nationalist-developmental</t>
         </is>
@@ -7460,10 +8182,20 @@
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the next category up</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
           <t>Market reform; EU accession; moderate social conservatism; controlled migration; NATO/security</t>
         </is>
       </c>
-      <c r="M115" s="2" t="inlineStr">
+      <c r="O115" s="2" t="inlineStr">
         <is>
           <t>C/L — liberal-conservative</t>
         </is>
@@ -7523,10 +8255,16 @@
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr"/>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
           <t>Monarchical/religious authority; market development; controlled migration; traditional social order with modernisation; energy/infrastructure</t>
         </is>
       </c>
-      <c r="M116" s="2" t="inlineStr">
+      <c r="O116" s="2" t="inlineStr">
         <is>
           <t>T/C — monarchic-developmental</t>
         </is>
@@ -7550,7 +8288,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -7560,7 +8298,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -7585,15 +8323,21 @@
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>Authoritarian rule; Developmentalism</t>
+          <t>Developmentalism</t>
         </is>
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr"/>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
           <t>State authority; resource development; traditional social order; security; foreign investment</t>
         </is>
       </c>
-      <c r="M117" s="2" t="inlineStr">
+      <c r="O117" s="2" t="inlineStr">
         <is>
           <t>C/T — nationalist-developmental</t>
         </is>
@@ -7617,7 +8361,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -7627,7 +8371,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -7652,15 +8396,21 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>Religion; Authoritarian rule</t>
+          <t>Religion</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr"/>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
           <t>Military authority; Buddhist-national identity; state control; restrictive migration; security</t>
         </is>
       </c>
-      <c r="M118" s="2" t="inlineStr">
+      <c r="O118" s="2" t="inlineStr">
         <is>
           <t>T — military-authoritarian</t>
         </is>
@@ -7716,10 +8466,20 @@
       <c r="K119" s="2" t="inlineStr"/>
       <c r="L119" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the category below</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
           <t>Social/developmental state; resource management; moderate social policy; regional diplomacy</t>
         </is>
       </c>
-      <c r="M119" s="2" t="inlineStr">
+      <c r="O119" s="2" t="inlineStr">
         <is>
           <t>L/C — centre-left nationalist</t>
         </is>
@@ -7775,10 +8535,16 @@
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr">
         <is>
+          <t>Not covered by V-Dem</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr"/>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
           <t>Small-state governance; resource/aid economy; traditional social order; migration/climate vulnerability</t>
         </is>
       </c>
-      <c r="M120" s="2" t="inlineStr">
+      <c r="O120" s="2" t="inlineStr">
         <is>
           <t>C/L — conservative-centrist</t>
         </is>
@@ -7834,10 +8600,16 @@
       <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr"/>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
           <t>Anti-corruption/state reform; mixed economy; traditional social context; migration/labour; regional balancing</t>
         </is>
       </c>
-      <c r="M121" s="2" t="inlineStr">
+      <c r="O121" s="2" t="inlineStr">
         <is>
           <t>L/C — populist-centrist</t>
         </is>
@@ -7893,10 +8665,16 @@
       <c r="K122" s="2" t="inlineStr"/>
       <c r="L122" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr"/>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
           <t>Market/welfare mix; relatively liberal social policy; migration/integration; climate transition; EU/NATO</t>
         </is>
       </c>
-      <c r="M122" s="2" t="inlineStr">
+      <c r="O122" s="2" t="inlineStr">
         <is>
           <t>L/C — liberal-centrist</t>
         </is>
@@ -7952,10 +8730,16 @@
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr"/>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
           <t>Market reform; deregulation; property/private enterprise; moderate social conservatism; migration controls; energy/resource pragmatism</t>
         </is>
       </c>
-      <c r="M123" s="2" t="inlineStr">
+      <c r="O123" s="2" t="inlineStr">
         <is>
           <t>C — liberal-conservative</t>
         </is>
@@ -8000,7 +8784,7 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>Authoritarian Sandinismo (co-presidency)</t>
+          <t>Late Sandinismo (co-presidency)</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -8008,17 +8792,19 @@
           <t>Nationalism; Populism</t>
         </is>
       </c>
-      <c r="K124" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr"/>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
           <t>Executive/family authority; state intervention; social conservatism; restrictive migration; security/sovereignty</t>
         </is>
       </c>
-      <c r="M124" s="2" t="inlineStr">
+      <c r="O124" s="2" t="inlineStr">
         <is>
           <t>T — authoritarian-nationalist</t>
         </is>
@@ -8042,7 +8828,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -8052,7 +8838,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr"/>
@@ -8071,17 +8857,19 @@
           <t>Nationalism</t>
         </is>
       </c>
-      <c r="K125" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K125" s="2" t="inlineStr"/>
       <c r="L125" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr"/>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
           <t>Military authority; sovereignty; state/resources; traditional social order; security</t>
         </is>
       </c>
-      <c r="M125" s="2" t="inlineStr">
+      <c r="O125" s="2" t="inlineStr">
         <is>
           <t>T — military-nationalist</t>
         </is>
@@ -8141,10 +8929,20 @@
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the category below</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
           <t>Religious/family values; market reform; security/order; migration management; oil/energy; regional leadership</t>
         </is>
       </c>
-      <c r="M126" s="2" t="inlineStr">
+      <c r="O126" s="2" t="inlineStr">
         <is>
           <t>C+ — socially conservative, market-oriented</t>
         </is>
@@ -8197,17 +8995,19 @@
           <t>Nationalism</t>
         </is>
       </c>
-      <c r="K127" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K127" s="2" t="inlineStr"/>
       <c r="L127" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr"/>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
           <t>State/party authority; hereditary leadership; controlled economy; social discipline; restricted migration; military security</t>
         </is>
       </c>
-      <c r="M127" s="2" t="inlineStr">
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>T/L — totalitarian-nationalist</t>
         </is>
@@ -8263,10 +9063,20 @@
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the category below</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
           <t>National identity; traditional social values; market economy; migration control; energy pragmatism; NATO/EU</t>
         </is>
       </c>
-      <c r="M128" s="2" t="inlineStr">
+      <c r="O128" s="2" t="inlineStr">
         <is>
           <t>C+ — national-conservative</t>
         </is>
@@ -8322,10 +9132,16 @@
       <c r="K129" s="2" t="inlineStr"/>
       <c r="L129" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr"/>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
           <t>Welfare state; regulated market; climate/energy balancing; moderate migration; NATO</t>
         </is>
       </c>
-      <c r="M129" s="2" t="inlineStr">
+      <c r="O129" s="2" t="inlineStr">
         <is>
           <t>L/C — social-democratic</t>
         </is>
@@ -8380,15 +9196,21 @@
       <c r="J130" s="2" t="inlineStr"/>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>Religion; Authoritarian rule; Developmentalism</t>
+          <t>Religion; Developmentalism</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr"/>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
           <t>Sultanate; Islamic tradition; state-led development; controlled migration; energy diversification; regional balancing</t>
         </is>
       </c>
-      <c r="M130" s="2" t="inlineStr">
+      <c r="O130" s="2" t="inlineStr">
         <is>
           <t>T — monarchic traditionalist</t>
         </is>
@@ -8443,15 +9265,21 @@
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>Religion; Authoritarian rule</t>
+          <t>Religion</t>
         </is>
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr"/>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
           <t>Islamic social values; strong state/security; mixed economy; controlled migration; energy/resources; regional balancing</t>
         </is>
       </c>
-      <c r="M131" s="2" t="inlineStr">
+      <c r="O131" s="2" t="inlineStr">
         <is>
           <t>C+/T — religious-national hybrid</t>
         </is>
@@ -8507,10 +9335,16 @@
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr">
         <is>
+          <t>Not covered by V-Dem</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr"/>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
           <t>Market/tourism; climate; US security alignment; migration/mobility</t>
         </is>
       </c>
-      <c r="M132" s="2" t="inlineStr">
+      <c r="O132" s="2" t="inlineStr">
         <is>
           <t>L/C — centrist</t>
         </is>
@@ -8566,10 +9400,20 @@
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>V-Dem unit: Palestine/West Bank (area administered by the Palestinian Authority)</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
           <t>National liberation; institutional state-building; social conservatism; refugee/mobility policy; security diplomacy</t>
         </is>
       </c>
-      <c r="M133" s="2" t="inlineStr">
+      <c r="O133" s="2" t="inlineStr">
         <is>
           <t>L/C — nationalist-centrist</t>
         </is>
@@ -8625,10 +9469,16 @@
       <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr"/>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
           <t>Market economy; security/order; migration control; canal/logistics; pragmatic foreign policy</t>
         </is>
       </c>
-      <c r="M134" s="2" t="inlineStr">
+      <c r="O134" s="2" t="inlineStr">
         <is>
           <t>R — centre-right</t>
         </is>
@@ -8684,10 +9534,16 @@
       </c>
       <c r="L135" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr"/>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
           <t>Resource development; customary/community authority; market + state role; migration; regional security</t>
         </is>
       </c>
-      <c r="M135" s="2" t="inlineStr">
+      <c r="O135" s="2" t="inlineStr">
         <is>
           <t>L/C — developmental-centrist</t>
         </is>
@@ -8743,10 +9599,16 @@
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr"/>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
           <t>Private property/market; traditional social values; controlled migration; agriculture/energy; sovereignty-oriented diplomacy</t>
         </is>
       </c>
-      <c r="M136" s="2" t="inlineStr">
+      <c r="O136" s="2" t="inlineStr">
         <is>
           <t>C — Christian-democratic/national conservative</t>
         </is>
@@ -8806,10 +9668,16 @@
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr"/>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
           <t>Security/order; market economy; traditional social values; migration control; private investment; strong US ties</t>
         </is>
       </c>
-      <c r="M137" s="2" t="inlineStr">
+      <c r="O137" s="2" t="inlineStr">
         <is>
           <t>C+ — conservative-populist</t>
         </is>
@@ -8865,10 +9733,16 @@
       <c r="K138" s="2" t="inlineStr"/>
       <c r="L138" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr"/>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
           <t>National identity; security/order; market + state development; traditional social policy; migration; US/China balancing</t>
         </is>
       </c>
-      <c r="M138" s="2" t="inlineStr">
+      <c r="O138" s="2" t="inlineStr">
         <is>
           <t>C+ — nationalist-conservative hybrid</t>
         </is>
@@ -8928,10 +9802,16 @@
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr"/>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
           <t>Conservative-national presidential office; liberal-centrist government; market economy; migration/security; strong NATO/EU security</t>
         </is>
       </c>
-      <c r="M139" s="2" t="inlineStr">
+      <c r="O139" s="2" t="inlineStr">
         <is>
           <t>L/C — split executive</t>
         </is>
@@ -8987,10 +9867,16 @@
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr"/>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
           <t>Market economy; fiscal reform; moderate social policy; migration controls; EU/NATO</t>
         </is>
       </c>
-      <c r="M140" s="2" t="inlineStr">
+      <c r="O140" s="2" t="inlineStr">
         <is>
           <t>C — moderate centre-right</t>
         </is>
@@ -9045,15 +9931,21 @@
       <c r="J141" s="2" t="inlineStr"/>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>Religion; Authoritarian rule</t>
+          <t>Religion</t>
         </is>
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr"/>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
           <t>Dynastic authority; Islamic tradition; state/energy economy; controlled migration; LNG; regional mediation/security</t>
         </is>
       </c>
-      <c r="M141" s="2" t="inlineStr">
+      <c r="O141" s="2" t="inlineStr">
         <is>
           <t>T — dynastic-religious traditionalist</t>
         </is>
@@ -9077,7 +9969,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -9087,7 +9979,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -9106,17 +9998,19 @@
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr"/>
-      <c r="K142" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr"/>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
           <t>Executive authority; state/resources; social traditionalism; security; continuity</t>
         </is>
       </c>
-      <c r="M142" s="2" t="inlineStr">
+      <c r="O142" s="2" t="inlineStr">
         <is>
           <t>T — authoritarian-nationalist</t>
         </is>
@@ -9168,10 +10062,16 @@
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr"/>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
           <t>Institutional reform; market economy; EU/NATO; migration/security; energy and fiscal reform</t>
         </is>
       </c>
-      <c r="M143" s="2" t="inlineStr">
+      <c r="O143" s="2" t="inlineStr">
         <is>
           <t>L/C — centrist caretaker</t>
         </is>
@@ -9216,7 +10116,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>Authoritarian civilisational conservatism ('traditional values')</t>
+          <t>Civilisational conservatism ('traditional values')</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -9226,15 +10126,21 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>Religion; Authoritarian rule</t>
+          <t>Religion</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr"/>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
           <t>Traditionalism; Orthodox-cultural identity; strong state/authority; strategic sectors; restrictive migration; military/security and sovereignty</t>
         </is>
       </c>
-      <c r="M144" s="2" t="inlineStr">
+      <c r="O144" s="2" t="inlineStr">
         <is>
           <t>T/C+ — authoritarian national-conservative</t>
         </is>
@@ -9258,7 +10164,7 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -9268,7 +10174,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr"/>
@@ -9279,7 +10185,7 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>Developmental-state authoritarianism (RPF)</t>
+          <t>Developmental-state ideology (RPF)</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
@@ -9289,15 +10195,21 @@
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>Authoritarian rule; Developmentalism</t>
+          <t>Developmentalism</t>
         </is>
       </c>
       <c r="L145" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr"/>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
           <t>Order/discipline; developmental state; national unity; controlled migration; security; regional diplomacy</t>
         </is>
       </c>
-      <c r="M145" s="2" t="inlineStr">
+      <c r="O145" s="2" t="inlineStr">
         <is>
           <t>T/C — authoritarian-developmental</t>
         </is>
@@ -9349,10 +10261,16 @@
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr">
         <is>
+          <t>Not covered by V-Dem</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr"/>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
           <t>Tourism; social programmes; climate resilience; regional diplomacy</t>
         </is>
       </c>
-      <c r="M146" s="2" t="inlineStr">
+      <c r="O146" s="2" t="inlineStr">
         <is>
           <t>L/C — centre-left</t>
         </is>
@@ -9404,10 +10322,16 @@
       <c r="K147" s="2" t="inlineStr"/>
       <c r="L147" s="2" t="inlineStr">
         <is>
+          <t>Not covered by V-Dem</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr"/>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
           <t>Social programmes; tourism; climate resilience; regional diplomacy</t>
         </is>
       </c>
-      <c r="M147" s="2" t="inlineStr">
+      <c r="O147" s="2" t="inlineStr">
         <is>
           <t>L/C — centre-left</t>
         </is>
@@ -9463,10 +10387,16 @@
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr">
         <is>
+          <t>Not covered by V-Dem</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr"/>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
           <t>Market economy; private enterprise; moderate social conservatism; tourism/climate; regional diplomacy</t>
         </is>
       </c>
-      <c r="M148" s="2" t="inlineStr">
+      <c r="O148" s="2" t="inlineStr">
         <is>
           <t>R — centre-right</t>
         </is>
@@ -9526,10 +10456,16 @@
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
+          <t>Not covered by V-Dem</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr"/>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
           <t>Customary authority; community tradition; development; climate; regional diplomacy</t>
         </is>
       </c>
-      <c r="M149" s="2" t="inlineStr">
+      <c r="O149" s="2" t="inlineStr">
         <is>
           <t>L/C — customary/centrist</t>
         </is>
@@ -9585,10 +10521,16 @@
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr">
         <is>
+          <t>Not covered by V-Dem</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr"/>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
           <t>Institutional continuity; small-state market economy; European integration</t>
         </is>
       </c>
-      <c r="M150" s="2" t="inlineStr">
+      <c r="O150" s="2" t="inlineStr">
         <is>
           <t>L/C — centrist</t>
         </is>
@@ -9644,10 +10586,16 @@
       <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr"/>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
           <t>Market/tourism; development; moderate social policy; regional diplomacy</t>
         </is>
       </c>
-      <c r="M151" s="2" t="inlineStr">
+      <c r="O151" s="2" t="inlineStr">
         <is>
           <t>L/C — centre-right/centrist</t>
         </is>
@@ -9702,15 +10650,21 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>Authoritarian rule; Developmentalism</t>
+          <t>Developmentalism</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr"/>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
           <t>Dynastic authority; Islamic tradition; state-led diversification; controlled migration; oil/energy; strategic balancing</t>
         </is>
       </c>
-      <c r="M152" s="2" t="inlineStr">
+      <c r="O152" s="2" t="inlineStr">
         <is>
           <t>T — monarchic-religious traditionalist + developmental modernisation</t>
         </is>
@@ -9766,10 +10720,16 @@
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr"/>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
           <t>National sovereignty; social/developmental state; traditional social context; migration; regional diplomacy</t>
         </is>
       </c>
-      <c r="M153" s="2" t="inlineStr">
+      <c r="O153" s="2" t="inlineStr">
         <is>
           <t>L/C — nationalist-developmental</t>
         </is>
@@ -9822,17 +10782,19 @@
           <t>Nationalism; Populism</t>
         </is>
       </c>
-      <c r="K154" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr"/>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
           <t>National identity; authority/order; market economy; migration control; energy/resource policy; strategic balancing</t>
         </is>
       </c>
-      <c r="M154" s="2" t="inlineStr">
+      <c r="O154" s="2" t="inlineStr">
         <is>
           <t>C+ — national-conservative</t>
         </is>
@@ -9888,10 +10850,16 @@
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr"/>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
           <t>Tourism; social policy; climate/ocean governance; moderate migration</t>
         </is>
       </c>
-      <c r="M155" s="2" t="inlineStr">
+      <c r="O155" s="2" t="inlineStr">
         <is>
           <t>L/C — centre-left/centrist</t>
         </is>
@@ -9947,10 +10915,20 @@
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the next category up</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
           <t>Development; social policy; democratic institutions; climate; regional diplomacy</t>
         </is>
       </c>
-      <c r="M156" s="2" t="inlineStr">
+      <c r="O156" s="2" t="inlineStr">
         <is>
           <t>L/C — centre-left</t>
         </is>
@@ -10010,10 +10988,16 @@
       </c>
       <c r="L157" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr"/>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
           <t>Order/institutions; meritocracy; market economy + state intervention; controlled migration; pragmatic climate; strategic trade/security</t>
         </is>
       </c>
-      <c r="M157" s="2" t="inlineStr">
+      <c r="O157" s="2" t="inlineStr">
         <is>
           <t>C/L — communitarian/technocratic conservative hybrid</t>
         </is>
@@ -10073,10 +11057,16 @@
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr"/>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
           <t>Traditional social values; strong state; migration restriction; climate/regulatory scepticism; sovereignty; less support for Ukraine</t>
         </is>
       </c>
-      <c r="M158" s="2" t="inlineStr">
+      <c r="O158" s="2" t="inlineStr">
         <is>
           <t>C+ — nationalist/social conservative</t>
         </is>
@@ -10132,10 +11122,16 @@
       <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr"/>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
           <t>Market/private enterprise; national identity; traditional social values; migration control; NATO/EU</t>
         </is>
       </c>
-      <c r="M159" s="2" t="inlineStr">
+      <c r="O159" s="2" t="inlineStr">
         <is>
           <t>C+ — national-conservative</t>
         </is>
@@ -10187,10 +11183,16 @@
       <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr"/>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
           <t>Customary/community authority; development; resource/tourism economy; climate; security partnerships</t>
         </is>
       </c>
-      <c r="M160" s="2" t="inlineStr">
+      <c r="O160" s="2" t="inlineStr">
         <is>
           <t>R — centre-right/coalitional</t>
         </is>
@@ -10214,7 +11216,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -10224,7 +11226,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -10254,10 +11256,16 @@
       </c>
       <c r="L161" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr"/>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
           <t>Islamic social order; state authority; security; migration/displacement; regional diplomacy</t>
         </is>
       </c>
-      <c r="M161" s="2" t="inlineStr">
+      <c r="O161" s="2" t="inlineStr">
         <is>
           <t>C/T — religious-national/state-building</t>
         </is>
@@ -10313,10 +11321,16 @@
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr"/>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
           <t>Mixed economy; social state; constitutional institutions; migration; energy reform; regional diplomacy</t>
         </is>
       </c>
-      <c r="M162" s="2" t="inlineStr">
+      <c r="O162" s="2" t="inlineStr">
         <is>
           <t>L/C — coalition/centrist</t>
         </is>
@@ -10372,10 +11386,16 @@
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr"/>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
           <t>Industrial policy; welfare; liberal social policy; controlled migration; energy transition; alliance with US</t>
         </is>
       </c>
-      <c r="M163" s="2" t="inlineStr">
+      <c r="O163" s="2" t="inlineStr">
         <is>
           <t>L/C — centre-left</t>
         </is>
@@ -10399,7 +11419,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -10409,7 +11429,7 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr"/>
@@ -10424,17 +11444,19 @@
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr"/>
-      <c r="K164" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K164" s="2" t="inlineStr"/>
       <c r="L164" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr"/>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
           <t>Executive authority; oil/state economy; traditional social order; security; migration/displacement</t>
         </is>
       </c>
-      <c r="M164" s="2" t="inlineStr">
+      <c r="O164" s="2" t="inlineStr">
         <is>
           <t>T — authoritarian-patrimonial</t>
         </is>
@@ -10490,10 +11512,16 @@
       <c r="K165" s="2" t="inlineStr"/>
       <c r="L165" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr"/>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
           <t>Welfare/social state; progressive social policy; managed migration; climate transition; EU/NATO</t>
         </is>
       </c>
-      <c r="M165" s="2" t="inlineStr">
+      <c r="O165" s="2" t="inlineStr">
         <is>
           <t>L — centre-left</t>
         </is>
@@ -10549,10 +11577,16 @@
       <c r="K166" s="2" t="inlineStr"/>
       <c r="L166" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr"/>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
           <t>State reform; mixed economy; social welfare; national sovereignty; migration/debt; regional balancing</t>
         </is>
       </c>
-      <c r="M166" s="2" t="inlineStr">
+      <c r="O166" s="2" t="inlineStr">
         <is>
           <t>L/C — left-national developmental</t>
         </is>
@@ -10576,7 +11610,7 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -10586,7 +11620,7 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr"/>
@@ -10601,17 +11635,19 @@
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr"/>
-      <c r="K167" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K167" s="2" t="inlineStr"/>
       <c r="L167" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr"/>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
           <t>Military authority; security; state continuity; traditional social order; displacement/migration</t>
         </is>
       </c>
-      <c r="M167" s="2" t="inlineStr">
+      <c r="O167" s="2" t="inlineStr">
         <is>
           <t>T — military-transitional</t>
         </is>
@@ -10667,10 +11703,16 @@
       <c r="K168" s="2" t="inlineStr"/>
       <c r="L168" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr"/>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
           <t>Social/developmental state; resource management; moderate social policy; regional diplomacy</t>
         </is>
       </c>
-      <c r="M168" s="2" t="inlineStr">
+      <c r="O168" s="2" t="inlineStr">
         <is>
           <t>L/C — centre-left</t>
         </is>
@@ -10730,10 +11772,16 @@
       <c r="K169" s="2" t="inlineStr"/>
       <c r="L169" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr"/>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
           <t>Market/welfare mix; restrictive migration; law/order; climate transition; NATO/security</t>
         </is>
       </c>
-      <c r="M169" s="2" t="inlineStr">
+      <c r="O169" s="2" t="inlineStr">
         <is>
           <t>R — centre-right caretaker</t>
         </is>
@@ -10789,10 +11837,16 @@
       <c r="K170" s="2" t="inlineStr"/>
       <c r="L170" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr"/>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
           <t>Federalism; property/market economy; gradualism; controlled migration; climate pragmatism; neutrality/security</t>
         </is>
       </c>
-      <c r="M170" s="2" t="inlineStr">
+      <c r="O170" s="2" t="inlineStr">
         <is>
           <t>L/C — consociational centre</t>
         </is>
@@ -10845,17 +11899,19 @@
           <t>Nationalism</t>
         </is>
       </c>
-      <c r="K171" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K171" s="2" t="inlineStr"/>
       <c r="L171" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr"/>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
           <t>Religious/traditional social order; state rebuilding; security; market reconstruction; migration/refugees; regional sovereignty</t>
         </is>
       </c>
-      <c r="M171" s="2" t="inlineStr">
+      <c r="O171" s="2" t="inlineStr">
         <is>
           <t>C+/T — Islamist-national transitional</t>
         </is>
@@ -10879,7 +11935,7 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -10889,7 +11945,7 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr"/>
@@ -10900,7 +11956,7 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>Personalist authoritarianism</t>
+          <t>Personalist state nationalism</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
@@ -10908,17 +11964,19 @@
           <t>Nationalism</t>
         </is>
       </c>
-      <c r="K172" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr"/>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
           <t>Executive authority; traditional social order; state development; controlled migration; security/regional balancing</t>
         </is>
       </c>
-      <c r="M172" s="2" t="inlineStr">
+      <c r="O172" s="2" t="inlineStr">
         <is>
           <t>T — authoritarian-traditionalist</t>
         </is>
@@ -10942,7 +12000,7 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -10952,7 +12010,7 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
@@ -10977,15 +12035,21 @@
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
-          <t>Authoritarian rule; Developmentalism</t>
+          <t>Developmentalism</t>
         </is>
       </c>
       <c r="L173" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr"/>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
           <t>Developmental state; market investment; social conservatism; migration; regional diplomacy</t>
         </is>
       </c>
-      <c r="M173" s="2" t="inlineStr">
+      <c r="O173" s="2" t="inlineStr">
         <is>
           <t>L/C — developmental-centrist</t>
         </is>
@@ -11041,10 +12105,16 @@
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr"/>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
           <t>Monarchy/national tradition; authority; mixed economy; controlled migration; energy/infrastructure; regional balancing</t>
         </is>
       </c>
-      <c r="M174" s="2" t="inlineStr">
+      <c r="O174" s="2" t="inlineStr">
         <is>
           <t>C+/T — monarchic-national conservative hybrid</t>
         </is>
@@ -11104,10 +12174,16 @@
       </c>
       <c r="L175" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr"/>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
           <t>National identity; customary/social tradition; state development; energy/resources; regional diplomacy</t>
         </is>
       </c>
-      <c r="M175" s="2" t="inlineStr">
+      <c r="O175" s="2" t="inlineStr">
         <is>
           <t>L/C — nationalist-developmental</t>
         </is>
@@ -11131,7 +12207,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -11141,7 +12217,7 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr"/>
@@ -11156,17 +12232,19 @@
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr"/>
-      <c r="K176" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr"/>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
           <t>Executive continuity; state/resource economy; social traditionalism; security</t>
         </is>
       </c>
-      <c r="M176" s="2" t="inlineStr">
+      <c r="O176" s="2" t="inlineStr">
         <is>
           <t>T — authoritarian-traditionalist</t>
         </is>
@@ -11222,10 +12300,16 @@
       </c>
       <c r="L177" s="2" t="inlineStr">
         <is>
+          <t>Not covered by V-Dem</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr"/>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
           <t>Monarchy/custom; community authority; development; climate; regional diplomacy</t>
         </is>
       </c>
-      <c r="M177" s="2" t="inlineStr">
+      <c r="O177" s="2" t="inlineStr">
         <is>
           <t>T/C — monarchic-traditionalist</t>
         </is>
@@ -11285,10 +12369,20 @@
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the category below</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
           <t>Market/energy economy; law/order; moderate social policy; migration; regional security</t>
         </is>
       </c>
-      <c r="M178" s="2" t="inlineStr">
+      <c r="O178" s="2" t="inlineStr">
         <is>
           <t>L/C — centre-right/centrist</t>
         </is>
@@ -11312,7 +12406,7 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -11322,7 +12416,7 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr"/>
@@ -11341,17 +12435,19 @@
           <t>Nationalism; Populism</t>
         </is>
       </c>
-      <c r="K179" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr"/>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
           <t>Executive authority; national sovereignty; social conservatism; state role; restrictive migration; security</t>
         </is>
       </c>
-      <c r="M179" s="2" t="inlineStr">
+      <c r="O179" s="2" t="inlineStr">
         <is>
           <t>T — presidential-authoritarian/traditionalist</t>
         </is>
@@ -11411,10 +12507,16 @@
       </c>
       <c r="L180" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="inlineStr"/>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
           <t>Family/religious values; strong executive; state-guided market economy; restrictive migration; energy development; strategic autonomy</t>
         </is>
       </c>
-      <c r="M180" s="2" t="inlineStr">
+      <c r="O180" s="2" t="inlineStr">
         <is>
           <t>C+ — religious-national conservative</t>
         </is>
@@ -11438,7 +12540,7 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -11448,7 +12550,7 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr"/>
@@ -11467,17 +12569,23 @@
           <t>Nationalism</t>
         </is>
       </c>
-      <c r="K181" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the next category up</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
           <t>Dynastic authority; state/resource economy; social traditionalism; controlled migration; security/neutrality</t>
         </is>
       </c>
-      <c r="M181" s="2" t="inlineStr">
+      <c r="O181" s="2" t="inlineStr">
         <is>
           <t>T — dynastic-authoritarian traditionalist</t>
         </is>
@@ -11537,10 +12645,16 @@
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr">
         <is>
+          <t>Not covered by V-Dem</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="inlineStr"/>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
           <t>Climate survival; community/custom; public development; migration/mobility</t>
         </is>
       </c>
-      <c r="M182" s="2" t="inlineStr">
+      <c r="O182" s="2" t="inlineStr">
         <is>
           <t>L/C — centrist</t>
         </is>
@@ -11564,7 +12678,7 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -11574,7 +12688,7 @@
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
@@ -11599,15 +12713,21 @@
       </c>
       <c r="K183" s="2" t="inlineStr">
         <is>
-          <t>Religion; Authoritarian rule</t>
+          <t>Religion</t>
         </is>
       </c>
       <c r="L183" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr"/>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
           <t>Executive authority; religious/social conservatism; market + state; security; migration; regional security</t>
         </is>
       </c>
-      <c r="M183" s="2" t="inlineStr">
+      <c r="O183" s="2" t="inlineStr">
         <is>
           <t>C+/T — nationalist/social conservative</t>
         </is>
@@ -11663,10 +12783,16 @@
       <c r="K184" s="2" t="inlineStr"/>
       <c r="L184" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="inlineStr"/>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
           <t>National sovereignty; security; state mobilisation; European integration; migration/displacement; defence diplomacy</t>
         </is>
       </c>
-      <c r="M184" s="2" t="inlineStr">
+      <c r="O184" s="2" t="inlineStr">
         <is>
           <t>L/C — wartime national-centrist</t>
         </is>
@@ -11721,15 +12847,21 @@
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
-          <t>Authoritarian rule; Developmentalism</t>
+          <t>Developmentalism</t>
         </is>
       </c>
       <c r="L185" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="inlineStr"/>
+      <c r="N185" s="2" t="inlineStr">
+        <is>
           <t>Dynastic authority; Islamic tradition; state-led diversification; controlled migration; energy/technology; strategic balancing</t>
         </is>
       </c>
-      <c r="M185" s="2" t="inlineStr">
+      <c r="O185" s="2" t="inlineStr">
         <is>
           <t>T — dynastic traditionalist + developmental modernisation</t>
         </is>
@@ -11785,10 +12917,20 @@
       <c r="K186" s="2" t="inlineStr"/>
       <c r="L186" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the next category up</t>
+        </is>
+      </c>
+      <c r="N186" s="2" t="inlineStr">
+        <is>
           <t>Welfare/public services; moderate migration reform; climate transition; NATO/US; institutional continuity</t>
         </is>
       </c>
-      <c r="M186" s="2" t="inlineStr">
+      <c r="O186" s="2" t="inlineStr">
         <is>
           <t>L — centre-left</t>
         </is>
@@ -11848,10 +12990,20 @@
       </c>
       <c r="L187" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the next category up</t>
+        </is>
+      </c>
+      <c r="N187" s="2" t="inlineStr">
+        <is>
           <t>Property/market + protectionism; traditional family/religious themes; restrictive migration; fossil-fuel expansion; sovereignty/transactional alliances</t>
         </is>
       </c>
-      <c r="M187" s="2" t="inlineStr">
+      <c r="O187" s="2" t="inlineStr">
         <is>
           <t>C+ — national-conservative/populist</t>
         </is>
@@ -11903,10 +13055,20 @@
       <c r="K188" s="2" t="inlineStr"/>
       <c r="L188" s="2" t="inlineStr">
         <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="M188" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the category below</t>
+        </is>
+      </c>
+      <c r="N188" s="2" t="inlineStr">
+        <is>
           <t>Welfare state; market economy; progressive social policy; climate; regional diplomacy</t>
         </is>
       </c>
-      <c r="M188" s="2" t="inlineStr">
+      <c r="O188" s="2" t="inlineStr">
         <is>
           <t>L — centre-left</t>
         </is>
@@ -11930,7 +13092,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -11940,7 +13102,7 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr"/>
@@ -11951,7 +13113,7 @@
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>Developmental authoritarianism</t>
+          <t>State-led developmentalism</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
@@ -11961,15 +13123,25 @@
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
-          <t>Authoritarian rule; Developmentalism</t>
+          <t>Developmentalism</t>
         </is>
       </c>
       <c r="L189" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M189" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the next category up</t>
+        </is>
+      </c>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
           <t>Executive authority; national/cultural tradition; market reform under state guidance; controlled migration; energy/resources; regional balancing</t>
         </is>
       </c>
-      <c r="M189" s="2" t="inlineStr">
+      <c r="O189" s="2" t="inlineStr">
         <is>
           <t>T/C — authoritarian-developmental</t>
         </is>
@@ -12029,10 +13201,20 @@
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr">
         <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the next category up</t>
+        </is>
+      </c>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
           <t>Customary/community authority; development; climate; migration/mobility; regional diplomacy</t>
         </is>
       </c>
-      <c r="M190" s="2" t="inlineStr">
+      <c r="O190" s="2" t="inlineStr">
         <is>
           <t>L/C — centrist</t>
         </is>
@@ -12084,10 +13266,16 @@
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr">
         <is>
+          <t>Not covered by V-Dem</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="inlineStr"/>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
           <t>Catholic doctrine; hierarchical authority; institutional continuity; social conservatism; humanitarian/multilateral diplomacy</t>
         </is>
       </c>
-      <c r="M191" s="2" t="inlineStr">
+      <c r="O191" s="2" t="inlineStr">
         <is>
           <t>T — religious-traditionalist</t>
         </is>
@@ -12132,7 +13320,7 @@
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>Authoritarian chavismo (Bolivarian socialism)</t>
+          <t>Chavismo (Bolivarian socialism)</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
@@ -12140,17 +13328,19 @@
           <t>Nationalism; Populism</t>
         </is>
       </c>
-      <c r="K192" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="inlineStr"/>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
           <t>State intervention; national sovereignty; social traditionalism; controlled migration; oil; security</t>
         </is>
       </c>
-      <c r="M192" s="2" t="inlineStr">
+      <c r="O192" s="2" t="inlineStr">
         <is>
           <t>L/T — socialist-authoritarian</t>
         </is>
@@ -12205,15 +13395,21 @@
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
-          <t>Authoritarian rule; Developmentalism</t>
+          <t>Developmentalism</t>
         </is>
       </c>
       <c r="L193" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M193" s="2" t="inlineStr"/>
+      <c r="N193" s="2" t="inlineStr">
+        <is>
           <t>Party/state authority; state-guided market economy; national continuity; social discipline; controlled migration; strategic balancing</t>
         </is>
       </c>
-      <c r="M193" s="2" t="inlineStr">
+      <c r="O193" s="2" t="inlineStr">
         <is>
           <t>T/L — communist-nationalist</t>
         </is>
@@ -12237,7 +13433,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -12247,7 +13443,7 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
@@ -12273,10 +13469,16 @@
       </c>
       <c r="L194" s="2" t="inlineStr">
         <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="inlineStr"/>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
           <t>Security/order; religious/social tradition; state reconstruction; migration/displacement; regional security</t>
         </is>
       </c>
-      <c r="M194" s="2" t="inlineStr">
+      <c r="O194" s="2" t="inlineStr">
         <is>
           <t>C/T — fragmented transitional</t>
         </is>
@@ -12328,10 +13530,20 @@
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="inlineStr">
+        <is>
+          <t>Borderline: the confidence interval overlaps the next category up</t>
+        </is>
+      </c>
+      <c r="N195" s="2" t="inlineStr">
+        <is>
           <t>Market/private enterprise; institutional reform; moderate social policy; mining/energy; regional diplomacy</t>
         </is>
       </c>
-      <c r="M195" s="2" t="inlineStr">
+      <c r="O195" s="2" t="inlineStr">
         <is>
           <t>L/C — liberal-centrist</t>
         </is>
@@ -12355,7 +13567,7 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -12365,7 +13577,7 @@
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
@@ -12380,7 +13592,7 @@
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>Liberation-movement authoritarianism (ZANU-PF)</t>
+          <t>Liberation-movement nationalism (ZANU-PF)</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
@@ -12388,24 +13600,26 @@
           <t>Nationalism</t>
         </is>
       </c>
-      <c r="K196" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
+      <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="inlineStr"/>
+      <c r="N196" s="2" t="inlineStr">
+        <is>
           <t>Executive authority; national sovereignty; state/resource economy; traditional social order; security</t>
         </is>
       </c>
-      <c r="M196" s="2" t="inlineStr">
+      <c r="O196" s="2" t="inlineStr">
         <is>
           <t>T/C — nationalist-authoritarian</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M196"/>
+  <autoFilter ref="A1:O196"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12416,14 +13630,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="80" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12442,8 +13658,6 @@
           <t>Share of states</t>
         </is>
       </c>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -12459,8 +13673,6 @@
         <f>B2/$B$8</f>
         <v/>
       </c>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -12476,8 +13688,6 @@
         <f>B3/$B$8</f>
         <v/>
       </c>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -12493,8 +13703,6 @@
         <f>B4/$B$8</f>
         <v/>
       </c>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -12510,13 +13718,11 @@
         <f>B5/$B$8</f>
         <v/>
       </c>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="B6" s="2">
@@ -12527,8 +13733,6 @@
         <f>B6/$B$8</f>
         <v/>
       </c>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -12544,8 +13748,6 @@
         <f>SUM(C2:C6)</f>
         <v/>
       </c>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -12557,16 +13759,6 @@
         <f>COUNTA('195 States'!$A$2:$A$196)</f>
         <v/>
       </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n"/>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -12695,7 +13887,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Conservative core combined strongly with nationalism, populism, religious-nationalist claims or authoritarian rule.</t>
+          <t>Conservative core combined strongly with nationalism, populism or religious-nationalist claims.</t>
         </is>
       </c>
     </row>
@@ -12773,7 +13965,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Socialist core combined strongly with nationalism, populism or authoritarianism.</t>
+          <t>Socialist core combined strongly with nationalism or populism.</t>
         </is>
       </c>
     </row>
@@ -12863,12 +14055,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="D21" s="2">
@@ -12877,7 +14069,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Order, hierarchy and continuity without a sustained macro-ideology (military, personalist or dominant-party rule).</t>
+          <t>Order, hierarchy and continuity without a sustained macro-ideology (typical of military, personalist or dominant-party governments).</t>
         </is>
       </c>
     </row>
@@ -12887,20 +14079,10 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
       <c r="D22" s="2">
         <f>SUM(D11:D21)</f>
         <v/>
       </c>
-      <c r="E22" s="2" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -12913,13 +14095,11 @@
           <t>Type</t>
         </is>
       </c>
-      <c r="C24" s="1" t="n"/>
       <c r="D24" s="1" t="inlineStr">
         <is>
           <t>States</t>
         </is>
       </c>
-      <c r="E24" s="1" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -12932,12 +14112,10 @@
           <t>Thin-centred ideology</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n"/>
       <c r="D25" s="2">
         <f>COUNTIF('195 States'!$J$2:$J$196,"*"&amp;A25&amp;"*")</f>
         <v/>
       </c>
-      <c r="E25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -12950,12 +14128,10 @@
           <t>Thin-centred ideology</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n"/>
       <c r="D26" s="2">
         <f>COUNTIF('195 States'!$J$2:$J$196,"*"&amp;A26&amp;"*")</f>
         <v/>
       </c>
-      <c r="E26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -12968,12 +14144,10 @@
           <t>Thin-centred ideology</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n"/>
       <c r="D27" s="2">
         <f>COUNTIF('195 States'!$J$2:$J$196,"*"&amp;A27&amp;"*")</f>
         <v/>
       </c>
-      <c r="E27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -12986,12 +14160,10 @@
           <t>Thin-centred ideology</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n"/>
       <c r="D28" s="2">
         <f>COUNTIF('195 States'!$J$2:$J$196,"*"&amp;A28&amp;"*")</f>
         <v/>
       </c>
-      <c r="E28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -13004,12 +14176,10 @@
           <t>Adjacent concept</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n"/>
       <c r="D29" s="2">
         <f>COUNTIF('195 States'!$K$2:$K$196,"*"&amp;A29&amp;"*")</f>
         <v/>
       </c>
-      <c r="E29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -13022,30 +14192,240 @@
           <t>Adjacent concept</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n"/>
       <c r="D30" s="2">
         <f>COUNTIF('195 States'!$K$2:$K$196,"*"&amp;A30&amp;"*")</f>
         <v/>
       </c>
-      <c r="E30" s="2" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Authoritarian rule</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Regime context (not an ideology)</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2">
-        <f>COUNTIF('195 States'!$K$2:$K$196,"*"&amp;A31&amp;"*")</f>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Regime type (V-Dem Regimes of the World, 2025) by ideological family</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>Closed autocracy</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>Electoral autocracy</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="inlineStr">
+        <is>
+          <t>Electoral democracy</t>
+        </is>
+      </c>
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t>Liberal democracy</t>
+        </is>
+      </c>
+      <c r="F33" s="1" t="inlineStr">
+        <is>
+          <t>Not covered by V-Dem</t>
+        </is>
+      </c>
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Liberalism</t>
+        </is>
+      </c>
+      <c r="B34" s="2">
+        <f>COUNTIFS('195 States'!$D$2:$D$196,$A34,'195 States'!$L$2:$L$196,B$33)</f>
         <v/>
       </c>
-      <c r="E31" s="2" t="n"/>
+      <c r="C34" s="2">
+        <f>COUNTIFS('195 States'!$D$2:$D$196,$A34,'195 States'!$L$2:$L$196,C$33)</f>
+        <v/>
+      </c>
+      <c r="D34" s="2">
+        <f>COUNTIFS('195 States'!$D$2:$D$196,$A34,'195 States'!$L$2:$L$196,D$33)</f>
+        <v/>
+      </c>
+      <c r="E34" s="2">
+        <f>COUNTIFS('195 States'!$D$2:$D$196,$A34,'195 States'!$L$2:$L$196,E$33)</f>
+        <v/>
+      </c>
+      <c r="F34" s="2">
+        <f>COUNTIFS('195 States'!$D$2:$D$196,$A34,'195 States'!$L$2:$L$196,F$33)</f>
+        <v/>
+      </c>
+      <c r="G34" s="2">
+        <f>SUM(B34:F34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Conservatism</t>
+        </is>
+      </c>
+      <c r="B35" s="2">
+        <f>COUNTIFS('195 States'!$D$2:$D$196,$A35,'195 States'!$L$2:$L$196,B$33)</f>
+        <v/>
+      </c>
+      <c r="C35" s="2">
+        <f>COUNTIFS('195 States'!$D$2:$D$196,$A35,'195 States'!$L$2:$L$196,C$33)</f>
+        <v/>
+      </c>
+      <c r="D35" s="2">
+        <f>COUNTIFS('195 States'!$D$2:$D$196,$A35,'195 States'!$L$2:$L$196,D$33)</f>
+        <v/>
+      </c>
+      <c r="E35" s="2">
+        <f>COUNTIFS('195 States'!$D$2:$D$196,$A35,'195 States'!$L$2:$L$196,E$33)</f>
+        <v/>
+      </c>
+      <c r="F35" s="2">
+        <f>COUNTIFS('195 States'!$D$2:$D$196,$A35,'195 States'!$L$2:$L$196,F$33)</f>
+        <v/>
+      </c>
+      <c r="G35" s="2">
+        <f>SUM(B35:F35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Socialism</t>
+        </is>
+      </c>
+      <c r="B36" s="2">
+        <f>COUNTIFS('195 States'!$D$2:$D$196,$A36,'195 States'!$L$2:$L$196,B$33)</f>
+        <v/>
+      </c>
+      <c r="C36" s="2">
+        <f>COUNTIFS('195 States'!$D$2:$D$196,$A36,'195 States'!$L$2:$L$196,C$33)</f>
+        <v/>
+      </c>
+      <c r="D36" s="2">
+        <f>COUNTIFS('195 States'!$D$2:$D$196,$A36,'195 States'!$L$2:$L$196,D$33)</f>
+        <v/>
+      </c>
+      <c r="E36" s="2">
+        <f>COUNTIFS('195 States'!$D$2:$D$196,$A36,'195 States'!$L$2:$L$196,E$33)</f>
+        <v/>
+      </c>
+      <c r="F36" s="2">
+        <f>COUNTIFS('195 States'!$D$2:$D$196,$A36,'195 States'!$L$2:$L$196,F$33)</f>
+        <v/>
+      </c>
+      <c r="G36" s="2">
+        <f>SUM(B36:F36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Religious-political ideology</t>
+        </is>
+      </c>
+      <c r="B37" s="2">
+        <f>COUNTIFS('195 States'!$D$2:$D$196,$A37,'195 States'!$L$2:$L$196,B$33)</f>
+        <v/>
+      </c>
+      <c r="C37" s="2">
+        <f>COUNTIFS('195 States'!$D$2:$D$196,$A37,'195 States'!$L$2:$L$196,C$33)</f>
+        <v/>
+      </c>
+      <c r="D37" s="2">
+        <f>COUNTIFS('195 States'!$D$2:$D$196,$A37,'195 States'!$L$2:$L$196,D$33)</f>
+        <v/>
+      </c>
+      <c r="E37" s="2">
+        <f>COUNTIFS('195 States'!$D$2:$D$196,$A37,'195 States'!$L$2:$L$196,E$33)</f>
+        <v/>
+      </c>
+      <c r="F37" s="2">
+        <f>COUNTIFS('195 States'!$D$2:$D$196,$A37,'195 States'!$L$2:$L$196,F$33)</f>
+        <v/>
+      </c>
+      <c r="G37" s="2">
+        <f>SUM(B37:F37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Traditionalist (order-centred)</t>
+        </is>
+      </c>
+      <c r="B38" s="2">
+        <f>COUNTIFS('195 States'!$D$2:$D$196,$A38,'195 States'!$L$2:$L$196,B$33)</f>
+        <v/>
+      </c>
+      <c r="C38" s="2">
+        <f>COUNTIFS('195 States'!$D$2:$D$196,$A38,'195 States'!$L$2:$L$196,C$33)</f>
+        <v/>
+      </c>
+      <c r="D38" s="2">
+        <f>COUNTIFS('195 States'!$D$2:$D$196,$A38,'195 States'!$L$2:$L$196,D$33)</f>
+        <v/>
+      </c>
+      <c r="E38" s="2">
+        <f>COUNTIFS('195 States'!$D$2:$D$196,$A38,'195 States'!$L$2:$L$196,E$33)</f>
+        <v/>
+      </c>
+      <c r="F38" s="2">
+        <f>COUNTIFS('195 States'!$D$2:$D$196,$A38,'195 States'!$L$2:$L$196,F$33)</f>
+        <v/>
+      </c>
+      <c r="G38" s="2">
+        <f>SUM(B38:F38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B39" s="2">
+        <f>SUM(B34:B38)</f>
+        <v/>
+      </c>
+      <c r="C39" s="2">
+        <f>SUM(C34:C38)</f>
+        <v/>
+      </c>
+      <c r="D39" s="2">
+        <f>SUM(D34:D38)</f>
+        <v/>
+      </c>
+      <c r="E39" s="2">
+        <f>SUM(E34:E38)</f>
+        <v/>
+      </c>
+      <c r="F39" s="2">
+        <f>SUM(F34:F38)</f>
+        <v/>
+      </c>
+      <c r="G39" s="2">
+        <f>SUM(G34:G38)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13058,7 +14438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -13085,7 +14465,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>This dataset's ideological codes were created with Claude (Anthropic's AI model), starting from a dataset generated with ChatGPT. It is a representative teaching illustration, not the result of actual research. Treat every code as material to question, not as evidence.</t>
+          <t>This dataset's ideological codes were created with Claude (Anthropic's AI model), starting from a dataset generated with ChatGPT. It is a representative teaching illustration, not the result of actual research. Treat every code as material to question, not as evidence. The regime-type column is the exception: it is taken directly from V-Dem, a peer-reviewed expert-coded dataset.</t>
         </is>
       </c>
     </row>
@@ -13097,7 +14477,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 (leaders as in the corrected conservatism dataset of the same date)</t>
+          <t>2026-10-03 for leaders and ideological codes; 2025 for V-Dem regime type (latest year in V-Dem v16).</t>
         </is>
       </c>
     </row>
@@ -13157,7 +14537,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>The macro-ideology whose core concepts organise the government's programme: Liberalism, Conservatism, Socialism, plus Religious-political ideology and a residual Traditionalist-authoritarian category. Nationalism is never coded as the family: in Freeden's account it is thin-centred and needs a host, so it is recorded as a component (and signalled by "+" variants).</t>
+          <t>The macro-ideology whose core concepts organise the government's programme: Liberalism, Conservatism, Socialism, plus Religious-political ideology and a residual Traditionalist (order-centred) category. Nationalism is never coded as the family: in Freeden's account it is thin-centred and needs a host, so it is recorded as a component (and signalled by "+" variants).</t>
         </is>
       </c>
     </row>
@@ -13212,12 +14592,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Traditionalist-authoritarian</t>
+          <t>Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Residual category, not a Freeden family: hierarchy, order, continuity and state authority dominate, but no liberal, conservative or socialist programme is sustained at the core. Typical of military, personalist and dominant-party regimes. Calling these conservative would overstate the presence of conservative morphology; nationalism usually appears as a component.</t>
+          <t>Residual category, not a Freeden family: hierarchy, order, continuity and state authority dominate the governing ideas, but no liberal, conservative or socialist programme is sustained at the core. Typical of military, personalist and dominant-party governments. Calling these conservative would overstate the presence of conservative morphology; nationalism usually appears as a component.</t>
         </is>
       </c>
     </row>
@@ -13265,7 +14645,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Conservative core combined strongly with nationalism, populism, religious-nationalist claims or authoritarian rule.</t>
+          <t>Conservative core combined strongly with nationalism, populism or religious-nationalist claims.</t>
         </is>
       </c>
     </row>
@@ -13301,7 +14681,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Socialist core combined strongly with nationalism, populism or authoritarianism.</t>
+          <t>Socialist core combined strongly with nationalism or populism.</t>
         </is>
       </c>
     </row>
@@ -13344,12 +14724,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>T - Traditionalist-authoritarian</t>
+          <t>T - Traditionalist (order-centred)</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Order, hierarchy and continuity without a sustained macro-ideology (military, personalist or dominant-party rule).</t>
+          <t>Order, hierarchy and continuity without a sustained macro-ideology (typical of military, personalist or dominant-party governments).</t>
         </is>
       </c>
     </row>
@@ -13361,7 +14741,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>As in the earlier conservatism scheme (C vs C+), "+" marks a family core combined strongly with a thin-centred ideology (nationalism, populism), with theocratic or religious-nationalist claims, or with authoritarian rule. C+ is national/religious/populist conservatism, S+ left-nationalist or left-populist socialism, L+ national or populist liberalism, RE+ religious-national rule.</t>
+          <t>As in the earlier conservatism scheme (C vs C+), "+" marks a family core combined strongly with a thin-centred ideology (nationalism, populism) or with theocratic or religious-nationalist claims. C+ is national/religious/populist conservatism, S+ left-nationalist or left-populist socialism, L+ national or populist liberalism, RE+ religious-national rule. How power is held (democracy or autocracy) is not part of the ideological code; it is recorded separately as the V-Dem regime type.</t>
         </is>
       </c>
     </row>
@@ -13373,7 +14753,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>A second family whose core concepts are clearly present in adjacent positions (e.g. coalition partners). Written VARIANT/SECONDARY, e.g. C/LIB = conservatism with liberal adjacency, T/SOC = traditionalist-authoritarian rule with a socialist legacy.</t>
+          <t>A second family whose core concepts are clearly present in adjacent positions (e.g. coalition partners). Written VARIANT/SECONDARY, e.g. C/LIB = conservatism with liberal adjacency, T/SOC = order-centred traditionalist rule with a socialist legacy.</t>
         </is>
       </c>
     </row>
@@ -13392,53 +14772,137 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Adjacent concepts / regime context</t>
+          <t>Adjacent concepts</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Religion and Developmentalism are recorded as adjacent concepts. Authoritarian rule is regime context, not an ideology: it is recorded so that students can separate how power is held from what ideas justify it.</t>
+          <t>Religion and Developmentalism, recorded where they sit close to the core of the governing ideology.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Hard cases</t>
+          <t>Regime type (V-Dem)</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Russia is coded C+ because "traditional values" conservatism is now official doctrine, not just regime practice. North Korea stays in the socialist family (SM) although Juche nationalism dominates its core. Ex-Marxist dominant parties (Angola, Mozambique, Tanzania, Eritrea, Zimbabwe, Republic of the Congo) are coded T with SOC as secondary family, because socialism survives only as a legacy.</t>
+          <t>Taken directly from the V-Dem Regimes of the World indicator (v2x_regime), V-Dem dataset v16, year 2025: closed autocracy, electoral autocracy, electoral democracy, liberal democracy (Lührmann, Tannenberg and Lindberg 2018). It replaces the earlier "Authoritarian rule" tag, which had been assigned by judgement. The V-Dem note flags borderline cases using v2x_regime_amb, where the confidence interval overlaps a neighbouring category.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Previous code</t>
+          <t>Closed autocracy (V-Dem)</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>The final column keeps the code from the conservatism-only scheme (C, C+, L/C, R, T and hybrids) so the two classifications can be compared.</t>
+          <t>No multiparty elections for the chief executive or the legislature.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>Electoral autocracy (V-Dem)</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Multiparty elections are held, but they are not free and fair, or basic freedoms of expression and association are missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Electoral democracy (V-Dem)</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Free and fair multiparty elections with satisfactory freedom of expression and association (V-Dem's minimal democracy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Liberal democracy (V-Dem)</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Electoral democracy plus strong rule of law, judicial and legislative constraints on the executive, and protection of individual liberties.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Not covered by V-Dem</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>22 states are not coded by V-Dem, mostly microstates (e.g. Andorra, Monaco, Vatican City, several Caribbean and Pacific island states, Brunei).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Timing mismatch</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>V-Dem rates each country for 2025, while leaders and ideological codes are as of 3 October 2026. Where government changed in 2026 the regime type describes the previous period (e.g. Hungary is rated an electoral autocracy for 2025, the last Orbán year).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Hard cases</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Russia is coded C+ because "traditional values" conservatism is now official doctrine, not just regime practice. North Korea stays in the socialist family (SM) although Juche nationalism dominates its core. Ex-Marxist dominant parties (Angola, Mozambique, Tanzania, Eritrea, Zimbabwe, Republic of the Congo) are coded T with SOC as secondary family, because socialism survives only as a legacy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Previous code</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>The final column keeps the code from the conservatism-only scheme (C, C+, L/C, R, T and hybrids) so the two classifications can be compared.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
           <t>Caveat</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Codes are interpretive judgements for teaching and discussion, not measurements. Coalitions, caretaker and transitional governments are coded by their dominant governing morphology. The policy column is descriptive and unchanged from the source dataset.</t>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Ideological codes are interpretive judgements for teaching and discussion, not measurements. Coalitions, caretaker and transitional governments are coded by their dominant governing morphology. The policy column is descriptive and unchanged from the source dataset.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B31"/>
+  <autoFilter ref="A1:B38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13449,7 +14913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -13628,8 +15092,110 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Regime type data</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Coppedge, M., Gerring, J., Knutsen, C.H., Lindberg, S.I., Teorell, J. et al. (2026) "V-Dem Country-Year Dataset v16." Varieties of Democracy (V-Dem) Project. Variables v2x_regime and v2x_regime_amb, year 2025; obtained via the vdemdata R package v16.0.</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.23696/vdemds26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Regime type classification</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Lührmann, A., Tannenberg, M. and Lindberg, S.I. (2018) "Regimes of the World (RoW): Opening New Avenues for the Comparative Study of Political Regimes." Politics and Governance 6(1): 60-77.</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.17645/pag.v6i1.1214</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Regime type data</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Coppedge, M., Gerring, J., Knutsen, C.H., Lindberg, S.I., Teorell, J. et al. (2026) "V-Dem Country-Year Dataset v16." Varieties of Democracy (V-Dem) Project. Variables v2x_regime and v2x_regime_amb, year 2025; obtained via the vdemdata R package v16.0.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.23696/vdemds26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Regime type classification</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Lührmann, A., Tannenberg, M. and Lindberg, S.I. (2018) "Regimes of the World (RoW): Opening New Avenues for the Comparative Study of Political Regimes." Politics and Governance 6(1): 60-77.</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.17645/pag.v6i1.1214</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Regime type data</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Coppedge, M., Gerring, J., Knutsen, C.H., Lindberg, S.I., Teorell, J. et al. (2026) "V-Dem Country-Year Dataset v16." Varieties of Democracy (V-Dem) Project. Variables v2x_regime and v2x_regime_amb, year 2025; obtained via the vdemdata R package v16.0.</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.23696/vdemds26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Regime type classification</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Lührmann, A., Tannenberg, M. and Lindberg, S.I. (2018) "Regimes of the World (RoW): Opening New Avenues for the Comparative Study of Political Regimes." Politics and Governance 6(1): 60-77.</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.17645/pag.v6i1.1214</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C11"/>
+  <autoFilter ref="A1:C17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13640,12 +15206,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F112"/>
+  <dimension ref="A1:F115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="70" customWidth="1" min="6" max="6"/>
@@ -13686,7 +15252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Notice</t>
+          <t>Regime type</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -13696,29 +15262,29 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Methodology</t>
+          <t>Adjacent concepts / regime context</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>"Authoritarian rule" tag (assigned by judgement)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>"Created with Claude. Illustrative only." notice; ChatGPT origin of the base dataset recorded; "+" variants worded as theocratic or religious-nationalist claims rather than religion</t>
+          <t>Regime type from V-Dem Regimes of the World, 2025 (v16), with borderline flags</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Clarify provenance and that the dataset is a teaching illustration, not research</t>
+          <t>Regime type now comes from an established expert-coded dataset instead of a judgement tag</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Recoding</t>
+          <t>Regime type</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -13728,86 +15294,86 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Variant definitions</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Five families with nationalism as a possible primary family (LIB, CON, SOC, NAT, REL)</t>
+          <t>"+" variants could rest on authoritarian rule; residual category named "Traditionalist-authoritarian"</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Variants within each family (L, L+; C, C+, Cm; S, S+, SM; RE, RE+) plus residual T; nationalism only as a component</t>
+          <t>"+" variants rest on nationalism, populism or theocratic/religious-nationalist claims; residual category renamed "Traditionalist (order-centred)"</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Nationalism is thin-centred (Freeden 1998) and is not treated as a host ideology; variants show the range of decontested forms within each family, as C and C+ did in the conservatism scheme</t>
+          <t>Keeps the ideological code separate from regime type, which V-Dem now measures; no state changed variant as a result</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Recoding</t>
+          <t>Regime type</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>18 states</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Decontested form</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>NAT/SOC</t>
+          <t>Descriptions using "authoritarian" (e.g. "Developmental authoritarianism")</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>Descriptions of the governing ideas only (e.g. "State-led developmentalism")</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
+          <t>How power is held is now shown by the V-Dem column, so the ideological description no longer repeats it</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Recoding</t>
+          <t>Notice</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>All 195 states</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Methodology</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>NAT/SOC</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>T/SOC</t>
+          <t>"Created with Claude. Illustrative only." notice; ChatGPT origin of the base dataset recorded; "+" variants worded as theocratic or religious-nationalist claims rather than religion</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
+          <t>Clarify provenance and that the dataset is a teaching illustration, not research</t>
         </is>
       </c>
     </row>
@@ -13819,7 +15385,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>All 195 states</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -13829,17 +15395,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>Five families with nationalism as a possible primary family (LIB, CON, SOC, NAT, REL)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Variants within each family (L, L+; C, C+, Cm; S, S+, SM; RE, RE+) plus residual T; nationalism only as a component</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
+          <t>Nationalism is thin-centred (Freeden 1998) and is not treated as a host ideology; variants show the range of decontested forms within each family, as C and C+ did in the conservatism scheme</t>
         </is>
       </c>
     </row>
@@ -13851,7 +15417,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -13861,12 +15427,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>NAT/CON</t>
+          <t>NAT/SOC</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>S+</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -13883,7 +15449,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -13893,7 +15459,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>NAT/CON</t>
+          <t>NAT/SOC</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -13915,7 +15481,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -13925,12 +15491,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>NAT/LIB</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>C+/SOC</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -13947,7 +15513,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -13957,12 +15523,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>NAT/SOC</t>
+          <t>NAT/CON</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -13979,7 +15545,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Belarus</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -13989,12 +15555,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>NAT/SOC</t>
+          <t>NAT/CON</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>T/SOC</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -14011,7 +15577,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -14021,12 +15587,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/LIB</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>C+/SOC</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -14043,7 +15609,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -14053,12 +15619,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>NAT/CON</t>
+          <t>NAT/SOC</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>T/CON</t>
+          <t>S+</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -14075,7 +15641,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -14085,12 +15651,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>NAT/CON</t>
+          <t>NAT/SOC</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>S+</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -14107,7 +15673,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Central African Republic</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -14139,7 +15705,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Chad</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -14149,12 +15715,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/CON</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>T/CON</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -14171,7 +15737,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -14181,12 +15747,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>NAT/REL</t>
+          <t>NAT/CON</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>T/REL</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -14203,7 +15769,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Central African Republic</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -14213,12 +15779,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>NAT/CON</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -14235,7 +15801,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Djibouti</t>
+          <t>Chad</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -14267,7 +15833,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -14277,12 +15843,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/REL</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>T/REL</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -14299,7 +15865,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>El Salvador</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -14331,7 +15897,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Equatorial Guinea</t>
+          <t>Djibouti</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -14363,7 +15929,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Eritrea</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -14373,12 +15939,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>NAT/SOC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>T/SOC</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -14395,7 +15961,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>El Salvador</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -14405,12 +15971,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>NAT/LIB</t>
+          <t>NAT/CON</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>T/LIB</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -14427,7 +15993,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Equatorial Guinea</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -14459,7 +16025,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Eritrea</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -14469,12 +16035,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>NAT/CON</t>
+          <t>NAT/SOC</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>T/SOC</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -14491,7 +16057,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -14501,12 +16067,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/LIB</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>T/LIB</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -14523,7 +16089,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -14555,7 +16121,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -14587,7 +16153,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -14597,12 +16163,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>NAT/CON</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -14619,7 +16185,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -14629,12 +16195,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>NAT/CON</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -14651,7 +16217,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -14661,12 +16227,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/CON</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -14683,7 +16249,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Kyrgyzstan</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -14698,7 +16264,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>T/CON</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -14715,7 +16281,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Libya</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -14725,12 +16291,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>NAT/LIB</t>
+          <t>NAT/CON</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>T/LIB</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -14747,7 +16313,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -14779,7 +16345,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Maldives</t>
+          <t>Kyrgyzstan</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -14789,12 +16355,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>NAT/REL</t>
+          <t>NAT/CON</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>T/CON</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -14811,7 +16377,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>Libya</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -14821,12 +16387,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/LIB</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>T/LIB</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -14843,7 +16409,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Mauritania</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -14853,12 +16419,12 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>NAT/REL</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>T/REL</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -14875,7 +16441,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Maldives</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -14885,12 +16451,12 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>NAT/SOC</t>
+          <t>NAT/REL</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>T/SOC</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -14907,7 +16473,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -14917,12 +16483,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>NAT/REL</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>T/REL</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -14939,7 +16505,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Nicaragua</t>
+          <t>Mauritania</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -14949,12 +16515,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>NAT/SOC</t>
+          <t>NAT/REL</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>T/REL</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -14971,7 +16537,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Niger</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -14981,12 +16547,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/SOC</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>T/SOC</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -15003,7 +16569,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>North Korea</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -15013,12 +16579,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>NAT/SOC</t>
+          <t>NAT/REL</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>SM</t>
+          <t>T/REL</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -15035,7 +16601,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Nicaragua</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -15045,12 +16611,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>NAT/REL</t>
+          <t>NAT/SOC</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>S+</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -15067,7 +16633,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Palestine</t>
+          <t>Niger</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -15082,7 +16648,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -15099,7 +16665,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Republic of the Congo</t>
+          <t>North Korea</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -15114,7 +16680,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>T/SOC</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -15131,7 +16697,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -15141,7 +16707,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>NAT/CON</t>
+          <t>NAT/REL</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -15163,7 +16729,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Palestine</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -15178,7 +16744,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>S+</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -15195,7 +16761,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Republic of the Congo</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -15210,7 +16776,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>T/SOC</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -15227,7 +16793,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -15259,7 +16825,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -15269,12 +16835,12 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>NAT/SOC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>S+/CON</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -15291,7 +16857,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -15301,12 +16867,12 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>NAT/REL</t>
+          <t>NAT/SOC</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>T/REL</t>
+          <t>S+</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -15323,7 +16889,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -15333,12 +16899,12 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/CON</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -15355,7 +16921,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Sudan</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -15365,12 +16931,12 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/SOC</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>S+/CON</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -15387,7 +16953,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Tajikistan</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -15397,12 +16963,12 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/REL</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>T/REL</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -15419,7 +16985,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -15429,12 +16995,12 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>NAT/SOC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>T/SOC</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -15451,7 +17017,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Timor-Leste</t>
+          <t>Sudan</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -15466,7 +17032,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L+</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -15483,7 +17049,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Tajikistan</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -15515,7 +17081,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -15525,12 +17091,12 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/SOC</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>T/SOC</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -15547,7 +17113,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Turkmenistan</t>
+          <t>Timor-Leste</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -15562,7 +17128,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>L+</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -15579,7 +17145,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -15589,12 +17155,12 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>NAT/CON</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>T/CON</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -15611,7 +17177,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -15621,12 +17187,12 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>NAT/CON</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -15643,7 +17209,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Turkmenistan</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -15675,7 +17241,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -15685,12 +17251,12 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>NAT/REL</t>
+          <t>NAT/CON</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>T/REL</t>
+          <t>T/CON</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -15707,7 +17273,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -15717,12 +17283,12 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NAT/CON</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>T/SOC</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -15739,7 +17305,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>All 195 states</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -15749,17 +17315,17 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Conservatism-only scheme (C, C+, L/C, R, T)</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Freeden ideological families (LIB, CON, SOC, NAT, REL) + secondary family + thin-centred components</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Dataset broadened from "how conservative is this government?" to "which ideological family organises it?"; previous code retained in the last column</t>
+          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
         </is>
       </c>
     </row>
@@ -15771,7 +17337,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -15781,17 +17347,17 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>R - centre-right security-oriented</t>
+          <t>NAT/REL</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>SOC/NAT - social democracy (LSDP-led coalition)</t>
+          <t>T/REL</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Prime Minister Sinkevičius leads the Social Democratic Party (LSDP); previous R code did not match the governing party</t>
+          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
         </is>
       </c>
     </row>
@@ -15803,7 +17369,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>T-coded states (39)</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -15813,17 +17379,17 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>T - traditionalist-authoritarian</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>NAT, CON (monarchical traditionalism) or REL</t>
+          <t>T/SOC</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>The residual T category is not a Freeden family; split by the core concepts that organise each regime</t>
+          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
         </is>
       </c>
     </row>
@@ -15835,7 +17401,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>L/C-coded states (59)</t>
+          <t>All 195 states</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -15845,61 +17411,61 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>L/C</t>
+          <t>Conservatism-only scheme (C, C+, L/C, R, T)</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>LIB or SOC (social democracy) by governing party, NAT where liberation/developmental nationalism dominates</t>
+          <t>Freeden ideological families (LIB, CON, SOC, NAT, REL) + secondary family + thin-centred components</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>L/C merged liberal and socialist governments; Freeden treats liberalism and socialism as distinct macro-ideologies</t>
+          <t>Dataset broadened from "how conservative is this government?" to "which ideological family organises it?"; previous code retained in the last column</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Factual</t>
+          <t>Recoding</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Head of state</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Mohammed Shahabuddin</t>
+          <t>R - centre-right security-oriented</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Mirza Fakhrul Islam Alamgir</t>
+          <t>SOC/NAT - social democracy (LSDP-led coalition)</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Shahabuddin resigned 24 Jul 2026; Alamgir elected 20 Aug 2026</t>
+          <t>Prime Minister Sinkevičius leads the Social Democratic Party (LSDP); previous R code did not match the governing party</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>C/L split</t>
+          <t>Recoding</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>T-coded states (39)</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -15909,29 +17475,29 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>C/L — centre-right liberal</t>
+          <t>T - traditionalist-authoritarian</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>R — centre-right liberal</t>
+          <t>NAT, CON (monarchical traditionalism) or REL</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
+          <t>The residual T category is not a Freeden family; split by the core concepts that organise each regime</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>C/L split</t>
+          <t>Recoding</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>L/C-coded states (59)</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -15941,49 +17507,49 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>C/L — fragmented coalition</t>
+          <t>L/C</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>L/C — fragmented coalition</t>
+          <t>LIB or SOC (social democracy) by governing party, NAT where liberation/developmental nationalism dominates</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
+          <t>L/C merged liberal and socialist governments; Freeden treats liberalism and socialism as distinct macro-ideologies</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>C/L split</t>
+          <t>Factual</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Congo, Democratic Republic of the</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Head of state</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>C/L — centrist-developmental</t>
+          <t>Mohammed Shahabuddin</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>L/C — centrist-developmental</t>
+          <t>Mirza Fakhrul Islam Alamgir</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
+          <t>Shahabuddin resigned 24 Jul 2026; Alamgir elected 20 Aug 2026</t>
         </is>
       </c>
     </row>
@@ -15995,7 +17561,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -16005,12 +17571,12 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>C/L — moderate centre-right</t>
+          <t>C/L — centre-right liberal</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>R — moderate centre-right</t>
+          <t>R — centre-right liberal</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -16027,7 +17593,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -16037,12 +17603,12 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>C/L — liberal-centrist, not primarily conservative</t>
+          <t>C/L — fragmented coalition</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L/C — liberal-centrist, not primarily conservative</t>
+          <t>L/C — fragmented coalition</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -16059,7 +17625,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Congo, Democratic Republic of the</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -16069,12 +17635,12 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>C/L — developmental-centrist</t>
+          <t>C/L — centrist-developmental</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>L/C — developmental-centrist</t>
+          <t>L/C — centrist-developmental</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -16091,7 +17657,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -16101,12 +17667,12 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>C/L — developmental centre-right</t>
+          <t>C/L — moderate centre-right</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>R — developmental centre-right</t>
+          <t>R — moderate centre-right</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -16123,7 +17689,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Kiribati</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -16133,12 +17699,12 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>C/L — developmental-centrist</t>
+          <t>C/L — liberal-centrist, not primarily conservative</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>L/C — developmental-centrist</t>
+          <t>L/C — liberal-centrist, not primarily conservative</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -16155,7 +17721,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -16165,17 +17731,17 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>C/L — centre-right liberal</t>
+          <t>C/L — developmental-centrist</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>R — centre-right liberal</t>
+          <t>L/C — developmental-centrist</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
+          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
         </is>
       </c>
     </row>
@@ -16187,7 +17753,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -16197,17 +17763,17 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>C/L — institutional/coalitional</t>
+          <t>C/L — developmental centre-right</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>L/C — institutional/coalitional</t>
+          <t>R — developmental centre-right</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
+          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
         </is>
       </c>
     </row>
@@ -16219,7 +17785,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Kiribati</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -16229,17 +17795,17 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>C/L — centre-right developmental</t>
+          <t>C/L — developmental-centrist</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>R — centre-right developmental</t>
+          <t>L/C — developmental-centrist</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
+          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
         </is>
       </c>
     </row>
@@ -16251,7 +17817,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Libya</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -16261,17 +17827,17 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>C/L — fragmented transitional</t>
+          <t>C/L — centre-right liberal</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>L/C — fragmented transitional</t>
+          <t>R — centre-right liberal</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
+          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
         </is>
       </c>
     </row>
@@ -16283,7 +17849,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -16293,17 +17859,17 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>C/L — centre-right security-oriented</t>
+          <t>C/L — institutional/coalitional</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>R — centre-right security-oriented</t>
+          <t>L/C — institutional/coalitional</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
+          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
         </is>
       </c>
     </row>
@@ -16315,7 +17881,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -16325,12 +17891,12 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>C/L — centre-right</t>
+          <t>C/L — centre-right developmental</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>R — centre-right</t>
+          <t>R — centre-right developmental</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -16347,7 +17913,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Libya</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -16357,12 +17923,12 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>C/L — coalition/centrist</t>
+          <t>C/L — fragmented transitional</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L/C — coalition/centrist</t>
+          <t>L/C — fragmented transitional</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -16379,7 +17945,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Moldova</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -16389,17 +17955,17 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>C/L — liberal-centrist</t>
+          <t>C/L — centre-right security-oriented</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>L/C — liberal-centrist</t>
+          <t>R — centre-right security-oriented</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
+          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
         </is>
       </c>
     </row>
@@ -16411,7 +17977,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -16421,17 +17987,17 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>C/L — populist-centrist</t>
+          <t>C/L — centre-right</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L/C — populist-centrist</t>
+          <t>R — centre-right</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
+          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
         </is>
       </c>
     </row>
@@ -16443,7 +18009,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -16453,17 +18019,17 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>C/L — centre-right</t>
+          <t>C/L — coalition/centrist</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>R — centre-right</t>
+          <t>L/C — coalition/centrist</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
+          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
         </is>
       </c>
     </row>
@@ -16475,7 +18041,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Papua New Guinea</t>
+          <t>Moldova</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -16485,12 +18051,12 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>C/L — developmental-centrist</t>
+          <t>C/L — liberal-centrist</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>L/C — developmental-centrist</t>
+          <t>L/C — liberal-centrist</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -16507,7 +18073,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -16517,12 +18083,12 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>C/L — split executive</t>
+          <t>C/L — populist-centrist</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>L/C — split executive</t>
+          <t>L/C — populist-centrist</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -16539,7 +18105,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -16549,17 +18115,17 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>C/L — centrist caretaker</t>
+          <t>C/L — centre-right</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>L/C — centrist caretaker</t>
+          <t>R — centre-right</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
+          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
         </is>
       </c>
     </row>
@@ -16571,7 +18137,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Saint Vincent and the Grenadines</t>
+          <t>Papua New Guinea</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -16581,17 +18147,17 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>C/L — centre-right</t>
+          <t>C/L — developmental-centrist</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>R — centre-right</t>
+          <t>L/C — developmental-centrist</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
+          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
         </is>
       </c>
     </row>
@@ -16603,7 +18169,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Samoa</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -16613,12 +18179,12 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>C/L — customary/centrist</t>
+          <t>C/L — split executive</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>L/C — customary/centrist</t>
+          <t>L/C — split executive</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -16635,7 +18201,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>San Marino</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -16645,12 +18211,12 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>C/L — centrist</t>
+          <t>C/L — centrist caretaker</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>L/C — centrist</t>
+          <t>L/C — centrist caretaker</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -16667,7 +18233,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>São Tomé and Príncipe</t>
+          <t>Saint Vincent and the Grenadines</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -16677,17 +18243,17 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>C/L — centre-right/centrist</t>
+          <t>C/L — centre-right</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>L/C — centre-right/centrist</t>
+          <t>R — centre-right</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
+          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
         </is>
       </c>
     </row>
@@ -16699,7 +18265,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Samoa</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -16709,12 +18275,12 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>C/L — nationalist-developmental</t>
+          <t>C/L — customary/centrist</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>L/C — nationalist-developmental</t>
+          <t>L/C — customary/centrist</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -16731,7 +18297,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Solomon Islands</t>
+          <t>San Marino</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -16741,17 +18307,17 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>C/L — centre-right/coalitional</t>
+          <t>C/L — centrist</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>R — centre-right/coalitional</t>
+          <t>L/C — centrist</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
+          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
         </is>
       </c>
     </row>
@@ -16763,7 +18329,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>São Tomé and Príncipe</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -16773,12 +18339,12 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>C/L — coalition/centrist</t>
+          <t>C/L — centre-right/centrist</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>L/C — coalition/centrist</t>
+          <t>L/C — centre-right/centrist</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -16795,7 +18361,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -16805,17 +18371,17 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>C/L — centre-right caretaker</t>
+          <t>C/L — nationalist-developmental</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>R — centre-right caretaker</t>
+          <t>L/C — nationalist-developmental</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
+          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
         </is>
       </c>
     </row>
@@ -16827,7 +18393,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Solomon Islands</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -16837,17 +18403,17 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>C/L — consociational centre</t>
+          <t>C/L — centre-right/coalitional</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>L/C — consociational centre</t>
+          <t>R — centre-right/coalitional</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
+          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
         </is>
       </c>
     </row>
@@ -16859,7 +18425,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -16869,12 +18435,12 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>C/L — developmental-centrist</t>
+          <t>C/L — coalition/centrist</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>L/C — developmental-centrist</t>
+          <t>L/C — coalition/centrist</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -16891,7 +18457,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Timor-Leste</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -16901,17 +18467,17 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>C/L — nationalist-developmental</t>
+          <t>C/L — centre-right caretaker</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>L/C — nationalist-developmental</t>
+          <t>R — centre-right caretaker</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
+          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
         </is>
       </c>
     </row>
@@ -16923,7 +18489,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Trinidad and Tobago</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -16933,12 +18499,12 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>C/L — centre-right/centrist</t>
+          <t>C/L — consociational centre</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>L/C — centre-right/centrist</t>
+          <t>L/C — consociational centre</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -16955,7 +18521,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -16965,12 +18531,12 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>C/L — wartime national-centrist</t>
+          <t>C/L — developmental-centrist</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>L/C — wartime national-centrist</t>
+          <t>L/C — developmental-centrist</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -16987,7 +18553,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Timor-Leste</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -16997,12 +18563,12 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>C/L — liberal-centrist</t>
+          <t>C/L — nationalist-developmental</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>L/C — liberal-centrist</t>
+          <t>L/C — nationalist-developmental</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -17014,96 +18580,96 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Naming</t>
+          <t>C/L split</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Congo, Democratic Republic of the</t>
+          <t>Trinidad and Tobago</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Congo, Democratic Republic of the</t>
+          <t>C/L — centre-right/centrist</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>L/C — centre-right/centrist</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Use UN official short name</t>
+          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Naming</t>
+          <t>C/L split</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Congo, Republic of the</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Congo, Republic of the</t>
+          <t>C/L — wartime national-centrist</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Republic of the Congo</t>
+          <t>L/C — wartime national-centrist</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Use UN official short name</t>
+          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Naming</t>
+          <t>C/L split</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>C/L — liberal-centrist</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>L/C — liberal-centrist</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Use UN official short name</t>
+          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
         </is>
       </c>
     </row>
@@ -17115,7 +18681,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Micronesia</t>
+          <t>Congo, Democratic Republic of the</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -17125,12 +18691,12 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Micronesia</t>
+          <t>Congo, Democratic Republic of the</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Federated States of Micronesia</t>
+          <t>Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -17147,27 +18713,27 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Congo, Republic of the</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Head of state / government</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Bongbong Marcos</t>
+          <t>Congo, Republic of the</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Ferdinand "Bongbong" Marcos Jr.</t>
+          <t>Republic of the Congo</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Full formal name</t>
+          <t>Use UN official short name</t>
         </is>
       </c>
     </row>
@@ -17179,27 +18745,27 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Head of state</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Salman</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Salman bin Abdulaziz Al Saud</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Full name for consistency</t>
+          <t>Use UN official short name</t>
         </is>
       </c>
     </row>
@@ -17211,32 +18777,128 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
+          <t>Micronesia</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Micronesia</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Federated States of Micronesia</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Use UN official short name</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Naming</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Head of state / government</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Bongbong Marcos</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Ferdinand "Bongbong" Marcos Jr.</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Full formal name</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Naming</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Head of state</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Salman</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Salman bin Abdulaziz Al Saud</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Full name for consistency</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Naming</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>Turkey</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Turkey</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Türkiye</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Use UN official short name</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F112"/>
+  <autoFilter ref="A1:F115"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Freedenian_Ideologies_Global_Dataset_2026-10-03.xlsx
+++ b/Freedenian_Ideologies_Global_Dataset_2026-10-03.xlsx
@@ -11,13 +11,11 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Methodology" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Sources" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Change log" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'195 States'!$A$1:$O$196</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Methodology'!$A$1:$B$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sources'!$A$1:$C$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Change log'!$A$1:$F$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'195 States'!$A$1:$N$196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Methodology'!$A$1:$B$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sources'!$A$1:$C$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O196"/>
+  <dimension ref="A1:N196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -467,7 +465,6 @@
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="34" customWidth="1" min="13" max="13"/>
     <col width="55" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -541,11 +538,6 @@
           <t>Policy approach / key domains</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Previous code (conservatism-only scheme)</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -602,11 +594,6 @@
           <t>Tradition/religion; sharia; authority/order; restrictive social policy; state-controlled economy; restrictive migration; security-first foreign policy</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>T — traditionalist-authoritarian</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -671,11 +658,6 @@
           <t>EU integration; social-democratic governance; market economy; gradual institutional reform; pragmatic migration policy</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centre-left</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -734,11 +716,6 @@
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>National sovereignty; state role in economy; social conservatism; controlled migration; hydrocarbons; security/state continuity</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>T — nationalist-authoritarian</t>
         </is>
       </c>
     </row>
@@ -801,11 +778,6 @@
           <t>Small-state market economy; institutional continuity; Catholic heritage; open European orientation</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>C/L — liberal-conservative hybrid</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -872,11 +844,6 @@
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>State authority; national development; market reform with state role; social conservatism; energy/resources; security</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>C+/T — nationalist-developmental</t>
         </is>
       </c>
     </row>
@@ -939,11 +906,6 @@
           <t>Social-democratic Caribbean governance; market economy; tourism; moderate social policy</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centre-left</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1006,11 +968,6 @@
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>Radical market liberalisation; individual liberty; deregulation; reduced state; restrictive fiscal policy; socially mixed; strong Western alignment</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>R — libertarian right, not primarily conservative</t>
         </is>
       </c>
     </row>
@@ -1069,11 +1026,6 @@
           <t>Market economy; democratic/institutional reform; secular social policy; security-focused foreign policy</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>L/C — liberal-centrist</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1136,11 +1088,6 @@
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>Mixed economy; welfare state; multicultural migration; climate transition; alliance with US</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>L — centre-left</t>
         </is>
       </c>
     </row>
@@ -1207,11 +1154,6 @@
           <t>Market economy + social partnership; institutional continuity; controlled migration; pragmatic climate policy; EU/NATO-aligned security</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>C — Christian-democratic conservative</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1270,11 +1212,6 @@
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>National sovereignty; executive authority; traditional social order; hydrocarbons; restrictive migration; security-first foreign policy</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>T — authoritarian-nationalist</t>
         </is>
       </c>
     </row>
@@ -1337,11 +1274,6 @@
           <t>Social-democratic Caribbean model; tourism; moderate migration; climate/vulnerability policy</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centre-left</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1406,11 +1338,6 @@
           <t>Dynastic authority; Sunni-Islamic tradition; state-led development; controlled migration; energy diversification; security alignment</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>T — monarchic traditionalist</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1475,11 +1402,6 @@
           <t>National identity; religious/social conservatism; market economy with state role; migration/labour policy; security and sovereignty</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>C+/N — conservative-nationalist hybrid</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1544,11 +1466,6 @@
           <t>Social-democratic welfare; tourism; progressive social policy; climate resilience; multilateral foreign policy</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>L — centre-left</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1613,11 +1530,6 @@
           <t>State authority; social conservatism; state economy; restrictive migration; energy/security dependence; continuity</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>T — authoritarian-traditionalist</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1676,11 +1588,6 @@
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>Market economy; fiscal restraint; institutional order; stricter migration/integration; pragmatic climate/industry; NATO/EU</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>C — national/Christian-democratic conservative</t>
         </is>
       </c>
     </row>
@@ -1743,11 +1650,6 @@
           <t>Mixed economy; social programmes; tourism; moderate migration; climate vulnerability</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centre-left</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1812,11 +1714,6 @@
           <t>State capacity; economic development; market reform; order/security; infrastructure and regional security</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>C+/T — developmental-conservative hybrid</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1883,11 +1780,6 @@
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>Monarchy and cultural continuity; regulated development; environmental stewardship; cautious social change</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>T/C — monarchic-traditionalist</t>
         </is>
       </c>
     </row>
@@ -1950,11 +1842,6 @@
           <t>Market reform; decentralisation; security/order; moderate social conservatism; pragmatic foreign policy</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>R — centre-right liberal</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2025,11 +1912,6 @@
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>Ethno-national and institutional interests; mixed economy; EU integration; migration/security; plural social positions</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>L/C — fragmented coalition</t>
         </is>
       </c>
     </row>
@@ -2092,11 +1974,6 @@
           <t>Social programmes; market economy; institutional democracy; mining; regional diplomacy</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centre-left</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2165,11 +2042,6 @@
           <t>Social welfare; developmental state; progressive social policy; environmental protection; multilateral diplomacy</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>L — left</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2234,11 +2106,6 @@
           <t>Absolute monarchy; Malay-Islamic tradition; state/energy economy; restrictive social policy; controlled migration</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>T — dynastic-religious traditionalist</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2299,11 +2166,6 @@
           <t>National sovereignty; security; mixed economy; EU orientation; more restrictive migration; pragmatic energy policy</t>
         </is>
       </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>C+/L — mixed centre-right/national</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2364,11 +2226,6 @@
           <t>National sovereignty; military authority; state-led development; traditional social order; restrictive external migration; anti-colonial foreign policy</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>T — military-nationalist</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2431,11 +2288,6 @@
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>Executive authority; national unity; state-led development; socially conservative; security-first</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>T/C — nationalist-authoritarian hybrid</t>
         </is>
       </c>
     </row>
@@ -2498,11 +2350,6 @@
           <t>Democratic institutions; tourism/services; social policy; climate resilience; EU/Atlantic orientation</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centre-left/centrist</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2569,11 +2416,6 @@
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>Monarchy/continuity; authority; state-led development; socially conservative; controlled migration; China/ASEAN balancing</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>T/C — conservative-developmental</t>
         </is>
       </c>
     </row>
@@ -2632,11 +2474,6 @@
           <t>Executive continuity; state authority; traditional social order; resource economy; security</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>T — authoritarian-traditionalist</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2699,11 +2536,6 @@
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>Market economy + welfare; multicultural migration; climate/industrial policy; Atlantic/NATO orientation</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>L/C — liberal-centrist</t>
         </is>
       </c>
     </row>
@@ -2762,11 +2594,6 @@
           <t>Executive authority; state-led development; security; resource extraction; sovereignty</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>T — authoritarian-developmental</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2827,11 +2654,6 @@
           <t>Authority/order; security; state-led development; traditional social order; regional security</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>T — military-nationalist</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2900,11 +2722,6 @@
           <t>Traditional family/social order; law and order; private property/market economy; restrictive migration; energy pragmatism; security-oriented foreign policy</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>C — national-conservative</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2969,11 +2786,6 @@
           <t>Party authority; national continuity; state capitalism; social discipline; controlled migration; strategic autonomy</t>
         </is>
       </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>T/R — communist-nationalist, not conservative in Freedenian sense</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3034,11 +2846,6 @@
           <t>Security/order; market economy; traditional social values; restrictive migration; resource/energy development; strong US/security ties</t>
         </is>
       </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>C+ — national-conservative</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3107,11 +2914,6 @@
           <t>Executive authority; Islamic social order; state-led development; security; regional diplomacy</t>
         </is>
       </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>T/C — presidential traditionalist</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3176,11 +2978,6 @@
           <t>Security/order; market economy; fiscal reform; socially mixed; migration control; climate policy retained</t>
         </is>
       </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>C+ — populist/centre-right hybrid</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3241,11 +3038,6 @@
           <t>Market investment; infrastructure; state capacity; security; regional diplomacy</t>
         </is>
       </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>R — developmental centre-right</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3306,11 +3098,6 @@
           <t>EU/NATO; market + social state; national identity; controlled migration; energy pragmatism; security</t>
         </is>
       </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>C — Christian-democratic/national conservative</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3369,11 +3156,6 @@
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>One-party authority; state economy; socialist social policy; controlled migration; security/sovereignty</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>L/T — communist authoritarian</t>
         </is>
       </c>
     </row>
@@ -3440,11 +3222,6 @@
           <t>Market economy; moderate social policy; EU orientation; controlled migration; energy/security in Eastern Mediterranean</t>
         </is>
       </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>C/L — centrist conservative-liberal</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3505,11 +3282,6 @@
           <t>Market economy with domestic spending; national sovereignty; migration restriction; climate-policy scepticism; NATO but less Ukraine activism</t>
         </is>
       </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>C+ — populist-conservative hybrid</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3574,11 +3346,6 @@
           <t>State capacity; resource development; social programmes; security; regional diplomacy</t>
         </is>
       </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centrist-developmental</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3641,11 +3408,6 @@
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>Welfare state; restrictive migration; strong institutions; climate transition; NATO/security</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>L/C — social-democratic with restrictive migration</t>
         </is>
       </c>
     </row>
@@ -3704,11 +3466,6 @@
           <t>Executive authority; strategic infrastructure; state security; traditional social order; military/diplomatic balancing</t>
         </is>
       </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>T — authoritarian-developmental</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3769,11 +3526,6 @@
           <t>Public investment; social programmes; climate resilience; tourism; regional diplomacy</t>
         </is>
       </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centre-left</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3836,11 +3588,6 @@
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>Market economy; private investment; migration control; moderate social conservatism; tourism/energy</t>
-        </is>
-      </c>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t>R — moderate centre-right</t>
         </is>
       </c>
     </row>
@@ -3903,11 +3650,6 @@
           <t>Security/order; market economy; fiscal reform; restrictive migration; energy/resource development</t>
         </is>
       </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>R/C — security-oriented centre-right</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3972,11 +3714,6 @@
           <t>Executive authority; traditional social order; state/development projects; controlled migration; energy; regional security</t>
         </is>
       </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>T — authoritarian-nationalist</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -4035,11 +3772,6 @@
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>Public order/security; strong executive; pro-business with state intervention; socially conservative rhetoric; migration/security</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>C+ — authoritarian-populist hybrid</t>
         </is>
       </c>
     </row>
@@ -4098,11 +3830,6 @@
           <t>Executive continuity; oil/state economy; social traditionalism; controlled migration; security</t>
         </is>
       </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>T — authoritarian-traditionalist</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -4165,11 +3892,6 @@
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>National sovereignty; state control; social discipline; restricted migration; militarised security</t>
-        </is>
-      </c>
-      <c r="O55" s="2" t="inlineStr">
-        <is>
-          <t>T — authoritarian-nationalist</t>
         </is>
       </c>
     </row>
@@ -4232,11 +3954,6 @@
           <t>Market economy; national security; restrictive migration/integration; digital state; strong NATO/EU orientation</t>
         </is>
       </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>C/L — liberal-conservative</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4293,11 +4010,6 @@
           <t>Monarchical authority; customary tradition; state-led development; socially conservative; controlled migration</t>
         </is>
       </c>
-      <c r="O57" s="2" t="inlineStr">
-        <is>
-          <t>T — monarchic traditionalist</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4366,11 +4078,6 @@
           <t>State capacity; developmentalism; mixed economy; traditional social order; security; regional diplomacy</t>
         </is>
       </c>
-      <c r="O58" s="2" t="inlineStr">
-        <is>
-          <t>C+/T — developmental-authoritarian hybrid</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4429,11 +4136,6 @@
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>Climate adaptation; public services; US security compact; migration/mobility</t>
-        </is>
-      </c>
-      <c r="O59" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centrist</t>
         </is>
       </c>
     </row>
@@ -4500,11 +4202,6 @@
           <t>Market/tourism economy; customary institutions; moderate social conservatism; climate vulnerability; regional security</t>
         </is>
       </c>
-      <c r="O60" s="2" t="inlineStr">
-        <is>
-          <t>C/L — conservative-liberal hybrid</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4563,11 +4260,6 @@
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>Market economy; fiscal discipline; institutional continuity; restrictive migration; nuclear/climate pragmatism; strong NATO</t>
-        </is>
-      </c>
-      <c r="O61" s="2" t="inlineStr">
-        <is>
-          <t>C — liberal/Christian-democratic conservative</t>
         </is>
       </c>
     </row>
@@ -4630,11 +4322,6 @@
           <t>State capacity; market reform; secular republicanism; controlled migration; nuclear/energy transition; European strategic autonomy</t>
         </is>
       </c>
-      <c r="O62" s="2" t="inlineStr">
-        <is>
-          <t>L/C — liberal-centrist, not primarily conservative</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4697,11 +4384,6 @@
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>Military authority; national resources; state-led development; social traditionalism; security</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr">
-        <is>
-          <t>T — military-developmental</t>
         </is>
       </c>
     </row>
@@ -4764,11 +4446,6 @@
           <t>Market/tourism; democratic institutions; moderate social policy; migration and regional diplomacy</t>
         </is>
       </c>
-      <c r="O64" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centrist</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4831,11 +4508,6 @@
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>National sovereignty; Orthodox cultural tradition; authority/order; restrictive NGO/foreign influence policy; migration/security; cautious EU orientation</t>
-        </is>
-      </c>
-      <c r="O65" s="2" t="inlineStr">
-        <is>
-          <t>C+ — national/traditionalist</t>
         </is>
       </c>
     </row>
@@ -4898,11 +4570,6 @@
           <t>Social market; fiscal discipline; property/private enterprise; controlled migration; industrial climate transition; strong EU/NATO</t>
         </is>
       </c>
-      <c r="O66" s="2" t="inlineStr">
-        <is>
-          <t>C — Christian-democratic conservative</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4965,11 +4632,6 @@
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>Social/developmental state; market economy; democratic institutions; regional diplomacy</t>
-        </is>
-      </c>
-      <c r="O67" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centre-left</t>
         </is>
       </c>
     </row>
@@ -5032,11 +4694,6 @@
           <t>Market reform; institutional continuity; controlled migration; family/social conservatism; renewables + energy security; NATO/EU</t>
         </is>
       </c>
-      <c r="O68" s="2" t="inlineStr">
-        <is>
-          <t>C — liberal-conservative</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -5095,11 +4752,6 @@
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>Social programmes; tourism; climate resilience; regional diplomacy</t>
-        </is>
-      </c>
-      <c r="O69" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centre-left</t>
         </is>
       </c>
     </row>
@@ -5162,11 +4814,6 @@
           <t>Anti-corruption/institutional reform; market economy; moderate social policy; migration/development</t>
         </is>
       </c>
-      <c r="O70" s="2" t="inlineStr">
-        <is>
-          <t>L/C — liberal-centrist</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -5225,11 +4872,6 @@
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>Military authority; national resources; state capacity; traditional social order; security</t>
-        </is>
-      </c>
-      <c r="O71" s="2" t="inlineStr">
-        <is>
-          <t>T — military-nationalist</t>
         </is>
       </c>
     </row>
@@ -5292,11 +4934,6 @@
           <t>Order/security; state continuity; resource/tactical governance</t>
         </is>
       </c>
-      <c r="O72" s="2" t="inlineStr">
-        <is>
-          <t>T — military/transitional</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -5363,11 +5000,6 @@
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>Resource-led development; infrastructure; market economy; social programmes; security/foreign investment</t>
-        </is>
-      </c>
-      <c r="O73" s="2" t="inlineStr">
-        <is>
-          <t>L/C — developmental-centrist</t>
         </is>
       </c>
     </row>
@@ -5426,11 +5058,6 @@
           <t>Security/order; institutional rebuilding; humanitarian governance; migration/displacement</t>
         </is>
       </c>
-      <c r="O74" s="2" t="inlineStr">
-        <is>
-          <t>T/L — transitional security government</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -5497,11 +5124,6 @@
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>Security/order; private investment; traditional social values; restrictive migration; market economy</t>
-        </is>
-      </c>
-      <c r="O75" s="2" t="inlineStr">
-        <is>
-          <t>C — national-conservative</t>
         </is>
       </c>
     </row>
@@ -5564,11 +5186,6 @@
           <t>EU-oriented centre-right; market economy; institutional repair; controlled migration; moderate social conservatism; security</t>
         </is>
       </c>
-      <c r="O76" s="2" t="inlineStr">
-        <is>
-          <t>C — centre-right conservative, post-Orbán</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -5633,11 +5250,6 @@
           <t>Welfare state; market economy; climate/energy; moderate migration; Nordic institutions</t>
         </is>
       </c>
-      <c r="O77" s="2" t="inlineStr">
-        <is>
-          <t>L/C — social-democratic</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -5702,11 +5314,6 @@
           <t>Hindu cultural/national identity; strong executive; mixed market/state development; restrictive citizenship/migration; energy pragmatism; strategic autonomy</t>
         </is>
       </c>
-      <c r="O78" s="2" t="inlineStr">
-        <is>
-          <t>C+ — national-cultural conservative</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -5775,11 +5382,6 @@
           <t>National unity; authority; state-led industrial policy; social/family conservatism; migration controlled; resource/energy development; strategic autonomy</t>
         </is>
       </c>
-      <c r="O79" s="2" t="inlineStr">
-        <is>
-          <t>C+ — nationalist-developmental</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -5844,11 +5446,6 @@
           <t>Islamic order; clerical authority; state-led economy; restrictive social policy; controlled migration; security/sovereignty</t>
         </is>
       </c>
-      <c r="O80" s="2" t="inlineStr">
-        <is>
-          <t>T — religious-authoritarian</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -5907,11 +5504,6 @@
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>Religious/social tradition; authority; state/resources; security; migration/displacement; regional balancing</t>
-        </is>
-      </c>
-      <c r="O81" s="2" t="inlineStr">
-        <is>
-          <t>C+/T — religious-national coalition</t>
         </is>
       </c>
     </row>
@@ -5974,11 +5566,6 @@
           <t>Market economy + welfare; relatively liberal social policy; migration/integration; climate transition; EU/Atlantic orientation</t>
         </is>
       </c>
-      <c r="O82" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centrist</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -6047,11 +5634,6 @@
           <t>Jewish national identity; security/order; market economy; socially conservative coalition; restrictive migration; defence-first foreign policy</t>
         </is>
       </c>
-      <c r="O83" s="2" t="inlineStr">
-        <is>
-          <t>C+ — national-conservative</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -6114,11 +5696,6 @@
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>Traditional family/cultural identity; market + strategic state; restrictive migration; energy pragmatism; strong NATO/EU with sovereignty emphasis</t>
-        </is>
-      </c>
-      <c r="O84" s="2" t="inlineStr">
-        <is>
-          <t>C+ — national-conservative</t>
         </is>
       </c>
     </row>
@@ -6181,11 +5758,6 @@
           <t>Private enterprise; law/order; moderate social conservatism; controlled migration; tourism/energy</t>
         </is>
       </c>
-      <c r="O85" s="2" t="inlineStr">
-        <is>
-          <t>C/L — centre-right conservative</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -6246,11 +5818,6 @@
           <t>Traditional institutions/family; national identity; market economy + fiscal stimulus; stronger defence; energy/nuclear pragmatism</t>
         </is>
       </c>
-      <c r="O86" s="2" t="inlineStr">
-        <is>
-          <t>C+ — national-conservative</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -6315,11 +5882,6 @@
           <t>Monarchical authority; Islamic/tribal tradition; state-led economy; controlled migration/refugees; security diplomacy</t>
         </is>
       </c>
-      <c r="O87" s="2" t="inlineStr">
-        <is>
-          <t>T — monarchic traditionalist</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -6384,11 +5946,6 @@
           <t>Executive order; national identity; state/resource economy; controlled migration; energy development; multi-vector diplomacy</t>
         </is>
       </c>
-      <c r="O88" s="2" t="inlineStr">
-        <is>
-          <t>T — authoritarian-developmental</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -6461,11 +6018,6 @@
           <t>Religious/family values; market reform; security/order; migration management; development/energy; regional diplomacy</t>
         </is>
       </c>
-      <c r="O89" s="2" t="inlineStr">
-        <is>
-          <t>C+ — social/religious conservative + market-oriented</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -6526,11 +6078,6 @@
           <t>Community/tradition; public development; climate adaptation; migration/mobility; regional diplomacy</t>
         </is>
       </c>
-      <c r="O90" s="2" t="inlineStr">
-        <is>
-          <t>L/C — developmental-centrist</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -6595,11 +6142,6 @@
           <t>Dynastic authority; Islamic tradition; oil/state economy; controlled migration; energy; Gulf security</t>
         </is>
       </c>
-      <c r="O91" s="2" t="inlineStr">
-        <is>
-          <t>T — monarchic traditionalist</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -6662,11 +6204,6 @@
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>Executive authority; national identity; state intervention; social conservatism; migration/security; regional balancing</t>
-        </is>
-      </c>
-      <c r="O92" s="2" t="inlineStr">
-        <is>
-          <t>C+/T — nationalist-authoritarian hybrid</t>
         </is>
       </c>
     </row>
@@ -6725,11 +6262,6 @@
           <t>Party authority; state economy; social discipline; controlled migration; hydropower/resources; regional balancing</t>
         </is>
       </c>
-      <c r="O93" s="2" t="inlineStr">
-        <is>
-          <t>T/L — communist-authoritarian</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -6790,11 +6322,6 @@
           <t>Market economy; national security; controlled migration; energy diversification; NATO/EU</t>
         </is>
       </c>
-      <c r="O94" s="2" t="inlineStr">
-        <is>
-          <t>R — centre-right liberal</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -6855,11 +6382,6 @@
           <t>Sectarian balance; market/private economy; institutional reconstruction; refugee/migration pressures; regional security</t>
         </is>
       </c>
-      <c r="O95" s="2" t="inlineStr">
-        <is>
-          <t>L/C — institutional/coalitional</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -6918,11 +6440,6 @@
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>Market investment; customary institutions; social programmes; migration/labour; regional diplomacy</t>
-        </is>
-      </c>
-      <c r="O96" s="2" t="inlineStr">
-        <is>
-          <t>R — centre-right developmental</t>
         </is>
       </c>
     </row>
@@ -6981,11 +6498,6 @@
           <t>Institutional reform; market economy; development; moderate social policy; regional diplomacy</t>
         </is>
       </c>
-      <c r="O97" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centrist</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -7046,11 +6558,6 @@
           <t>State reconstruction; competing authorities; market/resource economy; migration/security; regional balancing</t>
         </is>
       </c>
-      <c r="O98" s="2" t="inlineStr">
-        <is>
-          <t>L/C — fragmented transitional</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -7111,11 +6618,6 @@
           <t>Property/private enterprise; constitutional monarchy; low-tax economy; institutional continuity; European cooperation</t>
         </is>
       </c>
-      <c r="O99" s="2" t="inlineStr">
-        <is>
-          <t>C — liberal-conservative</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -7178,11 +6680,6 @@
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>Market economy; national security; migration control/integration; energy independence; NATO/EU</t>
-        </is>
-      </c>
-      <c r="O100" s="2" t="inlineStr">
-        <is>
-          <t>R — centre-right security-oriented</t>
         </is>
       </c>
     </row>
@@ -7245,11 +6742,6 @@
           <t>Market/finance; fiscal prudence; institutional continuity; moderate social policy; EU integration</t>
         </is>
       </c>
-      <c r="O101" s="2" t="inlineStr">
-        <is>
-          <t>C — Christian-democratic conservative</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -7306,11 +6798,6 @@
           <t>Order; state capacity; development; resource economy; security</t>
         </is>
       </c>
-      <c r="O102" s="2" t="inlineStr">
-        <is>
-          <t>T — military-transitional</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -7375,11 +6862,6 @@
           <t>Market economy; institutional continuity; moderate social conservatism; development/agriculture</t>
         </is>
       </c>
-      <c r="O103" s="2" t="inlineStr">
-        <is>
-          <t>R — centre-right</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -7448,11 +6930,6 @@
           <t>Market economy + state development; Islamic institutional context; moderate social policy; controlled migration; ASEAN balancing</t>
         </is>
       </c>
-      <c r="O104" s="2" t="inlineStr">
-        <is>
-          <t>L/C — coalition/centrist</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -7521,11 +6998,6 @@
           <t>Islamic social order; national sovereignty; infrastructure/state role; controlled migration; maritime security; India-China balancing</t>
         </is>
       </c>
-      <c r="O105" s="2" t="inlineStr">
-        <is>
-          <t>C+ — national/religious conservative</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -7584,11 +7056,6 @@
       <c r="N106" s="2" t="inlineStr">
         <is>
           <t>Military authority; sovereignty; state-led development; traditional social order; security; anti-Western foreign policy</t>
-        </is>
-      </c>
-      <c r="O106" s="2" t="inlineStr">
-        <is>
-          <t>T — military-nationalist</t>
         </is>
       </c>
     </row>
@@ -7655,11 +7122,6 @@
           <t>Welfare/social policy; market/tourism; relatively liberal social policy; migration management; EU orientation</t>
         </is>
       </c>
-      <c r="O107" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centre-left</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -7720,11 +7182,6 @@
           <t>Climate survival/adaptation; aid; US security ties; small-state governance</t>
         </is>
       </c>
-      <c r="O108" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centrist</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -7787,11 +7244,6 @@
       <c r="N109" s="2" t="inlineStr">
         <is>
           <t>Islamic tradition; executive authority; market/resource development; controlled migration; regional security</t>
-        </is>
-      </c>
-      <c r="O109" s="2" t="inlineStr">
-        <is>
-          <t>T/C — Islamic-national developmental</t>
         </is>
       </c>
     </row>
@@ -7858,11 +7310,6 @@
           <t>Welfare; diversified market economy; social pluralism; climate/vulnerability; regional diplomacy</t>
         </is>
       </c>
-      <c r="O110" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centre-left</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -7929,11 +7376,6 @@
       <c r="N111" s="2" t="inlineStr">
         <is>
           <t>State-led development; welfare; progressive social policy; migration diplomacy; energy sovereignty; regional/US balancing</t>
-        </is>
-      </c>
-      <c r="O111" s="2" t="inlineStr">
-        <is>
-          <t>L — left/national-developmental</t>
         </is>
       </c>
     </row>
@@ -7996,11 +7438,6 @@
           <t>European integration; market reform; institutional strengthening; controlled migration; energy independence; security</t>
         </is>
       </c>
-      <c r="O112" s="2" t="inlineStr">
-        <is>
-          <t>L/C — liberal-centrist</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -8057,11 +7494,6 @@
           <t>Monarchical continuity; property/private wealth; regulated social order; low-tax/service economy; cautious reform</t>
         </is>
       </c>
-      <c r="O113" s="2" t="inlineStr">
-        <is>
-          <t>C — monarchical conservative</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -8124,11 +7556,6 @@
       <c r="N114" s="2" t="inlineStr">
         <is>
           <t>National resources; state development; traditional culture; market economy; strategic balancing</t>
-        </is>
-      </c>
-      <c r="O114" s="2" t="inlineStr">
-        <is>
-          <t>C+/L — nationalist-developmental</t>
         </is>
       </c>
     </row>
@@ -8195,11 +7622,6 @@
           <t>Market reform; EU accession; moderate social conservatism; controlled migration; NATO/security</t>
         </is>
       </c>
-      <c r="O115" s="2" t="inlineStr">
-        <is>
-          <t>C/L — liberal-conservative</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -8264,11 +7686,6 @@
           <t>Monarchical/religious authority; market development; controlled migration; traditional social order with modernisation; energy/infrastructure</t>
         </is>
       </c>
-      <c r="O116" s="2" t="inlineStr">
-        <is>
-          <t>T/C — monarchic-developmental</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -8337,11 +7754,6 @@
           <t>State authority; resource development; traditional social order; security; foreign investment</t>
         </is>
       </c>
-      <c r="O117" s="2" t="inlineStr">
-        <is>
-          <t>C/T — nationalist-developmental</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -8410,11 +7822,6 @@
           <t>Military authority; Buddhist-national identity; state control; restrictive migration; security</t>
         </is>
       </c>
-      <c r="O118" s="2" t="inlineStr">
-        <is>
-          <t>T — military-authoritarian</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -8477,11 +7884,6 @@
       <c r="N119" s="2" t="inlineStr">
         <is>
           <t>Social/developmental state; resource management; moderate social policy; regional diplomacy</t>
-        </is>
-      </c>
-      <c r="O119" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centre-left nationalist</t>
         </is>
       </c>
     </row>
@@ -8544,11 +7946,6 @@
           <t>Small-state governance; resource/aid economy; traditional social order; migration/climate vulnerability</t>
         </is>
       </c>
-      <c r="O120" s="2" t="inlineStr">
-        <is>
-          <t>C/L — conservative-centrist</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -8607,11 +8004,6 @@
       <c r="N121" s="2" t="inlineStr">
         <is>
           <t>Anti-corruption/state reform; mixed economy; traditional social context; migration/labour; regional balancing</t>
-        </is>
-      </c>
-      <c r="O121" s="2" t="inlineStr">
-        <is>
-          <t>L/C — populist-centrist</t>
         </is>
       </c>
     </row>
@@ -8674,11 +8066,6 @@
           <t>Market/welfare mix; relatively liberal social policy; migration/integration; climate transition; EU/NATO</t>
         </is>
       </c>
-      <c r="O122" s="2" t="inlineStr">
-        <is>
-          <t>L/C — liberal-centrist</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -8739,11 +8126,6 @@
           <t>Market reform; deregulation; property/private enterprise; moderate social conservatism; migration controls; energy/resource pragmatism</t>
         </is>
       </c>
-      <c r="O123" s="2" t="inlineStr">
-        <is>
-          <t>C — liberal-conservative</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -8804,11 +8186,6 @@
           <t>Executive/family authority; state intervention; social conservatism; restrictive migration; security/sovereignty</t>
         </is>
       </c>
-      <c r="O124" s="2" t="inlineStr">
-        <is>
-          <t>T — authoritarian-nationalist</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -8869,11 +8246,6 @@
           <t>Military authority; sovereignty; state/resources; traditional social order; security</t>
         </is>
       </c>
-      <c r="O125" s="2" t="inlineStr">
-        <is>
-          <t>T — military-nationalist</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -8942,11 +8314,6 @@
           <t>Religious/family values; market reform; security/order; migration management; oil/energy; regional leadership</t>
         </is>
       </c>
-      <c r="O126" s="2" t="inlineStr">
-        <is>
-          <t>C+ — socially conservative, market-oriented</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -9007,11 +8374,6 @@
           <t>State/party authority; hereditary leadership; controlled economy; social discipline; restricted migration; military security</t>
         </is>
       </c>
-      <c r="O127" s="2" t="inlineStr">
-        <is>
-          <t>T/L — totalitarian-nationalist</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -9076,11 +8438,6 @@
           <t>National identity; traditional social values; market economy; migration control; energy pragmatism; NATO/EU</t>
         </is>
       </c>
-      <c r="O128" s="2" t="inlineStr">
-        <is>
-          <t>C+ — national-conservative</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -9141,11 +8498,6 @@
           <t>Welfare state; regulated market; climate/energy balancing; moderate migration; NATO</t>
         </is>
       </c>
-      <c r="O129" s="2" t="inlineStr">
-        <is>
-          <t>L/C — social-democratic</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -9210,11 +8562,6 @@
           <t>Sultanate; Islamic tradition; state-led development; controlled migration; energy diversification; regional balancing</t>
         </is>
       </c>
-      <c r="O130" s="2" t="inlineStr">
-        <is>
-          <t>T — monarchic traditionalist</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -9279,11 +8626,6 @@
           <t>Islamic social values; strong state/security; mixed economy; controlled migration; energy/resources; regional balancing</t>
         </is>
       </c>
-      <c r="O131" s="2" t="inlineStr">
-        <is>
-          <t>C+/T — religious-national hybrid</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -9344,11 +8686,6 @@
           <t>Market/tourism; climate; US security alignment; migration/mobility</t>
         </is>
       </c>
-      <c r="O132" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centrist</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -9411,11 +8748,6 @@
       <c r="N133" s="2" t="inlineStr">
         <is>
           <t>National liberation; institutional state-building; social conservatism; refugee/mobility policy; security diplomacy</t>
-        </is>
-      </c>
-      <c r="O133" s="2" t="inlineStr">
-        <is>
-          <t>L/C — nationalist-centrist</t>
         </is>
       </c>
     </row>
@@ -9478,11 +8810,6 @@
           <t>Market economy; security/order; migration control; canal/logistics; pragmatic foreign policy</t>
         </is>
       </c>
-      <c r="O134" s="2" t="inlineStr">
-        <is>
-          <t>R — centre-right</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -9543,11 +8870,6 @@
           <t>Resource development; customary/community authority; market + state role; migration; regional security</t>
         </is>
       </c>
-      <c r="O135" s="2" t="inlineStr">
-        <is>
-          <t>L/C — developmental-centrist</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -9608,11 +8930,6 @@
           <t>Private property/market; traditional social values; controlled migration; agriculture/energy; sovereignty-oriented diplomacy</t>
         </is>
       </c>
-      <c r="O136" s="2" t="inlineStr">
-        <is>
-          <t>C — Christian-democratic/national conservative</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -9677,11 +8994,6 @@
           <t>Security/order; market economy; traditional social values; migration control; private investment; strong US ties</t>
         </is>
       </c>
-      <c r="O137" s="2" t="inlineStr">
-        <is>
-          <t>C+ — conservative-populist</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -9742,11 +9054,6 @@
           <t>National identity; security/order; market + state development; traditional social policy; migration; US/China balancing</t>
         </is>
       </c>
-      <c r="O138" s="2" t="inlineStr">
-        <is>
-          <t>C+ — nationalist-conservative hybrid</t>
-        </is>
-      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -9809,11 +9116,6 @@
       <c r="N139" s="2" t="inlineStr">
         <is>
           <t>Conservative-national presidential office; liberal-centrist government; market economy; migration/security; strong NATO/EU security</t>
-        </is>
-      </c>
-      <c r="O139" s="2" t="inlineStr">
-        <is>
-          <t>L/C — split executive</t>
         </is>
       </c>
     </row>
@@ -9876,11 +9178,6 @@
           <t>Market economy; fiscal reform; moderate social policy; migration controls; EU/NATO</t>
         </is>
       </c>
-      <c r="O140" s="2" t="inlineStr">
-        <is>
-          <t>C — moderate centre-right</t>
-        </is>
-      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -9943,11 +9240,6 @@
       <c r="N141" s="2" t="inlineStr">
         <is>
           <t>Dynastic authority; Islamic tradition; state/energy economy; controlled migration; LNG; regional mediation/security</t>
-        </is>
-      </c>
-      <c r="O141" s="2" t="inlineStr">
-        <is>
-          <t>T — dynastic-religious traditionalist</t>
         </is>
       </c>
     </row>
@@ -10010,11 +9302,6 @@
           <t>Executive authority; state/resources; social traditionalism; security; continuity</t>
         </is>
       </c>
-      <c r="O142" s="2" t="inlineStr">
-        <is>
-          <t>T — authoritarian-nationalist</t>
-        </is>
-      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -10071,11 +9358,6 @@
           <t>Institutional reform; market economy; EU/NATO; migration/security; energy and fiscal reform</t>
         </is>
       </c>
-      <c r="O143" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centrist caretaker</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -10140,11 +9422,6 @@
           <t>Traditionalism; Orthodox-cultural identity; strong state/authority; strategic sectors; restrictive migration; military/security and sovereignty</t>
         </is>
       </c>
-      <c r="O144" s="2" t="inlineStr">
-        <is>
-          <t>T/C+ — authoritarian national-conservative</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -10207,11 +9484,6 @@
       <c r="N145" s="2" t="inlineStr">
         <is>
           <t>Order/discipline; developmental state; national unity; controlled migration; security; regional diplomacy</t>
-        </is>
-      </c>
-      <c r="O145" s="2" t="inlineStr">
-        <is>
-          <t>T/C — authoritarian-developmental</t>
         </is>
       </c>
     </row>
@@ -10270,11 +9542,6 @@
           <t>Tourism; social programmes; climate resilience; regional diplomacy</t>
         </is>
       </c>
-      <c r="O146" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centre-left</t>
-        </is>
-      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -10331,11 +9598,6 @@
           <t>Social programmes; tourism; climate resilience; regional diplomacy</t>
         </is>
       </c>
-      <c r="O147" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centre-left</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -10396,11 +9658,6 @@
           <t>Market economy; private enterprise; moderate social conservatism; tourism/climate; regional diplomacy</t>
         </is>
       </c>
-      <c r="O148" s="2" t="inlineStr">
-        <is>
-          <t>R — centre-right</t>
-        </is>
-      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -10463,11 +9720,6 @@
       <c r="N149" s="2" t="inlineStr">
         <is>
           <t>Customary authority; community tradition; development; climate; regional diplomacy</t>
-        </is>
-      </c>
-      <c r="O149" s="2" t="inlineStr">
-        <is>
-          <t>L/C — customary/centrist</t>
         </is>
       </c>
     </row>
@@ -10530,11 +9782,6 @@
           <t>Institutional continuity; small-state market economy; European integration</t>
         </is>
       </c>
-      <c r="O150" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centrist</t>
-        </is>
-      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -10595,11 +9842,6 @@
           <t>Market/tourism; development; moderate social policy; regional diplomacy</t>
         </is>
       </c>
-      <c r="O151" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centre-right/centrist</t>
-        </is>
-      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -10664,11 +9906,6 @@
           <t>Dynastic authority; Islamic tradition; state-led diversification; controlled migration; oil/energy; strategic balancing</t>
         </is>
       </c>
-      <c r="O152" s="2" t="inlineStr">
-        <is>
-          <t>T — monarchic-religious traditionalist + developmental modernisation</t>
-        </is>
-      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -10729,11 +9966,6 @@
           <t>National sovereignty; social/developmental state; traditional social context; migration; regional diplomacy</t>
         </is>
       </c>
-      <c r="O153" s="2" t="inlineStr">
-        <is>
-          <t>L/C — nationalist-developmental</t>
-        </is>
-      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -10792,11 +10024,6 @@
       <c r="N154" s="2" t="inlineStr">
         <is>
           <t>National identity; authority/order; market economy; migration control; energy/resource policy; strategic balancing</t>
-        </is>
-      </c>
-      <c r="O154" s="2" t="inlineStr">
-        <is>
-          <t>C+ — national-conservative</t>
         </is>
       </c>
     </row>
@@ -10859,11 +10086,6 @@
           <t>Tourism; social policy; climate/ocean governance; moderate migration</t>
         </is>
       </c>
-      <c r="O155" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centre-left/centrist</t>
-        </is>
-      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -10928,11 +10150,6 @@
           <t>Development; social policy; democratic institutions; climate; regional diplomacy</t>
         </is>
       </c>
-      <c r="O156" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centre-left</t>
-        </is>
-      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -10997,11 +10214,6 @@
           <t>Order/institutions; meritocracy; market economy + state intervention; controlled migration; pragmatic climate; strategic trade/security</t>
         </is>
       </c>
-      <c r="O157" s="2" t="inlineStr">
-        <is>
-          <t>C/L — communitarian/technocratic conservative hybrid</t>
-        </is>
-      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -11066,11 +10278,6 @@
           <t>Traditional social values; strong state; migration restriction; climate/regulatory scepticism; sovereignty; less support for Ukraine</t>
         </is>
       </c>
-      <c r="O158" s="2" t="inlineStr">
-        <is>
-          <t>C+ — nationalist/social conservative</t>
-        </is>
-      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -11129,11 +10336,6 @@
       <c r="N159" s="2" t="inlineStr">
         <is>
           <t>Market/private enterprise; national identity; traditional social values; migration control; NATO/EU</t>
-        </is>
-      </c>
-      <c r="O159" s="2" t="inlineStr">
-        <is>
-          <t>C+ — national-conservative</t>
         </is>
       </c>
     </row>
@@ -11192,11 +10394,6 @@
           <t>Customary/community authority; development; resource/tourism economy; climate; security partnerships</t>
         </is>
       </c>
-      <c r="O160" s="2" t="inlineStr">
-        <is>
-          <t>R — centre-right/coalitional</t>
-        </is>
-      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -11263,11 +10460,6 @@
       <c r="N161" s="2" t="inlineStr">
         <is>
           <t>Islamic social order; state authority; security; migration/displacement; regional diplomacy</t>
-        </is>
-      </c>
-      <c r="O161" s="2" t="inlineStr">
-        <is>
-          <t>C/T — religious-national/state-building</t>
         </is>
       </c>
     </row>
@@ -11330,11 +10522,6 @@
           <t>Mixed economy; social state; constitutional institutions; migration; energy reform; regional diplomacy</t>
         </is>
       </c>
-      <c r="O162" s="2" t="inlineStr">
-        <is>
-          <t>L/C — coalition/centrist</t>
-        </is>
-      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -11395,11 +10582,6 @@
           <t>Industrial policy; welfare; liberal social policy; controlled migration; energy transition; alliance with US</t>
         </is>
       </c>
-      <c r="O163" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centre-left</t>
-        </is>
-      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -11456,11 +10638,6 @@
           <t>Executive authority; oil/state economy; traditional social order; security; migration/displacement</t>
         </is>
       </c>
-      <c r="O164" s="2" t="inlineStr">
-        <is>
-          <t>T — authoritarian-patrimonial</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -11521,11 +10698,6 @@
           <t>Welfare/social state; progressive social policy; managed migration; climate transition; EU/NATO</t>
         </is>
       </c>
-      <c r="O165" s="2" t="inlineStr">
-        <is>
-          <t>L — centre-left</t>
-        </is>
-      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -11584,11 +10756,6 @@
       <c r="N166" s="2" t="inlineStr">
         <is>
           <t>State reform; mixed economy; social welfare; national sovereignty; migration/debt; regional balancing</t>
-        </is>
-      </c>
-      <c r="O166" s="2" t="inlineStr">
-        <is>
-          <t>L/C — left-national developmental</t>
         </is>
       </c>
     </row>
@@ -11647,11 +10814,6 @@
           <t>Military authority; security; state continuity; traditional social order; displacement/migration</t>
         </is>
       </c>
-      <c r="O167" s="2" t="inlineStr">
-        <is>
-          <t>T — military-transitional</t>
-        </is>
-      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -11712,11 +10874,6 @@
           <t>Social/developmental state; resource management; moderate social policy; regional diplomacy</t>
         </is>
       </c>
-      <c r="O168" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centre-left</t>
-        </is>
-      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -11779,11 +10936,6 @@
       <c r="N169" s="2" t="inlineStr">
         <is>
           <t>Market/welfare mix; restrictive migration; law/order; climate transition; NATO/security</t>
-        </is>
-      </c>
-      <c r="O169" s="2" t="inlineStr">
-        <is>
-          <t>R — centre-right caretaker</t>
         </is>
       </c>
     </row>
@@ -11846,11 +10998,6 @@
           <t>Federalism; property/market economy; gradualism; controlled migration; climate pragmatism; neutrality/security</t>
         </is>
       </c>
-      <c r="O170" s="2" t="inlineStr">
-        <is>
-          <t>L/C — consociational centre</t>
-        </is>
-      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -11911,11 +11058,6 @@
           <t>Religious/traditional social order; state rebuilding; security; market reconstruction; migration/refugees; regional sovereignty</t>
         </is>
       </c>
-      <c r="O171" s="2" t="inlineStr">
-        <is>
-          <t>C+/T — Islamist-national transitional</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -11976,11 +11118,6 @@
           <t>Executive authority; traditional social order; state development; controlled migration; security/regional balancing</t>
         </is>
       </c>
-      <c r="O172" s="2" t="inlineStr">
-        <is>
-          <t>T — authoritarian-traditionalist</t>
-        </is>
-      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -12049,11 +11186,6 @@
           <t>Developmental state; market investment; social conservatism; migration; regional diplomacy</t>
         </is>
       </c>
-      <c r="O173" s="2" t="inlineStr">
-        <is>
-          <t>L/C — developmental-centrist</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -12114,11 +11246,6 @@
           <t>Monarchy/national tradition; authority; mixed economy; controlled migration; energy/infrastructure; regional balancing</t>
         </is>
       </c>
-      <c r="O174" s="2" t="inlineStr">
-        <is>
-          <t>C+/T — monarchic-national conservative hybrid</t>
-        </is>
-      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -12181,11 +11308,6 @@
       <c r="N175" s="2" t="inlineStr">
         <is>
           <t>National identity; customary/social tradition; state development; energy/resources; regional diplomacy</t>
-        </is>
-      </c>
-      <c r="O175" s="2" t="inlineStr">
-        <is>
-          <t>L/C — nationalist-developmental</t>
         </is>
       </c>
     </row>
@@ -12244,11 +11366,6 @@
           <t>Executive continuity; state/resource economy; social traditionalism; security</t>
         </is>
       </c>
-      <c r="O176" s="2" t="inlineStr">
-        <is>
-          <t>T — authoritarian-traditionalist</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -12309,11 +11426,6 @@
           <t>Monarchy/custom; community authority; development; climate; regional diplomacy</t>
         </is>
       </c>
-      <c r="O177" s="2" t="inlineStr">
-        <is>
-          <t>T/C — monarchic-traditionalist</t>
-        </is>
-      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -12382,11 +11494,6 @@
           <t>Market/energy economy; law/order; moderate social policy; migration; regional security</t>
         </is>
       </c>
-      <c r="O178" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centre-right/centrist</t>
-        </is>
-      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -12447,11 +11554,6 @@
           <t>Executive authority; national sovereignty; social conservatism; state role; restrictive migration; security</t>
         </is>
       </c>
-      <c r="O179" s="2" t="inlineStr">
-        <is>
-          <t>T — presidential-authoritarian/traditionalist</t>
-        </is>
-      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -12516,11 +11618,6 @@
           <t>Family/religious values; strong executive; state-guided market economy; restrictive migration; energy development; strategic autonomy</t>
         </is>
       </c>
-      <c r="O180" s="2" t="inlineStr">
-        <is>
-          <t>C+ — religious-national conservative</t>
-        </is>
-      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -12585,11 +11682,6 @@
           <t>Dynastic authority; state/resource economy; social traditionalism; controlled migration; security/neutrality</t>
         </is>
       </c>
-      <c r="O181" s="2" t="inlineStr">
-        <is>
-          <t>T — dynastic-authoritarian traditionalist</t>
-        </is>
-      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -12654,11 +11746,6 @@
           <t>Climate survival; community/custom; public development; migration/mobility</t>
         </is>
       </c>
-      <c r="O182" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centrist</t>
-        </is>
-      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -12727,11 +11814,6 @@
           <t>Executive authority; religious/social conservatism; market + state; security; migration; regional security</t>
         </is>
       </c>
-      <c r="O183" s="2" t="inlineStr">
-        <is>
-          <t>C+/T — nationalist/social conservative</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -12792,11 +11874,6 @@
           <t>National sovereignty; security; state mobilisation; European integration; migration/displacement; defence diplomacy</t>
         </is>
       </c>
-      <c r="O184" s="2" t="inlineStr">
-        <is>
-          <t>L/C — wartime national-centrist</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -12859,11 +11936,6 @@
       <c r="N185" s="2" t="inlineStr">
         <is>
           <t>Dynastic authority; Islamic tradition; state-led diversification; controlled migration; energy/technology; strategic balancing</t>
-        </is>
-      </c>
-      <c r="O185" s="2" t="inlineStr">
-        <is>
-          <t>T — dynastic traditionalist + developmental modernisation</t>
         </is>
       </c>
     </row>
@@ -12930,11 +12002,6 @@
           <t>Welfare/public services; moderate migration reform; climate transition; NATO/US; institutional continuity</t>
         </is>
       </c>
-      <c r="O186" s="2" t="inlineStr">
-        <is>
-          <t>L — centre-left</t>
-        </is>
-      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -13001,11 +12068,6 @@
       <c r="N187" s="2" t="inlineStr">
         <is>
           <t>Property/market + protectionism; traditional family/religious themes; restrictive migration; fossil-fuel expansion; sovereignty/transactional alliances</t>
-        </is>
-      </c>
-      <c r="O187" s="2" t="inlineStr">
-        <is>
-          <t>C+ — national-conservative/populist</t>
         </is>
       </c>
     </row>
@@ -13068,11 +12130,6 @@
           <t>Welfare state; market economy; progressive social policy; climate; regional diplomacy</t>
         </is>
       </c>
-      <c r="O188" s="2" t="inlineStr">
-        <is>
-          <t>L — centre-left</t>
-        </is>
-      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -13141,11 +12198,6 @@
           <t>Executive authority; national/cultural tradition; market reform under state guidance; controlled migration; energy/resources; regional balancing</t>
         </is>
       </c>
-      <c r="O189" s="2" t="inlineStr">
-        <is>
-          <t>T/C — authoritarian-developmental</t>
-        </is>
-      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -13212,11 +12264,6 @@
       <c r="N190" s="2" t="inlineStr">
         <is>
           <t>Customary/community authority; development; climate; migration/mobility; regional diplomacy</t>
-        </is>
-      </c>
-      <c r="O190" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centrist</t>
         </is>
       </c>
     </row>
@@ -13275,11 +12322,6 @@
           <t>Catholic doctrine; hierarchical authority; institutional continuity; social conservatism; humanitarian/multilateral diplomacy</t>
         </is>
       </c>
-      <c r="O191" s="2" t="inlineStr">
-        <is>
-          <t>T — religious-traditionalist</t>
-        </is>
-      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -13340,11 +12382,6 @@
           <t>State intervention; national sovereignty; social traditionalism; controlled migration; oil; security</t>
         </is>
       </c>
-      <c r="O192" s="2" t="inlineStr">
-        <is>
-          <t>L/T — socialist-authoritarian</t>
-        </is>
-      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -13409,11 +12446,6 @@
           <t>Party/state authority; state-guided market economy; national continuity; social discipline; controlled migration; strategic balancing</t>
         </is>
       </c>
-      <c r="O193" s="2" t="inlineStr">
-        <is>
-          <t>T/L — communist-nationalist</t>
-        </is>
-      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -13476,11 +12508,6 @@
       <c r="N194" s="2" t="inlineStr">
         <is>
           <t>Security/order; religious/social tradition; state reconstruction; migration/displacement; regional security</t>
-        </is>
-      </c>
-      <c r="O194" s="2" t="inlineStr">
-        <is>
-          <t>C/T — fragmented transitional</t>
         </is>
       </c>
     </row>
@@ -13543,11 +12570,6 @@
           <t>Market/private enterprise; institutional reform; moderate social policy; mining/energy; regional diplomacy</t>
         </is>
       </c>
-      <c r="O195" s="2" t="inlineStr">
-        <is>
-          <t>L/C — liberal-centrist</t>
-        </is>
-      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -13612,14 +12634,9 @@
           <t>Executive authority; national sovereignty; state/resource economy; traditional social order; security</t>
         </is>
       </c>
-      <c r="O196" s="2" t="inlineStr">
-        <is>
-          <t>T/C — nationalist-authoritarian</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O196"/>
+  <autoFilter ref="A1:N196"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14438,7 +13455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -14549,7 +13566,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Core concepts (Freeden): liberty, rationality, individuality, progress, sociability, the general interest, and limited, accountable power.</t>
+          <t>Core concepts: liberty, individuality, rationality, progress, and limited, accountable power.</t>
         </is>
       </c>
     </row>
@@ -14561,7 +13578,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Core concepts (Freeden): change must be controlled so that it appears natural and organic; social order has extra-human origins (history, God, nature, the market or monarchy) and is independent of human will.</t>
+          <t>Core concepts: change that is controlled and appears organic, and a social order grounded in something beyond human will (history, God, nature, the market or monarchy).</t>
         </is>
       </c>
     </row>
@@ -14573,7 +13590,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Core concepts (Freeden): the constitutive nature of the group, equality, human welfare as the goal of politics, human activity/praxis, and history as the arena of change.</t>
+          <t>Core concepts: the group, equality, human welfare, human activity, and history as the arena of change.</t>
         </is>
       </c>
     </row>
@@ -14585,7 +13602,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Political order is derived from religious doctrine and religious authority. Not one of Freeden's three macro-ideologies; included because his morphological method treats such belief systems as ideologies with their own core concepts (divine sovereignty, sacred law, clerical or dynastic-religious authority).</t>
+          <t>Political order derived from religious doctrine and authority. Not one of Freeden's three main families, but analysable with his method.</t>
         </is>
       </c>
     </row>
@@ -14597,7 +13614,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Residual category, not a Freeden family: hierarchy, order, continuity and state authority dominate the governing ideas, but no liberal, conservative or socialist programme is sustained at the core. Typical of military, personalist and dominant-party governments. Calling these conservative would overstate the presence of conservative morphology; nationalism usually appears as a component.</t>
+          <t>Residual teaching category: order, hierarchy and continuity dominate, with no liberal, conservative or socialist programme at the core.</t>
         </is>
       </c>
     </row>
@@ -14741,7 +13758,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>As in the earlier conservatism scheme (C vs C+), "+" marks a family core combined strongly with a thin-centred ideology (nationalism, populism) or with theocratic or religious-nationalist claims. C+ is national/religious/populist conservatism, S+ left-nationalist or left-populist socialism, L+ national or populist liberalism, RE+ religious-national rule. How power is held (democracy or autocracy) is not part of the ideological code; it is recorded separately as the V-Dem regime type.</t>
+          <t>"+" marks a family core combined strongly with a thin-centred ideology (nationalism, populism) or with theocratic or religious-nationalist claims. C+ is national/religious/populist conservatism, S+ left-nationalist or left-populist socialism, L+ national or populist liberalism, RE+ religious-national rule. How power is held (democracy or autocracy) is not part of the ideological code; it is recorded separately as the V-Dem regime type.</t>
         </is>
       </c>
     </row>
@@ -14789,7 +13806,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Taken directly from the V-Dem Regimes of the World indicator (v2x_regime), V-Dem dataset v16, year 2025: closed autocracy, electoral autocracy, electoral democracy, liberal democracy (Lührmann, Tannenberg and Lindberg 2018). It replaces the earlier "Authoritarian rule" tag, which had been assigned by judgement. The V-Dem note flags borderline cases using v2x_regime_amb, where the confidence interval overlaps a neighbouring category.</t>
+          <t>Taken directly from the V-Dem Regimes of the World indicator (v2x_regime), V-Dem dataset v16, year 2025: closed autocracy, electoral autocracy, electoral democracy, liberal democracy (Lührmann, Tannenberg and Lindberg 2018). The V-Dem note flags borderline cases using v2x_regime_amb, where the confidence interval overlaps a neighbouring category.</t>
         </is>
       </c>
     </row>
@@ -14880,29 +13897,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Previous code</t>
+          <t>Caveat</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>The final column keeps the code from the conservatism-only scheme (C, C+, L/C, R, T and hybrids) so the two classifications can be compared.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Caveat</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
           <t>Ideological codes are interpretive judgements for teaching and discussion, not measurements. Coalitions, caretaker and transitional governments are coded by their dominant governing morphology. The policy column is descriptive and unchanged from the source dataset.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B38"/>
+  <autoFilter ref="A1:B37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14913,7 +13918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -14946,3959 +13951,154 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Freedenian Conservatism Global Dataset (snapshot 2026-10-03, corrected), generated with ChatGPT and supplied for this course; ideological codes revised with Claude.</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n"/>
+          <t>Leaders and policy summaries (snapshot 2026-10-03), generated with ChatGPT; ideological codes assigned with Claude.</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Current leaders</t>
+          <t>Leaders (as stated by the base dataset)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>UN Protocol &amp; Liaison Service</t>
+          <t>Wikipedia - List of current heads of state and government</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>https://www.un.org/dgacm/en/content/protocol/hshgnfa</t>
+          <t>https://en.wikipedia.org/wiki/List_of_current_heads_of_state_and_government</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Current leaders cross-check</t>
+          <t>Freeden framework</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CIA World Leaders</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cia.gov/resources/world-leaders/</t>
-        </is>
-      </c>
+          <t>Freeden, M. (1996) Ideologies and Political Theory: A Conceptual Approach. Oxford: Clarendon Press.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Current heads list used for 2026 snapshot</t>
+          <t>Freeden framework (introductory)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Wikipedia – List of current heads of state and government</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/List_of_current_heads_of_state_and_government</t>
-        </is>
-      </c>
+          <t>Freeden, M. (2003) Ideology: A Very Short Introduction. Oxford: Oxford University Press.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Freeden framework</t>
+          <t>Families and variants</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Stanford Encyclopedia of Philosophy – Conservatism</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>https://seop.illc.uva.nl/entries/conservatism/</t>
-        </is>
-      </c>
+          <t>Freeden, M., Sargent, L.T. and Stears, M. (eds) (2013) The Oxford Handbook of Political Ideologies. Oxford: Oxford University Press.</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Freeden framework</t>
+          <t>Thin-centred nationalism</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Freeden, M. (1996) Ideologies and Political Theory: A Conceptual Approach. Oxford: Clarendon Press.</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n"/>
+          <t>Freeden, M. (1998) "Is Nationalism a Distinct Ideology?" Political Studies 46(4): 748-765.</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1111/1467-9248.00165</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Thin-centred nationalism</t>
+          <t>Thin-centred populism</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Freeden, M. (1998) "Is Nationalism a Distinct Ideology?" Political Studies 46(4): 748-765.</t>
+          <t>Mudde, C. (2004) "The Populist Zeitgeist." Government and Opposition 39(4): 541-563.</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1111/1467-9248.00165</t>
+          <t>https://doi.org/10.1111/j.1477-7053.2004.00135.x</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Freeden framework (introductory)</t>
+          <t>Conservatism (overview)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Freeden, M. (2003) Ideology: A Very Short Introduction. Oxford: Oxford University Press.</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n"/>
+          <t>Stanford Encyclopedia of Philosophy - Conservatism</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>https://plato.stanford.edu/entries/conservatism/</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Families and variants</t>
+          <t>Regime type data</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Freeden, M., Sargent, L.T. and Stears, M. (eds) (2013) The Oxford Handbook of Political Ideologies. Oxford: Oxford University Press.</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n"/>
+          <t>Coppedge, M., Gerring, J., Knutsen, C.H., Lindberg, S.I., Teorell, J. et al. (2026) "V-Dem Country-Year Dataset v16." Varieties of Democracy (V-Dem) Project. Variables v2x_regime and v2x_regime_amb, year 2025; obtained via the vdemdata R package v16.0.</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.23696/vdemds26</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Thin-centred populism</t>
+          <t>Regime type classification</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Mudde, C. (2004) "The Populist Zeitgeist." Government and Opposition 39(4): 541-563.</t>
+          <t>Lührmann, A., Tannenberg, M. and Lindberg, S.I. (2018) "Regimes of the World (RoW): Opening New Avenues for the Comparative Study of Political Regimes." Politics and Governance 6(1): 60-77.</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1111/j.1477-7053.2004.00135.x</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Regime type data</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Coppedge, M., Gerring, J., Knutsen, C.H., Lindberg, S.I., Teorell, J. et al. (2026) "V-Dem Country-Year Dataset v16." Varieties of Democracy (V-Dem) Project. Variables v2x_regime and v2x_regime_amb, year 2025; obtained via the vdemdata R package v16.0.</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.23696/vdemds26</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Regime type classification</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Lührmann, A., Tannenberg, M. and Lindberg, S.I. (2018) "Regimes of the World (RoW): Opening New Avenues for the Comparative Study of Political Regimes." Politics and Governance 6(1): 60-77.</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
           <t>https://doi.org/10.17645/pag.v6i1.1214</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Regime type data</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Coppedge, M., Gerring, J., Knutsen, C.H., Lindberg, S.I., Teorell, J. et al. (2026) "V-Dem Country-Year Dataset v16." Varieties of Democracy (V-Dem) Project. Variables v2x_regime and v2x_regime_amb, year 2025; obtained via the vdemdata R package v16.0.</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.23696/vdemds26</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Regime type classification</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Lührmann, A., Tannenberg, M. and Lindberg, S.I. (2018) "Regimes of the World (RoW): Opening New Avenues for the Comparative Study of Political Regimes." Politics and Governance 6(1): 60-77.</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.17645/pag.v6i1.1214</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Regime type data</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Coppedge, M., Gerring, J., Knutsen, C.H., Lindberg, S.I., Teorell, J. et al. (2026) "V-Dem Country-Year Dataset v16." Varieties of Democracy (V-Dem) Project. Variables v2x_regime and v2x_regime_amb, year 2025; obtained via the vdemdata R package v16.0.</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.23696/vdemds26</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Regime type classification</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Lührmann, A., Tannenberg, M. and Lindberg, S.I. (2018) "Regimes of the World (RoW): Opening New Avenues for the Comparative Study of Political Regimes." Politics and Governance 6(1): 60-77.</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.17645/pag.v6i1.1214</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C17"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F115"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Old value</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>New value</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Regime type</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>All 195 states</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Adjacent concepts / regime context</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>"Authoritarian rule" tag (assigned by judgement)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Regime type from V-Dem Regimes of the World, 2025 (v16), with borderline flags</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Regime type now comes from an established expert-coded dataset instead of a judgement tag</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Regime type</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>All 195 states</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Variant definitions</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>"+" variants could rest on authoritarian rule; residual category named "Traditionalist-authoritarian"</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>"+" variants rest on nationalism, populism or theocratic/religious-nationalist claims; residual category renamed "Traditionalist (order-centred)"</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Keeps the ideological code separate from regime type, which V-Dem now measures; no state changed variant as a result</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Regime type</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>18 states</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Decontested form</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Descriptions using "authoritarian" (e.g. "Developmental authoritarianism")</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Descriptions of the governing ideas only (e.g. "State-led developmentalism")</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>How power is held is now shown by the V-Dem column, so the ideological description no longer repeats it</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Notice</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>All 195 states</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>"Created with Claude. Illustrative only." notice; ChatGPT origin of the base dataset recorded; "+" variants worded as theocratic or religious-nationalist claims rather than religion</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Clarify provenance and that the dataset is a teaching illustration, not research</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>All 195 states</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Five families with nationalism as a possible primary family (LIB, CON, SOC, NAT, REL)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Variants within each family (L, L+; C, C+, Cm; S, S+, SM; RE, RE+) plus residual T; nationalism only as a component</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Nationalism is thin-centred (Freeden 1998) and is not treated as a host ideology; variants show the range of decontested forms within each family, as C and C+ did in the conservatism scheme</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>NAT/SOC</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>S+</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Angola</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>NAT/SOC</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>T/SOC</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Azerbaijan</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Bangladesh</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>NAT/CON</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Belarus</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>NAT/CON</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>T/SOC</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Bosnia and Herzegovina</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>NAT/LIB</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>C+/SOC</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Bulgaria</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>NAT/SOC</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>S+</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Burkina Faso</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>NAT/SOC</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>S+</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Burundi</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Cambodia</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>NAT/CON</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>T/CON</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Cameroon</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>NAT/CON</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Central African Republic</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Chad</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Comoros</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>NAT/REL</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>T/REL</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Czechia</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>NAT/CON</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Djibouti</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>El Salvador</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>NAT/CON</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Equatorial Guinea</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Eritrea</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>NAT/SOC</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>T/SOC</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Ethiopia</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>NAT/LIB</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>T/LIB</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Gabon</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Georgia</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>NAT/CON</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Guinea</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Guinea-Bissau</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>NAT/CON</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>NAT/CON</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Israel</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>NAT/CON</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Kazakhstan</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Kyrgyzstan</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>NAT/CON</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>T/CON</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Libya</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>NAT/LIB</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>T/LIB</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Madagascar</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Maldives</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>NAT/REL</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Mali</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Mauritania</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>NAT/REL</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>T/REL</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Mozambique</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>NAT/SOC</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>T/SOC</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Myanmar</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>NAT/REL</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>T/REL</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Nicaragua</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>NAT/SOC</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>S+</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Niger</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>North Korea</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>NAT/SOC</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>SM</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Pakistan</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>NAT/REL</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Palestine</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>S+</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Republic of the Congo</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>NAT/SOC</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>T/SOC</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Russia</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>NAT/CON</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Rwanda</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>NAT/SOC</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>S+</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Serbia</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>NAT/CON</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Slovakia</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>NAT/SOC</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>S+/CON</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Somalia</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>NAT/REL</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>T/REL</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>South Sudan</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Sudan</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>Tajikistan</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>Tanzania</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>NAT/SOC</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>T/SOC</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Timor-Leste</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>L+</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Togo</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>Turkmenistan</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Uganda</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>NAT/CON</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>T/CON</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>NAT/CON</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Yemen</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>NAT/REL</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>T/REL</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>T/SOC</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>Former NAT-primary state reassigned to the family whose core concepts it draws on, or to the residual T category</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>All 195 states</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Conservatism-only scheme (C, C+, L/C, R, T)</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>Freeden ideological families (LIB, CON, SOC, NAT, REL) + secondary family + thin-centred components</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>Dataset broadened from "how conservative is this government?" to "which ideological family organises it?"; previous code retained in the last column</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Lithuania</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>R - centre-right security-oriented</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>SOC/NAT - social democracy (LSDP-led coalition)</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>Prime Minister Sinkevičius leads the Social Democratic Party (LSDP); previous R code did not match the governing party</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>T-coded states (39)</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>T - traditionalist-authoritarian</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>NAT, CON (monarchical traditionalism) or REL</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>The residual T category is not a Freeden family; split by the core concepts that organise each regime</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>Recoding</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>L/C-coded states (59)</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>L/C</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>LIB or SOC (social democracy) by governing party, NAT where liberation/developmental nationalism dominates</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>L/C merged liberal and socialist governments; Freeden treats liberalism and socialism as distinct macro-ideologies</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>Factual</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>Bangladesh</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Head of state</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>Mohammed Shahabuddin</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>Mirza Fakhrul Islam Alamgir</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>Shahabuddin resigned 24 Jul 2026; Alamgir elected 20 Aug 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>Bolivia</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>C/L — centre-right liberal</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>R — centre-right liberal</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>Bosnia and Herzegovina</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>C/L — fragmented coalition</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>L/C — fragmented coalition</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>Congo, Democratic Republic of the</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>C/L — centrist-developmental</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centrist-developmental</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>C/L — moderate centre-right</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>R — moderate centre-right</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>C/L — liberal-centrist, not primarily conservative</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>L/C — liberal-centrist, not primarily conservative</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>C/L — developmental-centrist</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>L/C — developmental-centrist</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>Ivory Coast</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>C/L — developmental centre-right</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>R — developmental centre-right</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>Kiribati</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>C/L — developmental-centrist</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>L/C — developmental-centrist</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>Latvia</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>C/L — centre-right liberal</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>R — centre-right liberal</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>Lebanon</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>C/L — institutional/coalitional</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>L/C — institutional/coalitional</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>Lesotho</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>C/L — centre-right developmental</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>R — centre-right developmental</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>Libya</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>C/L — fragmented transitional</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>L/C — fragmented transitional</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>Lithuania</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>C/L — centre-right security-oriented</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>R — centre-right security-oriented</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>Malawi</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>C/L — centre-right</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>R — centre-right</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>C/L — coalition/centrist</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>L/C — coalition/centrist</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>Moldova</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>C/L — liberal-centrist</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>L/C — liberal-centrist</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>Nepal</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>C/L — populist-centrist</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>L/C — populist-centrist</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>Panama</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>C/L — centre-right</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>R — centre-right</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>Papua New Guinea</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>C/L — developmental-centrist</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>L/C — developmental-centrist</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>C/L — split executive</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>L/C — split executive</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>Romania</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>C/L — centrist caretaker</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centrist caretaker</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>Saint Vincent and the Grenadines</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>C/L — centre-right</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>R — centre-right</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>Samoa</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>C/L — customary/centrist</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>L/C — customary/centrist</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>San Marino</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>C/L — centrist</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centrist</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>São Tomé and Príncipe</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>C/L — centre-right/centrist</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centre-right/centrist</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>C/L — nationalist-developmental</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>L/C — nationalist-developmental</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>Solomon Islands</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>C/L — centre-right/coalitional</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>R — centre-right/coalitional</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>C/L — coalition/centrist</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>L/C — coalition/centrist</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>C/L — centre-right caretaker</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>R — centre-right caretaker</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centre-right/liberal market government without a conservative morphology; Methodology code R</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>C/L — consociational centre</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>L/C — consociational centre</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>Tanzania</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>C/L — developmental-centrist</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>L/C — developmental-centrist</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>Timor-Leste</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>C/L — nationalist-developmental</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>L/C — nationalist-developmental</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>Trinidad and Tobago</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>C/L — centre-right/centrist</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>L/C — centre-right/centrist</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>Ukraine</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>C/L — wartime national-centrist</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>L/C — wartime national-centrist</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>C/L split</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>C/L — liberal-centrist</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>L/C — liberal-centrist</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>Label describes a centrist/developmental/coalitional/transitional government; Methodology says L/C is not coded primarily conservative</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>Naming</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>Congo, Democratic Republic of the</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>Congo, Democratic Republic of the</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>Democratic Republic of the Congo</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>Use UN official short name</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>Naming</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>Congo, Republic of the</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>Congo, Republic of the</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>Republic of the Congo</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>Use UN official short name</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>Naming</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>Ivory Coast</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>Ivory Coast</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>Côte d'Ivoire</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>Use UN official short name</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>Naming</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>Micronesia</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>Micronesia</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>Federated States of Micronesia</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>Use UN official short name</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>Naming</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Head of state / government</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>Bongbong Marcos</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>Ferdinand "Bongbong" Marcos Jr.</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>Full formal name</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>Naming</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>Saudi Arabia</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Head of state</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>Salman</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>Salman bin Abdulaziz Al Saud</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>Full name for consistency</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>Naming</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>Turkey</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>Turkey</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>Türkiye</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>Use UN official short name</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F115"/>
+  <autoFilter ref="A1:C11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>